--- a/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2365.74</v>
+        <v>27573.39</v>
       </c>
       <c r="C4" t="n">
-        <v>589176</v>
+        <v>5355000</v>
       </c>
       <c r="D4" t="n">
-        <v>462924</v>
+        <v>4207500</v>
       </c>
       <c r="E4" t="n">
-        <v>146700</v>
+        <v>1445400</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>6540</v>
+        <v>81450</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>9090</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19590</v>
+        <v>199290</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3915.99</v>
+        <v>30315.15</v>
       </c>
       <c r="C5" t="n">
-        <v>688464</v>
+        <v>4651416</v>
       </c>
       <c r="D5" t="n">
-        <v>540936</v>
+        <v>3654684</v>
       </c>
       <c r="E5" t="n">
-        <v>118800</v>
+        <v>1084500</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>8610</v>
+        <v>88380</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>7560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20760</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3992.31</v>
+        <v>35101.17</v>
       </c>
       <c r="C6" t="n">
-        <v>405216</v>
+        <v>4851504</v>
       </c>
       <c r="D6" t="n">
-        <v>318384</v>
+        <v>3811896</v>
       </c>
       <c r="E6" t="n">
-        <v>65700</v>
+        <v>864900</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>8340</v>
+        <v>84750</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>12150</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>23100</v>
+        <v>211500</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2616.48</v>
+        <v>27787.14</v>
       </c>
       <c r="C7" t="n">
-        <v>226800</v>
+        <v>2284128</v>
       </c>
       <c r="D7" t="n">
-        <v>178200</v>
+        <v>1794672</v>
       </c>
       <c r="E7" t="n">
-        <v>40500</v>
+        <v>252900</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4920</v>
+        <v>63390</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3960</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10110</v>
+        <v>130650</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1348.56</v>
+        <v>23272.92</v>
       </c>
       <c r="C8" t="n">
-        <v>65520</v>
+        <v>1658160</v>
       </c>
       <c r="D8" t="n">
-        <v>51480</v>
+        <v>1302840</v>
       </c>
       <c r="E8" t="n">
-        <v>8100</v>
+        <v>129600</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1860</v>
+        <v>38370</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3870</v>
+        <v>76740</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>643.3200000000001</v>
+        <v>12784.05</v>
       </c>
       <c r="C9" t="n">
-        <v>18144</v>
+        <v>855792</v>
       </c>
       <c r="D9" t="n">
-        <v>14256</v>
+        <v>672408</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>45900</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18630</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>810</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>780</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>393.12</v>
+        <v>1375.74</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>113904</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>89496</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>2520</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>630</v>
+        <v>9270</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>220.23</v>
+        <v>268.2</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>26208</v>
       </c>
       <c r="D11" t="n">
-        <v>1980</v>
+        <v>20592</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.24</v>
+        <v>195.12</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>8064</v>
       </c>
       <c r="D12" t="n">
-        <v>1188</v>
+        <v>6336</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.93</v>
+        <v>90</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>49.05</v>
+        <v>13.68</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1980</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.68</v>
+        <v>17.19</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>9.9</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.17</v>
+        <v>5.04</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19">
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1762.2</v>
+        <v>13641.82</v>
       </c>
       <c r="C5" t="n">
-        <v>378655.2</v>
+        <v>2558278.8</v>
       </c>
       <c r="D5" t="n">
-        <v>179049.82</v>
+        <v>1209700.4</v>
       </c>
       <c r="E5" t="n">
-        <v>13103.64</v>
+        <v>119620.35</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2721.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4359.6</v>
+        <v>40068</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3193.85</v>
+        <v>28080.94</v>
       </c>
       <c r="C6" t="n">
-        <v>364694.4</v>
+        <v>4366353.6</v>
       </c>
       <c r="D6" t="n">
-        <v>161420.69</v>
+        <v>1932631.27</v>
       </c>
       <c r="E6" t="n">
-        <v>11103.3</v>
+        <v>146168.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>417</v>
+        <v>4237.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>6925.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8547</v>
+        <v>78255</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2485.66</v>
+        <v>26397.78</v>
       </c>
       <c r="C7" t="n">
-        <v>226800</v>
+        <v>2284128</v>
       </c>
       <c r="D7" t="n">
-        <v>113691.6</v>
+        <v>1145000.74</v>
       </c>
       <c r="E7" t="n">
-        <v>8614.35</v>
+        <v>53791.83</v>
       </c>
       <c r="F7" t="n">
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>738</v>
+        <v>9508.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2890.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6066</v>
+        <v>78390</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1348.56</v>
+        <v>23272.92</v>
       </c>
       <c r="C8" t="n">
-        <v>65520</v>
+        <v>1658160</v>
       </c>
       <c r="D8" t="n">
-        <v>37889.28</v>
+        <v>958890.24</v>
       </c>
       <c r="E8" t="n">
-        <v>1986.93</v>
+        <v>31790.88</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1209</v>
+        <v>24940.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>382.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2747.7</v>
+        <v>54485.4</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>643.3200000000001</v>
+        <v>12784.05</v>
       </c>
       <c r="C9" t="n">
-        <v>18144</v>
+        <v>855792</v>
       </c>
       <c r="D9" t="n">
-        <v>11447.57</v>
+        <v>539943.62</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>12287.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>688.5</v>
+        <v>15835.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11921,13 +11915,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>631.8</v>
+        <v>32805</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>393.12</v>
+        <v>1375.74</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>113904</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>77861.52</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1305</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>420</v>
+        <v>2520</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>560.7</v>
+        <v>8250.299999999999</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>220.23</v>
+        <v>268.2</v>
       </c>
       <c r="C11" t="n">
-        <v>2520</v>
+        <v>26208</v>
       </c>
       <c r="D11" t="n">
-        <v>1779.03</v>
+        <v>18501.91</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>368.82</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.24</v>
+        <v>195.12</v>
       </c>
       <c r="C12" t="n">
-        <v>1512</v>
+        <v>8064</v>
       </c>
       <c r="D12" t="n">
-        <v>1101.28</v>
+        <v>5873.47</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.93</v>
+        <v>90</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1504.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>49.05</v>
+        <v>13.68</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2520</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1924.56</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.68</v>
+        <v>17.19</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>9.9</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.17</v>
+        <v>5.04</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19">
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3876830.1</v>
+        <v>30011998.5</v>
       </c>
       <c r="C5" t="n">
-        <v>20826036</v>
+        <v>140705334</v>
       </c>
       <c r="D5" t="n">
-        <v>18143117.86</v>
+        <v>122578941.94</v>
       </c>
       <c r="E5" t="n">
-        <v>2414214.63</v>
+        <v>22038853.28</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.36</v>
+        <v>16666.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>752930.64</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>157499.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>41067.43</v>
+        <v>377440.56</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7026465.6</v>
+        <v>61778059.2</v>
       </c>
       <c r="C6" t="n">
-        <v>20058192</v>
+        <v>240149448</v>
       </c>
       <c r="D6" t="n">
-        <v>16356758.32</v>
+        <v>195833526.79</v>
       </c>
       <c r="E6" t="n">
-        <v>2045671.99</v>
+        <v>26930010.74</v>
       </c>
       <c r="F6" t="n">
-        <v>20833.5</v>
+        <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7714.5</v>
+        <v>78393.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1915939.57</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>80512.74000000001</v>
+        <v>737162.1</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5468443.2</v>
+        <v>58075122.6</v>
       </c>
       <c r="C7" t="n">
-        <v>12474000</v>
+        <v>125627040</v>
       </c>
       <c r="D7" t="n">
-        <v>11520369.83</v>
+        <v>116022924.58</v>
       </c>
       <c r="E7" t="n">
-        <v>1587107.84</v>
+        <v>9910606.76</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13653</v>
+        <v>175907.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>799739.8199999999</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>57141.72</v>
+        <v>738433.8</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2966832</v>
+        <v>51200424</v>
       </c>
       <c r="C8" t="n">
-        <v>3603600</v>
+        <v>91198800</v>
       </c>
       <c r="D8" t="n">
-        <v>3839320.74</v>
+        <v>97164348.02</v>
       </c>
       <c r="E8" t="n">
-        <v>366071.98</v>
+        <v>5857151.73</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>22366.5</v>
+        <v>461399.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>105818.62</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>25883.33</v>
+        <v>513252.47</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1415304</v>
+        <v>28124910</v>
       </c>
       <c r="C9" t="n">
-        <v>997920</v>
+        <v>47068560</v>
       </c>
       <c r="D9" t="n">
-        <v>1159982.07</v>
+        <v>54712487.42</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>2263836.1</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>12737.25</v>
+        <v>292956.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12853,13 +12847,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>55416.35</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5951.56</v>
+        <v>309023.1</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>864864</v>
+        <v>3026628</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>6264720</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>7889707.82</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>240433.2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7770</v>
+        <v>46620</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5281.79</v>
+        <v>77717.83</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>484506</v>
+        <v>590040</v>
       </c>
       <c r="C11" t="n">
-        <v>138600</v>
+        <v>1441440</v>
       </c>
       <c r="D11" t="n">
-        <v>180269.11</v>
+        <v>1874798.74</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>67951.39999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>16650</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>40411.8</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>343728</v>
+        <v>429264</v>
       </c>
       <c r="C12" t="n">
-        <v>83160</v>
+        <v>443520</v>
       </c>
       <c r="D12" t="n">
-        <v>111592.3</v>
+        <v>595158.92</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>2775</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>32499</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>371646</v>
+        <v>198000</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>152401.13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>11586.6</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>107910</v>
+        <v>30096</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>138600</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>195015.66</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>1665</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>10296</v>
+        <v>37818</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>21780</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2574</v>
+        <v>11088</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2970</v>
+        <v>3168</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>6217.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>198</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>68265</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1130.4</v>
       </c>
     </row>
     <row r="20">
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>160506.72</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>27573.39</v>
+        <v>28316.25</v>
       </c>
       <c r="C4" t="n">
-        <v>5355000</v>
+        <v>2832984</v>
       </c>
       <c r="D4" t="n">
-        <v>4207500</v>
+        <v>2225916</v>
       </c>
       <c r="E4" t="n">
-        <v>1445400</v>
+        <v>891900</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>81450</v>
+        <v>84540</v>
       </c>
       <c r="H4" t="n">
-        <v>9090</v>
+        <v>9930</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>199290</v>
+        <v>274380</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>30315.15</v>
+        <v>7966.8</v>
       </c>
       <c r="C5" t="n">
-        <v>4651416</v>
+        <v>546840</v>
       </c>
       <c r="D5" t="n">
-        <v>3654684</v>
+        <v>429660</v>
       </c>
       <c r="E5" t="n">
-        <v>1084500</v>
+        <v>212400</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>88380</v>
+        <v>18990</v>
       </c>
       <c r="H5" t="n">
-        <v>7560</v>
+        <v>1860</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>190800</v>
+        <v>80880</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>35101.17</v>
+        <v>703.26</v>
       </c>
       <c r="C6" t="n">
-        <v>4851504</v>
+        <v>63504</v>
       </c>
       <c r="D6" t="n">
-        <v>3811896</v>
+        <v>49896</v>
       </c>
       <c r="E6" t="n">
-        <v>864900</v>
+        <v>19800</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>84750</v>
+        <v>1920</v>
       </c>
       <c r="H6" t="n">
-        <v>12150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>211500</v>
+        <v>12210</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>27787.14</v>
+        <v>105.66</v>
       </c>
       <c r="C7" t="n">
-        <v>2284128</v>
+        <v>13104</v>
       </c>
       <c r="D7" t="n">
-        <v>1794672</v>
+        <v>10296</v>
       </c>
       <c r="E7" t="n">
-        <v>252900</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>63390</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>130650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23272.92</v>
+        <v>7.92</v>
       </c>
       <c r="C8" t="n">
-        <v>1658160</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1302840</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>129600</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>38370</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>76740</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>12784.05</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>855792</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>672408</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18630</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13785,13 +13779,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>40500</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1375.74</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>113904</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>89496</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9270</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>268.2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26208</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>20592</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4290</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>195.12</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>8064</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>6336</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.68</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.19</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,13 +14135,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13641.82</v>
+        <v>3585.06</v>
       </c>
       <c r="C5" t="n">
-        <v>2558278.8</v>
+        <v>300762</v>
       </c>
       <c r="D5" t="n">
-        <v>1209700.4</v>
+        <v>142217.46</v>
       </c>
       <c r="E5" t="n">
-        <v>119620.35</v>
+        <v>23427.72</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2721.6</v>
+        <v>669.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40068</v>
+        <v>16984.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>28080.94</v>
+        <v>562.61</v>
       </c>
       <c r="C6" t="n">
-        <v>4366353.6</v>
+        <v>57153.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1932631.27</v>
+        <v>25297.27</v>
       </c>
       <c r="E6" t="n">
-        <v>146168.1</v>
+        <v>3346.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4237.5</v>
+        <v>96</v>
       </c>
       <c r="H6" t="n">
-        <v>6925.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>78255</v>
+        <v>4517.7</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>26397.78</v>
+        <v>100.38</v>
       </c>
       <c r="C7" t="n">
-        <v>2284128</v>
+        <v>13104</v>
       </c>
       <c r="D7" t="n">
-        <v>1145000.74</v>
+        <v>6568.85</v>
       </c>
       <c r="E7" t="n">
-        <v>53791.83</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>9508.5</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>2890.8</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>78390</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23272.92</v>
+        <v>7.92</v>
       </c>
       <c r="C8" t="n">
-        <v>1658160</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>958890.24</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>31790.88</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>24940.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>382.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>54485.4</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>12784.05</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>855792</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>539943.62</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>12287.43</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>15835.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14717,13 +14711,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>32805</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1375.74</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>113904</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>77861.52</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1305</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8250.299999999999</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>268.2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26208</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>18501.91</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>368.82</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4290</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>195.12</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>8064</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5873.47</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1504.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>13.68</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1924.56</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>17.19</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,13 +15067,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>30011998.5</v>
+        <v>7887132</v>
       </c>
       <c r="C5" t="n">
-        <v>140705334</v>
+        <v>16541910</v>
       </c>
       <c r="D5" t="n">
-        <v>122578941.94</v>
+        <v>14410895.22</v>
       </c>
       <c r="E5" t="n">
-        <v>22038853.28</v>
+        <v>4316323.13</v>
       </c>
       <c r="F5" t="n">
-        <v>16666.8</v>
+        <v>5833.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>752930.64</v>
+        <v>185244.84</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>157499.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>377440.56</v>
+        <v>159996.82</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>61778059.2</v>
+        <v>1237737.6</v>
       </c>
       <c r="C6" t="n">
-        <v>240149448</v>
+        <v>3143448</v>
       </c>
       <c r="D6" t="n">
-        <v>195833526.79</v>
+        <v>2563372.57</v>
       </c>
       <c r="E6" t="n">
-        <v>26930010.74</v>
+        <v>616503.89</v>
       </c>
       <c r="F6" t="n">
-        <v>16666.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>78393.75</v>
+        <v>1776</v>
       </c>
       <c r="H6" t="n">
-        <v>1915939.57</v>
+        <v>42576.43</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>737162.1</v>
+        <v>42556.73</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>58075122.6</v>
+        <v>220829.4</v>
       </c>
       <c r="C7" t="n">
-        <v>125627040</v>
+        <v>720720</v>
       </c>
       <c r="D7" t="n">
-        <v>116022924.58</v>
+        <v>665621.37</v>
       </c>
       <c r="E7" t="n">
-        <v>9910606.76</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>175907.25</v>
+        <v>166.5</v>
       </c>
       <c r="H7" t="n">
-        <v>799739.8199999999</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>738433.8</v>
+        <v>6782.4</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>51200424</v>
+        <v>17424</v>
       </c>
       <c r="C8" t="n">
-        <v>91198800</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>97164348.02</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5857151.73</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>461399.25</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>105818.62</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>513252.47</v>
+        <v>1404.52</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>28124910</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>47068560</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>54712487.42</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2263836.1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>292956.75</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,13 +15643,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>55416.35</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>309023.1</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>3026628</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>6264720</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>7889707.82</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>46620</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>77717.83</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>590040</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1441440</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1874798.74</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>16650</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>40411.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>429264</v>
-      </c>
-      <c r="C12" t="n">
-        <v>443520</v>
-      </c>
-      <c r="D12" t="n">
-        <v>595158.92</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>32499</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>198000</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11586.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>30096</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>37818</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>21780</v>
-      </c>
-      <c r="C16" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D16" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>11088</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3168</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6217.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>198</v>
-      </c>
-      <c r="C19" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D19" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>68265</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1130.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D20" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4310.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1078056</v>
-      </c>
-      <c r="D4" t="n">
-        <v>847044</v>
-      </c>
-      <c r="E4" t="n">
-        <v>317700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>12</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14970</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>38040</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5636.52</v>
-      </c>
-      <c r="C5" t="n">
-        <v>856800</v>
-      </c>
-      <c r="D5" t="n">
-        <v>673200</v>
-      </c>
-      <c r="E5" t="n">
-        <v>189000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17130</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2490</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>33390</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5383.44</v>
-      </c>
-      <c r="C6" t="n">
-        <v>540792</v>
-      </c>
-      <c r="D6" t="n">
-        <v>424908</v>
-      </c>
-      <c r="E6" t="n">
-        <v>99900</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8250</v>
-      </c>
-      <c r="H6" t="n">
-        <v>840</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4840.02</v>
-      </c>
-      <c r="C7" t="n">
-        <v>276192</v>
-      </c>
-      <c r="D7" t="n">
-        <v>217008</v>
-      </c>
-      <c r="E7" t="n">
-        <v>54000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4680</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>13710</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4040.46</v>
-      </c>
-      <c r="C8" t="n">
-        <v>203112</v>
-      </c>
-      <c r="D8" t="n">
-        <v>159588</v>
-      </c>
-      <c r="E8" t="n">
-        <v>28800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3960</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>13950</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2702.88</v>
-      </c>
-      <c r="C9" t="n">
-        <v>78120</v>
-      </c>
-      <c r="D9" t="n">
-        <v>61380</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2790</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5820</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1849.95</v>
-      </c>
-      <c r="C10" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D10" t="n">
-        <v>24156</v>
-      </c>
-      <c r="E10" t="n">
-        <v>900</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>390</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>974.0700000000001</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6732</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>621.54</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3024</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2376</v>
-      </c>
-      <c r="E12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>391.86</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3024</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2376</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>349.92</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>431.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>792</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>315</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2536.43</v>
-      </c>
-      <c r="C5" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D5" t="n">
-        <v>222829.2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>20846.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>896.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7011.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4306.75</v>
-      </c>
-      <c r="C6" t="n">
-        <v>486712.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>215428.36</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16883.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>412.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>478.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8103</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4598.02</v>
-      </c>
-      <c r="C7" t="n">
-        <v>276192</v>
-      </c>
-      <c r="D7" t="n">
-        <v>138451.1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11485.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>702</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8226</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4040.46</v>
-      </c>
-      <c r="C8" t="n">
-        <v>203112</v>
-      </c>
-      <c r="D8" t="n">
-        <v>117456.77</v>
-      </c>
-      <c r="E8" t="n">
-        <v>7064.64</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2574</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>9904.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2702.88</v>
-      </c>
-      <c r="C9" t="n">
-        <v>78120</v>
-      </c>
-      <c r="D9" t="n">
-        <v>49288.14</v>
-      </c>
-      <c r="E9" t="n">
-        <v>722.79</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2371.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4714.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1849.95</v>
-      </c>
-      <c r="C10" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D10" t="n">
-        <v>21015.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>261</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>390</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>907.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>974.0700000000001</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8568</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6048.7</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>621.54</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3024</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2202.55</v>
-      </c>
-      <c r="E12" t="n">
-        <v>430.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>391.86</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3024</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2256.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>349.92</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1154.74</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>431.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D15" t="n">
-        <v>780.91</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>315</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5580154.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>25918200</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22579282.84</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3840796.01</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>247989.06</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>66052.10000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9474854.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26769204</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21829355.31</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3110542.34</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12500.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7631.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>132460.02</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>76330.25999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>10115641.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>15190560</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14029250.37</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2116143.79</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12987</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>77488.92</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8889012</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11171160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>11901894.3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1301589.27</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>47619</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>93300.39</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5946336</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4296600</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4994367.23</v>
-      </c>
-      <c r="E9" t="n">
-        <v>133166.83</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>43872.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>44407.76</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>4069890</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1690920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2129522.91</v>
-      </c>
-      <c r="E10" t="n">
-        <v>48086.64</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>7215</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8551.48</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2142954</v>
-      </c>
-      <c r="C11" t="n">
-        <v>471240</v>
-      </c>
-      <c r="D11" t="n">
-        <v>612914.97</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3108.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1367388</v>
-      </c>
-      <c r="C12" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D12" t="n">
-        <v>223184.59</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>862092</v>
-      </c>
-      <c r="C13" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D13" t="n">
-        <v>228601.7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>769824</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>949410</v>
-      </c>
-      <c r="C15" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D15" t="n">
-        <v>79129.81</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>693000</v>
-      </c>
-      <c r="C16" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D16" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>104940</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>94446</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>28316.25</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2832984</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2225916</v>
-      </c>
-      <c r="E4" t="n">
-        <v>891900</v>
-      </c>
-      <c r="F4" t="n">
-        <v>33</v>
-      </c>
-      <c r="G4" t="n">
-        <v>84540</v>
-      </c>
-      <c r="H4" t="n">
-        <v>9930</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>274380</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7966.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>546840</v>
-      </c>
-      <c r="D5" t="n">
-        <v>429660</v>
-      </c>
-      <c r="E5" t="n">
-        <v>212400</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>18990</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1860</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>80880</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>703.26</v>
-      </c>
-      <c r="C6" t="n">
-        <v>63504</v>
-      </c>
-      <c r="D6" t="n">
-        <v>49896</v>
-      </c>
-      <c r="E6" t="n">
-        <v>19800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H6" t="n">
-        <v>270</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>12210</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>105.66</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13104</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10296</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3585.06</v>
-      </c>
-      <c r="C5" t="n">
-        <v>300762</v>
-      </c>
-      <c r="D5" t="n">
-        <v>142217.46</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23427.72</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>669.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>16984.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>562.61</v>
-      </c>
-      <c r="C6" t="n">
-        <v>57153.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>25297.27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3346.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>96</v>
-      </c>
-      <c r="H6" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4517.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>100.38</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13104</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6568.85</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>149.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>60</v>
+        <v>565.2</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7887132</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16541910</v>
-      </c>
-      <c r="D5" t="n">
-        <v>14410895.22</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4316323.13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>185244.84</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>159996.82</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1237737.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3143448</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2563372.57</v>
-      </c>
-      <c r="E6" t="n">
-        <v>616503.89</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1776</v>
-      </c>
-      <c r="H6" t="n">
-        <v>42576.43</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>42556.73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>220829.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>720720</v>
-      </c>
-      <c r="D7" t="n">
-        <v>665621.37</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6782.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>17424</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1404.52</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>565.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>69060</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>41</v>
@@ -576,7 +576,7 @@
         <v>49080</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
@@ -614,7 +614,7 @@
         <v>57150</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>10</v>
@@ -652,7 +652,7 @@
         <v>26130</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>13</v>
@@ -690,7 +690,7 @@
         <v>6270</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
@@ -766,7 +766,7 @@
         <v>5340</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -880,7 +880,7 @@
         <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>2940</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1698,7 +1698,7 @@
         <v>5310</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1812,7 +1812,7 @@
         <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>2499</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -2630,7 +2630,7 @@
         <v>5310</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -2744,7 +2744,7 @@
         <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>691348.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -3562,7 +3562,7 @@
         <v>1469011.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>735993.6</v>
       </c>
       <c r="J10" t="n">
         <v>116666</v>
@@ -3676,7 +3676,7 @@
         <v>224086.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>9090</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>
@@ -9896,7 +9896,7 @@
         <v>7560</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>9</v>
@@ -9934,7 +9934,7 @@
         <v>12150</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -9972,7 +9972,7 @@
         <v>3960</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>17668.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>7.2</v>
@@ -10866,7 +10866,7 @@
         <v>32575.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -10904,7 +10904,7 @@
         <v>19074.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>9.1</v>
@@ -10942,7 +10942,7 @@
         <v>5329.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>5.95</v>
@@ -11018,7 +11018,7 @@
         <v>5340</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -11132,7 +11132,7 @@
         <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2721.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>2.7</v>
@@ -11798,7 +11798,7 @@
         <v>6925.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -11836,7 +11836,7 @@
         <v>2890.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11950,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>752930.64</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>157499.1</v>
@@ -12730,7 +12730,7 @@
         <v>1915939.57</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>58333</v>
@@ -12768,7 +12768,7 @@
         <v>799739.8199999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>632494.5</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>9930</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>4888073.52</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>419997.6</v>
@@ -16458,7 +16458,7 @@
         <v>9012012.07</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>291665</v>
@@ -16496,7 +16496,7 @@
         <v>5277071.08</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>843326</v>
       </c>
       <c r="J7" t="n">
         <v>530830.3</v>
@@ -16534,7 +16534,7 @@
         <v>1474406.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>347081.35</v>
@@ -16610,7 +16610,7 @@
         <v>1477311</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1103990.4</v>
       </c>
       <c r="J10" t="n">
         <v>174999</v>
@@ -16724,7 +16724,7 @@
         <v>224086.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>8910</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -17428,7 +17428,7 @@
         <v>15240</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>9</v>
@@ -18360,7 +18360,7 @@
         <v>11125.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>6.3</v>
@@ -19292,7 +19292,7 @@
         <v>3077786.58</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>367497.9</v>
@@ -20110,7 +20110,7 @@
         <v>25920</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="L4" t="n">
         <v>1331070</v>
@@ -582,7 +582,7 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="L5" t="n">
         <v>832110</v>
@@ -620,7 +620,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="L6" t="n">
         <v>637950</v>
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="L7" t="n">
         <v>493980</v>
@@ -696,7 +696,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="L8" t="n">
         <v>386160</v>
@@ -734,7 +734,7 @@
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="L9" t="n">
         <v>271770</v>
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="L10" t="n">
         <v>180150</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L11" t="n">
         <v>159780</v>
@@ -848,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L12" t="n">
         <v>80280</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L13" t="n">
         <v>36240</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>14700</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1860</v>
@@ -1476,7 +1476,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>18060</v>
@@ -1514,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
         <v>29190</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L6" t="n">
         <v>33090</v>
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
         <v>41130</v>
@@ -1628,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
         <v>48480</v>
@@ -1666,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>44820</v>
@@ -1704,7 +1704,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
         <v>69960</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
         <v>93510</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
         <v>53220</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>25920</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>11310</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>3630</v>
@@ -2446,7 +2446,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9.66</v>
       </c>
       <c r="L5" t="n">
         <v>6129.9</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>14.95</v>
       </c>
       <c r="L6" t="n">
         <v>12243.3</v>
@@ -2522,7 +2522,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>18.86</v>
       </c>
       <c r="L7" t="n">
         <v>24678</v>
@@ -2560,7 +2560,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="L8" t="n">
         <v>34420.8</v>
@@ -2598,7 +2598,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>36304.2</v>
@@ -2636,7 +2636,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
         <v>62264.4</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L11" t="n">
         <v>93510</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
         <v>53220</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
         <v>25920</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>11310</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>3630</v>
@@ -3378,7 +3378,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>206086.44</v>
       </c>
       <c r="L5" t="n">
         <v>57743.66</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>318943.3</v>
       </c>
       <c r="L6" t="n">
         <v>115331.89</v>
@@ -3454,7 +3454,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>402359.24</v>
       </c>
       <c r="L7" t="n">
         <v>232466.76</v>
@@ -3492,7 +3492,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>480015</v>
       </c>
       <c r="L8" t="n">
         <v>324243.94</v>
@@ -3530,7 +3530,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L9" t="n">
         <v>341985.56</v>
@@ -3568,7 +3568,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>682688</v>
       </c>
       <c r="L10" t="n">
         <v>586530.65</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>938696</v>
       </c>
       <c r="L11" t="n">
         <v>880864.2</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L12" t="n">
         <v>501332.4</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L13" t="n">
         <v>244166.4</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L14" t="n">
         <v>106540.2</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L15" t="n">
         <v>34194.6</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L4" t="n">
         <v>120480</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>45240</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>9120</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1980</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.82</v>
       </c>
       <c r="L5" t="n">
         <v>9500.4</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>3374.4</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1188</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>188165.88</v>
       </c>
       <c r="L5" t="n">
         <v>89493.77</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>31786.85</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>11190.96</v>
@@ -7068,7 +7068,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L4" t="n">
         <v>94260</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>28800</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>7080</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2790</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1020</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>10.08</v>
       </c>
       <c r="L5" t="n">
         <v>6048</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>2619.6</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>1674</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
         <v>724.2</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>215046.72</v>
       </c>
       <c r="L5" t="n">
         <v>56972.16</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>110936.8</v>
       </c>
       <c r="L6" t="n">
         <v>24676.63</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>15769.08</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>19200.6</v>
       </c>
       <c r="L8" t="n">
         <v>6821.96</v>
@@ -9864,7 +9864,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="L4" t="n">
         <v>199290</v>
@@ -9902,7 +9902,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L5" t="n">
         <v>190800</v>
@@ -9940,7 +9940,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="L6" t="n">
         <v>211500</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="L7" t="n">
         <v>130650</v>
@@ -10016,7 +10016,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L8" t="n">
         <v>76740</v>
@@ -10054,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L9" t="n">
         <v>40500</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>9270</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>4290</v>
@@ -10834,7 +10834,7 @@
         <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>235.2</v>
       </c>
       <c r="L5" t="n">
         <v>174743.1</v>
@@ -10872,7 +10872,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>341.9</v>
       </c>
       <c r="L6" t="n">
         <v>236041.5</v>
@@ -10910,7 +10910,7 @@
         <v>9.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>314.06</v>
       </c>
       <c r="L7" t="n">
         <v>296388</v>
@@ -10948,7 +10948,7 @@
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L8" t="n">
         <v>274173.6</v>
@@ -10986,7 +10986,7 @@
         <v>7.6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="L9" t="n">
         <v>220133.7</v>
@@ -11024,7 +11024,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="L10" t="n">
         <v>160333.5</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L11" t="n">
         <v>159780</v>
@@ -11100,7 +11100,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L12" t="n">
         <v>80280</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L13" t="n">
         <v>36240</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>14700</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1860</v>
@@ -11766,7 +11766,7 @@
         <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.98</v>
       </c>
       <c r="L5" t="n">
         <v>40068</v>
@@ -11804,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>148.2</v>
       </c>
       <c r="L6" t="n">
         <v>78255</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>100.04</v>
       </c>
       <c r="L7" t="n">
         <v>78390</v>
@@ -11880,7 +11880,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="L8" t="n">
         <v>54485.4</v>
@@ -11918,7 +11918,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L9" t="n">
         <v>32805</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>8250.299999999999</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>4290</v>
@@ -12698,7 +12698,7 @@
         <v>157499.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1514287.32</v>
       </c>
       <c r="L5" t="n">
         <v>377440.56</v>
@@ -12736,7 +12736,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3161698.8</v>
       </c>
       <c r="L6" t="n">
         <v>737162.1</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2134253.36</v>
       </c>
       <c r="L7" t="n">
         <v>738433.8</v>
@@ -12812,7 +12812,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1689652.8</v>
       </c>
       <c r="L8" t="n">
         <v>513252.47</v>
@@ -12850,7 +12850,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>960030</v>
       </c>
       <c r="L9" t="n">
         <v>309023.1</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L10" t="n">
         <v>77717.83</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L11" t="n">
         <v>40411.8</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L4" t="n">
         <v>274380</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
         <v>80880</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="L5" t="n">
         <v>16984.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>179205.6</v>
       </c>
       <c r="L5" t="n">
         <v>159996.82</v>
@@ -16426,7 +16426,7 @@
         <v>419997.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5017756.8</v>
       </c>
       <c r="L5" t="n">
         <v>1646080</v>
@@ -16464,7 +16464,7 @@
         <v>291665</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7294094.6</v>
       </c>
       <c r="L6" t="n">
         <v>2223510.93</v>
@@ -16502,7 +16502,7 @@
         <v>530830.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6700156.04</v>
       </c>
       <c r="L7" t="n">
         <v>2791974.96</v>
@@ -16540,7 +16540,7 @@
         <v>347081.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6144192</v>
       </c>
       <c r="L8" t="n">
         <v>2582715.31</v>
@@ -16578,7 +16578,7 @@
         <v>443330.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5568174</v>
       </c>
       <c r="L9" t="n">
         <v>2073659.45</v>
@@ -16616,7 +16616,7 @@
         <v>174999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3285436</v>
       </c>
       <c r="L10" t="n">
         <v>1510341.57</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2474744</v>
       </c>
       <c r="L11" t="n">
         <v>1505127.6</v>
@@ -16692,7 +16692,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1045366</v>
       </c>
       <c r="L12" t="n">
         <v>756237.6</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L13" t="n">
         <v>341380.8</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L14" t="n">
         <v>138474</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L15" t="n">
         <v>45498.6</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>17521.2</v>
@@ -17320,7 +17320,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="L4" t="n">
         <v>157620</v>
@@ -17358,7 +17358,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="L5" t="n">
         <v>194280</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L6" t="n">
         <v>206370</v>
@@ -17434,7 +17434,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
         <v>251190</v>
@@ -17472,7 +17472,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="L8" t="n">
         <v>234330</v>
@@ -17510,7 +17510,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L9" t="n">
         <v>178050</v>
@@ -17548,7 +17548,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L10" t="n">
         <v>98070</v>
@@ -17586,7 +17586,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L11" t="n">
         <v>60960</v>
@@ -17624,7 +17624,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>23400</v>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
         <v>8940</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>2370</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>120</v>
@@ -18290,7 +18290,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>65.94</v>
       </c>
       <c r="L5" t="n">
         <v>40798.8</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>109.85</v>
       </c>
       <c r="L6" t="n">
         <v>76356.89999999999</v>
@@ -18366,7 +18366,7 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>170.56</v>
       </c>
       <c r="L7" t="n">
         <v>150714</v>
@@ -18404,7 +18404,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>182.7</v>
       </c>
       <c r="L8" t="n">
         <v>166374.3</v>
@@ -18442,7 +18442,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L9" t="n">
         <v>144220.5</v>
@@ -18480,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L10" t="n">
         <v>87282.3</v>
@@ -18518,7 +18518,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L11" t="n">
         <v>60960</v>
@@ -18556,7 +18556,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L12" t="n">
         <v>23400</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
         <v>8940</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>2370</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>120</v>
@@ -19222,7 +19222,7 @@
         <v>87499.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1406763.96</v>
       </c>
       <c r="L5" t="n">
         <v>384324.7</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2343539.9</v>
       </c>
       <c r="L6" t="n">
         <v>719282</v>
@@ -19298,7 +19298,7 @@
         <v>367497.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3638727.04</v>
       </c>
       <c r="L7" t="n">
         <v>1419725.88</v>
@@ -19336,7 +19336,7 @@
         <v>148749.15</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3897721.8</v>
       </c>
       <c r="L8" t="n">
         <v>1567245.91</v>
@@ -19374,7 +19374,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4074794</v>
       </c>
       <c r="L9" t="n">
         <v>1358557.11</v>
@@ -19412,7 +19412,7 @@
         <v>58333</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2496078</v>
       </c>
       <c r="L10" t="n">
         <v>822199.27</v>
@@ -19450,7 +19450,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1472046</v>
       </c>
       <c r="L11" t="n">
         <v>574243.2</v>
@@ -19488,7 +19488,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L12" t="n">
         <v>220428</v>
@@ -19526,7 +19526,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L13" t="n">
         <v>84214.8</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L14" t="n">
         <v>22325.4</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>1130.4</v>
@@ -20116,7 +20116,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
         <v>404670</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L5" t="n">
         <v>200700</v>
@@ -20192,7 +20192,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L6" t="n">
         <v>106110</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>38730</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>6480</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>60.48</v>
       </c>
       <c r="L5" t="n">
         <v>42147</v>
@@ -21124,7 +21124,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>61.75</v>
       </c>
       <c r="L6" t="n">
         <v>39260.7</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="L7" t="n">
         <v>23238</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>4600.8</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1290280.32</v>
       </c>
       <c r="L5" t="n">
         <v>397024.74</v>
@@ -22056,7 +22056,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1317374.5</v>
       </c>
       <c r="L6" t="n">
         <v>369835.79</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>437347</v>
       </c>
       <c r="L7" t="n">
         <v>218901.96</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>43339.54</v>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>159492.87</v>
+        <v>159339.24</v>
       </c>
       <c r="C4" t="n">
         <v>33290712</v>
@@ -529,10 +534,10 @@
         <v>7975800</v>
       </c>
       <c r="F4" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G4" t="n">
-        <v>499770</v>
+        <v>497340</v>
       </c>
       <c r="H4" t="n">
         <v>69060</v>
@@ -544,10 +549,13 @@
         <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="L4" t="n">
-        <v>1331070</v>
+        <v>1328160</v>
+      </c>
+      <c r="M4" t="n">
+        <v>66180</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>108949.5</v>
+        <v>108791.1</v>
       </c>
       <c r="C5" t="n">
         <v>19102608</v>
@@ -570,7 +578,7 @@
         <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>331740</v>
+        <v>330270</v>
       </c>
       <c r="H5" t="n">
         <v>49080</v>
@@ -582,10 +590,13 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="L5" t="n">
-        <v>832110</v>
+        <v>830100</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50400</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>86572.17</v>
+        <v>86436.99000000001</v>
       </c>
       <c r="C6" t="n">
         <v>14168448</v>
@@ -608,7 +619,7 @@
         <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>248970</v>
+        <v>248220</v>
       </c>
       <c r="H6" t="n">
         <v>57150</v>
@@ -620,10 +631,13 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L6" t="n">
-        <v>637950</v>
+        <v>636210</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29670</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>70800.21000000001</v>
+        <v>70754.22</v>
       </c>
       <c r="C7" t="n">
         <v>8392608</v>
@@ -646,7 +660,7 @@
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>203040</v>
+        <v>202590</v>
       </c>
       <c r="H7" t="n">
         <v>26130</v>
@@ -661,7 +675,10 @@
         <v>383</v>
       </c>
       <c r="L7" t="n">
-        <v>493980</v>
+        <v>492990</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20550</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>62209.62</v>
+        <v>62209.26</v>
       </c>
       <c r="C8" t="n">
         <v>6862464</v>
@@ -684,7 +701,7 @@
         <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>164040</v>
+        <v>163590</v>
       </c>
       <c r="H8" t="n">
         <v>6270</v>
@@ -699,7 +716,10 @@
         <v>320</v>
       </c>
       <c r="L8" t="n">
-        <v>386160</v>
+        <v>385440</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12540</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +742,7 @@
         <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>125640</v>
+        <v>125310</v>
       </c>
       <c r="H9" t="n">
         <v>4290</v>
@@ -737,7 +757,10 @@
         <v>261</v>
       </c>
       <c r="L9" t="n">
-        <v>271770</v>
+        <v>271410</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9990</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>29836.17</v>
+        <v>29835.81</v>
       </c>
       <c r="C10" t="n">
         <v>2575944</v>
@@ -775,7 +798,10 @@
         <v>154</v>
       </c>
       <c r="L10" t="n">
-        <v>180150</v>
+        <v>180060</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6570</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>116</v>
       </c>
       <c r="L11" t="n">
-        <v>159780</v>
+        <v>159510</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3180</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>49</v>
       </c>
       <c r="L12" t="n">
-        <v>80280</v>
+        <v>80070</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2880</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>36240</v>
       </c>
+      <c r="M13" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>14700</v>
       </c>
+      <c r="M14" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>4830</v>
       </c>
+      <c r="M15" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>1860</v>
       </c>
+      <c r="M16" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>1320</v>
       </c>
+      <c r="M17" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>1560</v>
       </c>
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>630</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1479,7 +1556,10 @@
         <v>10</v>
       </c>
       <c r="L4" t="n">
-        <v>18060</v>
+        <v>18090</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6300</v>
       </c>
     </row>
     <row r="5">
@@ -1517,7 +1597,10 @@
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>29190</v>
+        <v>29160</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13440</v>
       </c>
     </row>
     <row r="6">
@@ -1525,7 +1608,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3491.19</v>
+        <v>3491.1</v>
       </c>
       <c r="C6" t="n">
         <v>589176</v>
@@ -1540,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>9780</v>
+        <v>9930</v>
       </c>
       <c r="H6" t="n">
         <v>3030</v>
@@ -1555,7 +1638,10 @@
         <v>23</v>
       </c>
       <c r="L6" t="n">
-        <v>33090</v>
+        <v>33270</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9510</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>17580</v>
+        <v>17610</v>
       </c>
       <c r="H7" t="n">
         <v>4260</v>
@@ -1593,7 +1679,10 @@
         <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>41130</v>
+        <v>41400</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6660</v>
       </c>
     </row>
     <row r="8">
@@ -1631,7 +1720,10 @@
         <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>48480</v>
+        <v>48540</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3630</v>
       </c>
     </row>
     <row r="9">
@@ -1654,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>15660</v>
+        <v>15690</v>
       </c>
       <c r="H9" t="n">
         <v>3570</v>
@@ -1670,6 +1762,9 @@
       </c>
       <c r="L9" t="n">
         <v>44820</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="10">
@@ -1692,7 +1787,7 @@
         <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>24000</v>
+        <v>24030</v>
       </c>
       <c r="H10" t="n">
         <v>5310</v>
@@ -1707,7 +1802,10 @@
         <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>69960</v>
+        <v>70290</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="11">
@@ -1747,6 +1845,9 @@
       <c r="L11" t="n">
         <v>93510</v>
       </c>
+      <c r="M11" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,7 +1884,10 @@
         <v>28</v>
       </c>
       <c r="L12" t="n">
-        <v>53220</v>
+        <v>53310</v>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -1806,7 +1910,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>11040</v>
+        <v>11070</v>
       </c>
       <c r="H13" t="n">
         <v>810</v>
@@ -1821,7 +1925,10 @@
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>25920</v>
+        <v>25980</v>
+      </c>
+      <c r="M13" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -1859,7 +1966,10 @@
         <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>11310</v>
+        <v>11340</v>
+      </c>
+      <c r="M14" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>3630</v>
       </c>
+      <c r="M15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>1440</v>
       </c>
+      <c r="M16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>810</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>780</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>510</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2598,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>9.66</v>
+        <v>7.61</v>
       </c>
       <c r="L5" t="n">
-        <v>6129.9</v>
+        <v>6123.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>268.8</v>
       </c>
     </row>
     <row r="6">
@@ -2457,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2792.95</v>
+        <v>2792.88</v>
       </c>
       <c r="C6" t="n">
         <v>530258.4</v>
@@ -2472,7 +2627,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>489</v>
+        <v>496.5</v>
       </c>
       <c r="H6" t="n">
         <v>1727.1</v>
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14.95</v>
+        <v>11.66</v>
       </c>
       <c r="L6" t="n">
-        <v>12243.3</v>
+        <v>12309.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>760.8</v>
       </c>
     </row>
     <row r="7">
@@ -2510,7 +2668,7 @@
         <v>5.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2637</v>
+        <v>2641.5</v>
       </c>
       <c r="H7" t="n">
         <v>3109.8</v>
@@ -2522,10 +2680,13 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>18.86</v>
+        <v>14.67</v>
       </c>
       <c r="L7" t="n">
-        <v>24678</v>
+        <v>24840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2331</v>
       </c>
     </row>
     <row r="8">
@@ -2554,16 +2715,19 @@
         <v>2499</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>22.5</v>
+        <v>18.4</v>
       </c>
       <c r="L8" t="n">
-        <v>34420.8</v>
+        <v>34463.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2178</v>
       </c>
     </row>
     <row r="9">
@@ -2586,7 +2750,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>13311</v>
+        <v>13336.5</v>
       </c>
       <c r="H9" t="n">
         <v>3570</v>
@@ -2598,10 +2762,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>18.47</v>
       </c>
       <c r="L9" t="n">
         <v>36304.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2700</v>
       </c>
     </row>
     <row r="10">
@@ -2624,22 +2791,25 @@
         <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>24000</v>
+        <v>24030</v>
       </c>
       <c r="H10" t="n">
         <v>5310</v>
       </c>
       <c r="I10" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>27.84</v>
       </c>
       <c r="L10" t="n">
-        <v>62264.4</v>
+        <v>62558.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1830</v>
       </c>
     </row>
     <row r="11">
@@ -2674,10 +2844,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>39.53</v>
       </c>
       <c r="L11" t="n">
         <v>93510</v>
+      </c>
+      <c r="M11" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="12">
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>25.96</v>
       </c>
       <c r="L12" t="n">
-        <v>53220</v>
+        <v>53310</v>
+      </c>
+      <c r="M12" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -2738,22 +2914,25 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>11040</v>
+        <v>11070</v>
       </c>
       <c r="H13" t="n">
         <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>10.44</v>
       </c>
       <c r="L13" t="n">
-        <v>25920</v>
+        <v>25980</v>
+      </c>
+      <c r="M13" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -2788,10 +2967,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="L14" t="n">
-        <v>11310</v>
+        <v>11340</v>
+      </c>
+      <c r="M14" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -2826,10 +3008,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="L15" t="n">
         <v>3630</v>
+      </c>
+      <c r="M15" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>1440</v>
       </c>
+      <c r="M16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>810</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>780</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>510</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3354,13 +3578,13 @@
         <v>1641043.8</v>
       </c>
       <c r="C5" t="n">
-        <v>16267482</v>
+        <v>12422440.8</v>
       </c>
       <c r="D5" t="n">
-        <v>14171820.46</v>
+        <v>26852753.66</v>
       </c>
       <c r="E5" t="n">
-        <v>6730537.77</v>
+        <v>12603319.2</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>224086.5</v>
+        <v>4617000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>206086.44</v>
+        <v>369656.83</v>
       </c>
       <c r="L5" t="n">
-        <v>57743.66</v>
+        <v>1102248</v>
+      </c>
+      <c r="M5" t="n">
+        <v>80640</v>
       </c>
     </row>
     <row r="6">
@@ -3389,25 +3616,25 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6144494.4</v>
+        <v>6144336</v>
       </c>
       <c r="C6" t="n">
-        <v>29164212</v>
+        <v>22270852.8</v>
       </c>
       <c r="D6" t="n">
-        <v>23782401.08</v>
+        <v>45062873.86</v>
       </c>
       <c r="E6" t="n">
-        <v>10984978.37</v>
+        <v>20570004</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>9046.5</v>
+        <v>26811</v>
       </c>
       <c r="H6" t="n">
-        <v>477802.21</v>
+        <v>9844470</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>318943.3</v>
+        <v>566211.52</v>
       </c>
       <c r="L6" t="n">
-        <v>115331.89</v>
+        <v>2215782</v>
+      </c>
+      <c r="M6" t="n">
+        <v>228240</v>
       </c>
     </row>
     <row r="7">
@@ -3430,34 +3660,37 @@
         <v>9645768</v>
       </c>
       <c r="C7" t="n">
-        <v>35786520</v>
+        <v>27327888</v>
       </c>
       <c r="D7" t="n">
-        <v>33050661</v>
+        <v>62624365.06</v>
       </c>
       <c r="E7" t="n">
-        <v>15730002.19</v>
+        <v>29455334.1</v>
       </c>
       <c r="F7" t="n">
         <v>225001.8</v>
       </c>
       <c r="G7" t="n">
-        <v>48784.5</v>
+        <v>142641</v>
       </c>
       <c r="H7" t="n">
-        <v>860326.17</v>
+        <v>17725860</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>402359.24</v>
+        <v>712510.74</v>
       </c>
       <c r="L7" t="n">
-        <v>232466.76</v>
+        <v>4471200</v>
+      </c>
+      <c r="M7" t="n">
+        <v>699300</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>10834362</v>
       </c>
       <c r="C8" t="n">
-        <v>43076880</v>
+        <v>32895072</v>
       </c>
       <c r="D8" t="n">
-        <v>45894649.49</v>
+        <v>86961143.81</v>
       </c>
       <c r="E8" t="n">
-        <v>18425623.15</v>
+        <v>34503039.45</v>
       </c>
       <c r="F8" t="n">
         <v>197918.25</v>
       </c>
       <c r="G8" t="n">
-        <v>268758.75</v>
+        <v>784485</v>
       </c>
       <c r="H8" t="n">
-        <v>691348.35</v>
+        <v>14244300</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>480015</v>
+        <v>893430.4</v>
       </c>
       <c r="L8" t="n">
-        <v>324243.94</v>
+        <v>6203412</v>
+      </c>
+      <c r="M8" t="n">
+        <v>653400</v>
       </c>
     </row>
     <row r="9">
@@ -3506,34 +3742,37 @@
         <v>9911880</v>
       </c>
       <c r="C9" t="n">
-        <v>34067880</v>
+        <v>26015472</v>
       </c>
       <c r="D9" t="n">
-        <v>39600498.85</v>
+        <v>75034992.38</v>
       </c>
       <c r="E9" t="n">
-        <v>11052846.86</v>
+        <v>20697091.65</v>
       </c>
       <c r="F9" t="n">
         <v>125001</v>
       </c>
       <c r="G9" t="n">
-        <v>246253.5</v>
+        <v>720171</v>
       </c>
       <c r="H9" t="n">
-        <v>987640.5</v>
+        <v>20349000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>490682</v>
+        <v>896780.76</v>
       </c>
       <c r="L9" t="n">
-        <v>341985.56</v>
+        <v>6534756</v>
+      </c>
+      <c r="M9" t="n">
+        <v>810000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,34 +3783,37 @@
         <v>10111662</v>
       </c>
       <c r="C10" t="n">
-        <v>35148960</v>
+        <v>26841024</v>
       </c>
       <c r="D10" t="n">
-        <v>44266148.31</v>
+        <v>83875461.12</v>
       </c>
       <c r="E10" t="n">
-        <v>11059927.2</v>
+        <v>20710350</v>
       </c>
       <c r="F10" t="n">
         <v>458337</v>
       </c>
       <c r="G10" t="n">
-        <v>444000</v>
+        <v>1297620</v>
       </c>
       <c r="H10" t="n">
-        <v>1469011.5</v>
+        <v>30267000</v>
       </c>
       <c r="I10" t="n">
-        <v>735993.6</v>
+        <v>337949.76</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>682688</v>
+        <v>1351799.04</v>
       </c>
       <c r="L10" t="n">
-        <v>586530.65</v>
+        <v>11260458</v>
+      </c>
+      <c r="M10" t="n">
+        <v>549000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,22 +3824,22 @@
         <v>14344506</v>
       </c>
       <c r="C11" t="n">
-        <v>32432400</v>
+        <v>24766560</v>
       </c>
       <c r="D11" t="n">
-        <v>42182971.72</v>
+        <v>79928259.84</v>
       </c>
       <c r="E11" t="n">
-        <v>10464515.11</v>
+        <v>19595406.6</v>
       </c>
       <c r="F11" t="n">
         <v>375003</v>
       </c>
       <c r="G11" t="n">
-        <v>623265</v>
+        <v>1819260</v>
       </c>
       <c r="H11" t="n">
-        <v>971041.5</v>
+        <v>20007000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -3606,10 +3848,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>938696</v>
+        <v>1919612.9</v>
       </c>
       <c r="L11" t="n">
-        <v>880864.2</v>
+        <v>16831800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>198000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>11679426</v>
       </c>
       <c r="C12" t="n">
-        <v>22370040</v>
+        <v>17082576</v>
       </c>
       <c r="D12" t="n">
-        <v>30018327.91</v>
+        <v>56878702.85</v>
       </c>
       <c r="E12" t="n">
-        <v>9828245.949999999</v>
+        <v>18403956</v>
       </c>
       <c r="F12" t="n">
         <v>208335</v>
       </c>
       <c r="G12" t="n">
-        <v>461760</v>
+        <v>1347840</v>
       </c>
       <c r="H12" t="n">
-        <v>248985</v>
+        <v>5130000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>597352</v>
+        <v>1260319.54</v>
       </c>
       <c r="L12" t="n">
-        <v>501332.4</v>
+        <v>9595800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,34 +3906,37 @@
         <v>5396886</v>
       </c>
       <c r="C13" t="n">
-        <v>13305600</v>
+        <v>10160640</v>
       </c>
       <c r="D13" t="n">
-        <v>18288135.68</v>
+        <v>34652344.32</v>
       </c>
       <c r="E13" t="n">
-        <v>4738490.67</v>
+        <v>8873096.4</v>
       </c>
       <c r="F13" t="n">
         <v>83334</v>
       </c>
       <c r="G13" t="n">
-        <v>204240</v>
+        <v>597780</v>
       </c>
       <c r="H13" t="n">
-        <v>224086.5</v>
+        <v>4617000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>234674</v>
+        <v>507143.14</v>
       </c>
       <c r="L13" t="n">
-        <v>244166.4</v>
+        <v>4676400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,22 +3947,22 @@
         <v>3108402</v>
       </c>
       <c r="C14" t="n">
-        <v>6320160</v>
+        <v>4826304</v>
       </c>
       <c r="D14" t="n">
-        <v>8892714.310000001</v>
+        <v>16849907.71</v>
       </c>
       <c r="E14" t="n">
-        <v>2359976.22</v>
+        <v>4419191.25</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>81030</v>
+        <v>236520</v>
       </c>
       <c r="H14" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3720,10 +3971,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>192006</v>
+        <v>424767.89</v>
       </c>
       <c r="L14" t="n">
-        <v>106540.2</v>
+        <v>2041200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,22 +3988,22 @@
         <v>1236510</v>
       </c>
       <c r="C15" t="n">
-        <v>1607760</v>
+        <v>1227744</v>
       </c>
       <c r="D15" t="n">
-        <v>2294764.58</v>
+        <v>4348118.02</v>
       </c>
       <c r="E15" t="n">
-        <v>494380.4</v>
+        <v>925755.75</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>21645</v>
+        <v>63180</v>
       </c>
       <c r="H15" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3758,10 +4012,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>42668</v>
+        <v>95752.42999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>34194.6</v>
+        <v>653400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="16">
@@ -3772,10 +4029,10 @@
         <v>778536</v>
       </c>
       <c r="C16" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D16" t="n">
-        <v>561773.52</v>
+        <v>1064448</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3784,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H16" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3799,7 +4056,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>13564.8</v>
+        <v>259200</v>
+      </c>
+      <c r="M16" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="17">
@@ -3810,10 +4070,10 @@
         <v>289674</v>
       </c>
       <c r="C17" t="n">
-        <v>277200</v>
+        <v>211680</v>
       </c>
       <c r="D17" t="n">
-        <v>401266.8</v>
+        <v>760320</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3822,10 +4082,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3837,7 +4097,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>7630.2</v>
+        <v>145800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="18">
@@ -3875,7 +4138,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>7347.6</v>
+        <v>140400</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3898,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H19" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3913,7 +4179,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4804.2</v>
+        <v>91800</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>38430</v>
+        <v>38490</v>
       </c>
       <c r="H4" t="n">
         <v>4170</v>
@@ -4275,7 +4568,10 @@
         <v>51</v>
       </c>
       <c r="L4" t="n">
-        <v>120480</v>
+        <v>120360</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>13800</v>
+        <v>13860</v>
       </c>
       <c r="H5" t="n">
         <v>480</v>
@@ -4313,7 +4609,10 @@
         <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>45240</v>
+        <v>45690</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4336,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1740</v>
+        <v>1770</v>
       </c>
       <c r="H6" t="n">
         <v>150</v>
@@ -4352,6 +4651,9 @@
       </c>
       <c r="L6" t="n">
         <v>9120</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1980</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>420</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.82</v>
+        <v>6.95</v>
       </c>
       <c r="L5" t="n">
-        <v>9500.4</v>
+        <v>9594.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5268,7 +5639,7 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="H6" t="n">
         <v>85.5</v>
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>3374.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5318,10 +5692,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
         <v>1188</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>298.2</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>3853396.8</v>
       </c>
       <c r="C5" t="n">
-        <v>16038792</v>
+        <v>12247804.8</v>
       </c>
       <c r="D5" t="n">
-        <v>13972591.5</v>
+        <v>26475254.78</v>
       </c>
       <c r="E5" t="n">
-        <v>2798294.23</v>
+        <v>5239966.95</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>47805.12</v>
+        <v>984960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>188165.88</v>
+        <v>337512.76</v>
       </c>
       <c r="L5" t="n">
-        <v>89493.77</v>
+        <v>1727082</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>562953.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4765068</v>
+        <v>3638779.2</v>
       </c>
       <c r="D6" t="n">
-        <v>3885747.31</v>
+        <v>7362710.78</v>
       </c>
       <c r="E6" t="n">
-        <v>1485213.91</v>
+        <v>2781148.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1609.5</v>
+        <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>31786.85</v>
+        <v>607392</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>74299.5</v>
       </c>
       <c r="C7" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D7" t="n">
-        <v>819226.3</v>
+        <v>1552269.31</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1165.5</v>
+        <v>3402</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6250,10 +6696,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>11190.96</v>
+        <v>213840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>42966</v>
       </c>
       <c r="C8" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D8" t="n">
-        <v>118132.95</v>
+        <v>223838.21</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2809.04</v>
+        <v>53676</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,19 +6754,19 @@
         <v>21978</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>63480</v>
+        <v>63540</v>
       </c>
       <c r="H4" t="n">
         <v>4470</v>
@@ -7071,7 +7580,10 @@
         <v>120</v>
       </c>
       <c r="L4" t="n">
-        <v>94260</v>
+        <v>94350</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7094,7 +7606,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>14910</v>
+        <v>14940</v>
       </c>
       <c r="H5" t="n">
         <v>3180</v>
@@ -7110,6 +7622,9 @@
       </c>
       <c r="L5" t="n">
         <v>28800</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>7080</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>2790</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>1020</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.08</v>
+        <v>7.94</v>
       </c>
       <c r="L5" t="n">
         <v>6048</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>2619.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>1674</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8152,10 +8745,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>724.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>4224854.7</v>
       </c>
       <c r="C5" t="n">
-        <v>16496172</v>
+        <v>12597076.8</v>
       </c>
       <c r="D5" t="n">
-        <v>14371049.43</v>
+        <v>27230252.54</v>
       </c>
       <c r="E5" t="n">
-        <v>1975266.52</v>
+        <v>3698800.2</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>316708.92</v>
+        <v>6525360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>215046.72</v>
+        <v>385728.86</v>
       </c>
       <c r="L5" t="n">
-        <v>56972.16</v>
+        <v>1088640</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>1030233.6</v>
       </c>
       <c r="C6" t="n">
-        <v>6536376</v>
+        <v>4991414.4</v>
       </c>
       <c r="D6" t="n">
-        <v>5330187.41</v>
+        <v>10099634.69</v>
       </c>
       <c r="E6" t="n">
-        <v>1176961.97</v>
+        <v>2203929</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4107</v>
+        <v>11988</v>
       </c>
       <c r="H6" t="n">
-        <v>151382.88</v>
+        <v>3119040</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>110936.8</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>24676.63</v>
+        <v>471528</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,22 +9684,22 @@
         <v>321462.9</v>
       </c>
       <c r="C7" t="n">
-        <v>3437280</v>
+        <v>2624832</v>
       </c>
       <c r="D7" t="n">
-        <v>3174501.91</v>
+        <v>6015043.58</v>
       </c>
       <c r="E7" t="n">
-        <v>458497.82</v>
+        <v>858563.55</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4162.5</v>
+        <v>12150</v>
       </c>
       <c r="H7" t="n">
-        <v>24234.54</v>
+        <v>499320</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>15769.08</v>
+        <v>301320</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,19 +9725,19 @@
         <v>118008</v>
       </c>
       <c r="C8" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D8" t="n">
-        <v>767864.15</v>
+        <v>1454948.35</v>
       </c>
       <c r="E8" t="n">
-        <v>122023.99</v>
+        <v>228496.95</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>360.75</v>
+        <v>1053</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -9084,10 +9749,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>19200.6</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>6821.96</v>
+        <v>130356</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>81450</v>
+        <v>81510</v>
       </c>
       <c r="H4" t="n">
-        <v>9090</v>
+        <v>9060</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -9867,7 +10592,10 @@
         <v>223</v>
       </c>
       <c r="L4" t="n">
-        <v>199290</v>
+        <v>199770</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17280</v>
       </c>
     </row>
     <row r="5">
@@ -9890,10 +10618,10 @@
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>88380</v>
+        <v>88410</v>
       </c>
       <c r="H5" t="n">
-        <v>7560</v>
+        <v>7590</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -9905,7 +10633,10 @@
         <v>169</v>
       </c>
       <c r="L5" t="n">
-        <v>190800</v>
+        <v>190710</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18630</v>
       </c>
     </row>
     <row r="6">
@@ -9928,7 +10659,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>84750</v>
+        <v>84780</v>
       </c>
       <c r="H6" t="n">
         <v>12150</v>
@@ -9943,7 +10674,10 @@
         <v>228</v>
       </c>
       <c r="L6" t="n">
-        <v>211500</v>
+        <v>211560</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10740</v>
       </c>
     </row>
     <row r="7">
@@ -9966,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>63390</v>
+        <v>63510</v>
       </c>
       <c r="H7" t="n">
         <v>3960</v>
@@ -9981,7 +10715,10 @@
         <v>122</v>
       </c>
       <c r="L7" t="n">
-        <v>130650</v>
+        <v>130770</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6480</v>
       </c>
     </row>
     <row r="8">
@@ -10004,7 +10741,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>38370</v>
+        <v>38400</v>
       </c>
       <c r="H8" t="n">
         <v>450</v>
@@ -10019,7 +10756,10 @@
         <v>88</v>
       </c>
       <c r="L8" t="n">
-        <v>76740</v>
+        <v>76770</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3570</v>
       </c>
     </row>
     <row r="9">
@@ -10054,10 +10794,13 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L9" t="n">
         <v>40500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="10">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>9270</v>
       </c>
+      <c r="M10" t="n">
+        <v>930</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>4290</v>
       </c>
+      <c r="M11" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>3450</v>
       </c>
+      <c r="M12" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>1230</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>480</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>360</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>300</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>660</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>120</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>49027.28</v>
+        <v>48956</v>
       </c>
       <c r="C5" t="n">
         <v>10506434.4</v>
@@ -10828,16 +11628,19 @@
         <v>17668.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>235.2</v>
+        <v>182.05</v>
       </c>
       <c r="L5" t="n">
-        <v>174743.1</v>
+        <v>174321</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1008</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>69257.74000000001</v>
+        <v>69149.59</v>
       </c>
       <c r="C6" t="n">
         <v>12751603.2</v>
@@ -10860,22 +11663,25 @@
         <v>5.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12448.5</v>
+        <v>12411</v>
       </c>
       <c r="H6" t="n">
         <v>32575.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>341.9</v>
+        <v>266.18</v>
       </c>
       <c r="L6" t="n">
-        <v>236041.5</v>
+        <v>235397.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2373.6</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>67260.2</v>
+        <v>67216.50999999999</v>
       </c>
       <c r="C7" t="n">
         <v>8392608</v>
@@ -10898,22 +11704,25 @@
         <v>16.8</v>
       </c>
       <c r="G7" t="n">
-        <v>30456</v>
+        <v>30388.5</v>
       </c>
       <c r="H7" t="n">
         <v>19074.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
         <v>9.1</v>
       </c>
       <c r="K7" t="n">
-        <v>314.06</v>
+        <v>244.35</v>
       </c>
       <c r="L7" t="n">
-        <v>296388</v>
+        <v>295794</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7192.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>62209.62</v>
+        <v>62209.26</v>
       </c>
       <c r="C8" t="n">
         <v>6862464</v>
@@ -10936,22 +11745,25 @@
         <v>13.3</v>
       </c>
       <c r="G8" t="n">
-        <v>106626</v>
+        <v>106333.5</v>
       </c>
       <c r="H8" t="n">
         <v>5329.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>288</v>
+        <v>235.52</v>
       </c>
       <c r="L8" t="n">
-        <v>274173.6</v>
+        <v>273662.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7524</v>
       </c>
     </row>
     <row r="9">
@@ -10974,7 +11786,7 @@
         <v>19</v>
       </c>
       <c r="G9" t="n">
-        <v>106794</v>
+        <v>106513.5</v>
       </c>
       <c r="H9" t="n">
         <v>4290</v>
@@ -10986,10 +11798,13 @@
         <v>7.6</v>
       </c>
       <c r="K9" t="n">
-        <v>261</v>
+        <v>209.58</v>
       </c>
       <c r="L9" t="n">
-        <v>220133.7</v>
+        <v>219842.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9990</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>29836.17</v>
+        <v>29835.81</v>
       </c>
       <c r="C10" t="n">
         <v>2575944</v>
@@ -11018,16 +11833,19 @@
         <v>5340</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>154</v>
+        <v>133.98</v>
       </c>
       <c r="L10" t="n">
-        <v>160333.5</v>
+        <v>160253.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6570</v>
       </c>
     </row>
     <row r="11">
@@ -11062,10 +11880,13 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>116</v>
+        <v>104.23</v>
       </c>
       <c r="L11" t="n">
-        <v>159780</v>
+        <v>159510</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3180</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>49</v>
+        <v>45.42</v>
       </c>
       <c r="L12" t="n">
-        <v>80280</v>
+        <v>80070</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2880</v>
       </c>
     </row>
     <row r="13">
@@ -11132,16 +11956,19 @@
         <v>810</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>19.94</v>
       </c>
       <c r="L13" t="n">
         <v>36240</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="14">
@@ -11176,10 +12003,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L14" t="n">
         <v>14700</v>
+      </c>
+      <c r="M14" t="n">
+        <v>330</v>
       </c>
     </row>
     <row r="15">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
+      </c>
+      <c r="M15" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>1860</v>
       </c>
+      <c r="M16" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>1320</v>
       </c>
+      <c r="M17" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>1560</v>
       </c>
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>630</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11757,19 +12629,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2721.6</v>
+        <v>2732.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="J5" t="n">
         <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>70.98</v>
+        <v>55.94</v>
       </c>
       <c r="L5" t="n">
-        <v>40068</v>
+        <v>40049.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>372.6</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4237.5</v>
+        <v>4239</v>
       </c>
       <c r="H6" t="n">
         <v>6925.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>148.2</v>
+        <v>115.6</v>
       </c>
       <c r="L6" t="n">
-        <v>78255</v>
+        <v>78277.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>859.2</v>
       </c>
     </row>
     <row r="7">
@@ -11830,22 +12708,25 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9508.5</v>
+        <v>9526.5</v>
       </c>
       <c r="H7" t="n">
         <v>2890.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>100.04</v>
+        <v>77.84</v>
       </c>
       <c r="L7" t="n">
-        <v>78390</v>
+        <v>78462</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2268</v>
       </c>
     </row>
     <row r="8">
@@ -11868,7 +12749,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>24940.5</v>
+        <v>24960</v>
       </c>
       <c r="H8" t="n">
         <v>382.5</v>
@@ -11880,10 +12761,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>79.2</v>
+        <v>64.77</v>
       </c>
       <c r="L8" t="n">
-        <v>54485.4</v>
+        <v>54506.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2142</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>45</v>
+        <v>36.94</v>
       </c>
       <c r="L9" t="n">
         <v>32805</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="10">
@@ -11950,16 +12837,19 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>8250.299999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>930</v>
       </c>
     </row>
     <row r="11">
@@ -11994,10 +12884,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>4290</v>
+      </c>
+      <c r="M11" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>3450</v>
       </c>
+      <c r="M12" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>1230</v>
       </c>
+      <c r="M13" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>480</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>360</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>300</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>660</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>120</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>30011998.5</v>
       </c>
       <c r="C5" t="n">
-        <v>140705334</v>
+        <v>107447709.6</v>
       </c>
       <c r="D5" t="n">
-        <v>122578941.94</v>
+        <v>232262477.57</v>
       </c>
       <c r="E5" t="n">
-        <v>22038853.28</v>
+        <v>41269020.75</v>
       </c>
       <c r="F5" t="n">
         <v>16666.8</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>752930.64</v>
+        <v>15574680</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>157499.1</v>
+        <v>65550.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1514287.32</v>
+        <v>2716174.08</v>
       </c>
       <c r="L5" t="n">
-        <v>377440.56</v>
+        <v>7208838</v>
+      </c>
+      <c r="M5" t="n">
+        <v>111780</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>61778059.2</v>
       </c>
       <c r="C6" t="n">
-        <v>240149448</v>
+        <v>183386851.2</v>
       </c>
       <c r="D6" t="n">
-        <v>195833526.79</v>
+        <v>371065204.22</v>
       </c>
       <c r="E6" t="n">
-        <v>26930010.74</v>
+        <v>50427994.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>78393.75</v>
+        <v>228906</v>
       </c>
       <c r="H6" t="n">
-        <v>1915939.57</v>
+        <v>39475350</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>3161698.8</v>
+        <v>5612879.38</v>
       </c>
       <c r="L6" t="n">
-        <v>737162.1</v>
+        <v>14089896</v>
+      </c>
+      <c r="M6" t="n">
+        <v>257760</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>58075122.6</v>
       </c>
       <c r="C7" t="n">
-        <v>125627040</v>
+        <v>95933376</v>
       </c>
       <c r="D7" t="n">
-        <v>116022924.58</v>
+        <v>219840141.31</v>
       </c>
       <c r="E7" t="n">
-        <v>9910606.76</v>
+        <v>18558181.35</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>175907.25</v>
+        <v>514431</v>
       </c>
       <c r="H7" t="n">
-        <v>799739.8199999999</v>
+        <v>16477560</v>
       </c>
       <c r="I7" t="n">
-        <v>632494.5</v>
+        <v>371744.74</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2134253.36</v>
+        <v>3779404.82</v>
       </c>
       <c r="L7" t="n">
-        <v>738433.8</v>
+        <v>14123160</v>
+      </c>
+      <c r="M7" t="n">
+        <v>680400</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>51200424</v>
       </c>
       <c r="C8" t="n">
-        <v>91198800</v>
+        <v>69642720</v>
       </c>
       <c r="D8" t="n">
-        <v>97164348.02</v>
+        <v>184106926.08</v>
       </c>
       <c r="E8" t="n">
-        <v>5857151.73</v>
+        <v>10967853.6</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>461399.25</v>
+        <v>1347840</v>
       </c>
       <c r="H8" t="n">
-        <v>105818.62</v>
+        <v>2180250</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1689652.8</v>
+        <v>3144875.01</v>
       </c>
       <c r="L8" t="n">
-        <v>513252.47</v>
+        <v>9811206</v>
+      </c>
+      <c r="M8" t="n">
+        <v>642600</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>28124910</v>
       </c>
       <c r="C9" t="n">
-        <v>47068560</v>
+        <v>35943264</v>
       </c>
       <c r="D9" t="n">
-        <v>54712487.42</v>
+        <v>103669175.81</v>
       </c>
       <c r="E9" t="n">
-        <v>2263836.1</v>
+        <v>4239163.35</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>292956.75</v>
+        <v>855117</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12847,13 +13803,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>55416.35</v>
+        <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>960030</v>
+        <v>1793561.53</v>
       </c>
       <c r="L9" t="n">
-        <v>309023.1</v>
+        <v>5904900</v>
+      </c>
+      <c r="M9" t="n">
+        <v>630000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,34 +13823,37 @@
         <v>3026628</v>
       </c>
       <c r="C10" t="n">
-        <v>6264720</v>
+        <v>4783968</v>
       </c>
       <c r="D10" t="n">
-        <v>7889707.82</v>
+        <v>14949411.84</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>450225</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>46620</v>
+        <v>136080</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>367996.8</v>
+        <v>168974.88</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>106670</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>77717.83</v>
+        <v>1485054</v>
+      </c>
+      <c r="M10" t="n">
+        <v>279000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,22 +13864,22 @@
         <v>590040</v>
       </c>
       <c r="C11" t="n">
-        <v>1441440</v>
+        <v>1100736</v>
       </c>
       <c r="D11" t="n">
-        <v>1874798.74</v>
+        <v>3552367.1</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>16650</v>
+        <v>48600</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12926,10 +13888,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>42668</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>40411.8</v>
+        <v>772200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>429264</v>
       </c>
       <c r="C12" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D12" t="n">
-        <v>595158.92</v>
+        <v>1127706.62</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>32499</v>
+        <v>621000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>198000</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>11586.6</v>
+        <v>221400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>30096</v>
       </c>
       <c r="C14" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D14" t="n">
-        <v>195015.66</v>
+        <v>369515.52</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4521.6</v>
+        <v>86400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>37818</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3391.2</v>
+        <v>64800</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>21780</v>
       </c>
       <c r="C16" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D16" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>11088</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13157,7 +14137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>3168</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13180,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13195,7 +14178,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>6217.2</v>
+        <v>118800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -13206,10 +14192,10 @@
         <v>198</v>
       </c>
       <c r="C19" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D19" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13218,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>68265</v>
+        <v>199260</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13233,7 +14219,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D20" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>84540</v>
+        <v>84570</v>
       </c>
       <c r="H4" t="n">
         <v>9930</v>
@@ -13595,7 +14608,10 @@
         <v>99</v>
       </c>
       <c r="L4" t="n">
-        <v>274380</v>
+        <v>276810</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>18990</v>
+        <v>19050</v>
       </c>
       <c r="H5" t="n">
         <v>1860</v>
@@ -13633,7 +14649,10 @@
         <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>80880</v>
+        <v>81420</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1920</v>
+        <v>2010</v>
       </c>
       <c r="H6" t="n">
         <v>270</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12210</v>
+        <v>12450</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>1200</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>210</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>60</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>60</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8.4</v>
+        <v>6.62</v>
       </c>
       <c r="L5" t="n">
-        <v>16984.8</v>
+        <v>17098.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>96</v>
+        <v>100.5</v>
       </c>
       <c r="H6" t="n">
         <v>153.9</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4517.7</v>
+        <v>4606.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>720</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>149.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>48.6</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>60</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>7887132</v>
       </c>
       <c r="C5" t="n">
-        <v>16541910</v>
+        <v>12632004</v>
       </c>
       <c r="D5" t="n">
-        <v>14410895.22</v>
+        <v>27305752.32</v>
       </c>
       <c r="E5" t="n">
-        <v>4316323.13</v>
+        <v>8082563.4</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>185244.84</v>
+        <v>3816720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>179205.6</v>
+        <v>321440.72</v>
       </c>
       <c r="L5" t="n">
-        <v>159996.82</v>
+        <v>3077676</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>1237737.6</v>
       </c>
       <c r="C6" t="n">
-        <v>3143448</v>
+        <v>2400451.2</v>
       </c>
       <c r="D6" t="n">
-        <v>2563372.57</v>
+        <v>4857076.22</v>
       </c>
       <c r="E6" t="n">
-        <v>616503.89</v>
+        <v>1154439</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1776</v>
+        <v>5427</v>
       </c>
       <c r="H6" t="n">
-        <v>42576.43</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>42556.73</v>
+        <v>829170</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>220829.4</v>
       </c>
       <c r="C7" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D7" t="n">
-        <v>665621.37</v>
+        <v>1261218.82</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>166.5</v>
+        <v>486</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6782.4</v>
+        <v>129600</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1404.52</v>
+        <v>26838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>457.81</v>
+        <v>8748</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>107860005</v>
+        <v>107703189</v>
       </c>
       <c r="C5" t="n">
-        <v>577853892</v>
+        <v>441270244.8</v>
       </c>
       <c r="D5" t="n">
-        <v>503411751.79</v>
+        <v>953864169.98</v>
       </c>
       <c r="E5" t="n">
-        <v>99165695.03</v>
+        <v>185693469.3</v>
       </c>
       <c r="F5" t="n">
         <v>64167.18</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4888073.52</v>
+        <v>100712160</v>
       </c>
       <c r="I5" t="n">
-        <v>172498.5</v>
+        <v>192864.43</v>
       </c>
       <c r="J5" t="n">
-        <v>419997.6</v>
+        <v>174801.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5017756.8</v>
+        <v>8839619.800000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1646080</v>
+        <v>31377780</v>
+      </c>
+      <c r="M5" t="n">
+        <v>302400</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>152367019.2</v>
+        <v>152129102.4</v>
       </c>
       <c r="C6" t="n">
-        <v>701338176</v>
+        <v>535567334.4</v>
       </c>
       <c r="D6" t="n">
-        <v>571916902.6799999</v>
+        <v>1083667673.09</v>
       </c>
       <c r="E6" t="n">
-        <v>110606402.09</v>
+        <v>207116851.5</v>
       </c>
       <c r="F6" t="n">
         <v>229168.5</v>
       </c>
       <c r="G6" t="n">
-        <v>230297.25</v>
+        <v>670194</v>
       </c>
       <c r="H6" t="n">
-        <v>9012012.07</v>
+        <v>185680350</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>291665</v>
+        <v>121390</v>
       </c>
       <c r="K6" t="n">
-        <v>7294094.6</v>
+        <v>12924393.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2223510.93</v>
+        <v>42371586</v>
+      </c>
+      <c r="M6" t="n">
+        <v>712080</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>147972438.9</v>
+        <v>147876319.8</v>
       </c>
       <c r="C7" t="n">
-        <v>461593440</v>
+        <v>352489536</v>
       </c>
       <c r="D7" t="n">
-        <v>426304885.28</v>
+        <v>807762143.23</v>
       </c>
       <c r="E7" t="n">
-        <v>89689227.72</v>
+        <v>167948239.05</v>
       </c>
       <c r="F7" t="n">
         <v>700005.6</v>
       </c>
       <c r="G7" t="n">
-        <v>563436</v>
+        <v>1640979</v>
       </c>
       <c r="H7" t="n">
-        <v>5277071.08</v>
+        <v>108726930</v>
       </c>
       <c r="I7" t="n">
-        <v>843326</v>
+        <v>495659.65</v>
       </c>
       <c r="J7" t="n">
-        <v>530830.3</v>
+        <v>220929.8</v>
       </c>
       <c r="K7" t="n">
-        <v>6700156.04</v>
+        <v>11864852.82</v>
       </c>
       <c r="L7" t="n">
-        <v>2791974.96</v>
+        <v>53242920</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2157750</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>136861164</v>
+        <v>136860372</v>
       </c>
       <c r="C8" t="n">
-        <v>377435520</v>
+        <v>288223488</v>
       </c>
       <c r="D8" t="n">
-        <v>402124547.91</v>
+        <v>761945260.03</v>
       </c>
       <c r="E8" t="n">
-        <v>80535836.3</v>
+        <v>150807987</v>
       </c>
       <c r="F8" t="n">
         <v>554171.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1972581</v>
+        <v>5742009</v>
       </c>
       <c r="H8" t="n">
-        <v>1474406.17</v>
+        <v>30378150</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>347081.35</v>
+        <v>144454.1</v>
       </c>
       <c r="K8" t="n">
-        <v>6144192</v>
+        <v>11435909.12</v>
       </c>
       <c r="L8" t="n">
-        <v>2582715.31</v>
+        <v>49259232</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2257200</v>
       </c>
     </row>
     <row r="9">
@@ -16554,34 +17798,37 @@
         <v>108718830</v>
       </c>
       <c r="C9" t="n">
-        <v>278419680</v>
+        <v>212611392</v>
       </c>
       <c r="D9" t="n">
-        <v>323634996.26</v>
+        <v>613223322.62</v>
       </c>
       <c r="E9" t="n">
-        <v>56729069.41</v>
+        <v>106228446.3</v>
       </c>
       <c r="F9" t="n">
         <v>791673</v>
       </c>
       <c r="G9" t="n">
-        <v>1975689</v>
+        <v>5751729</v>
       </c>
       <c r="H9" t="n">
-        <v>1186828.5</v>
+        <v>24453000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>443330.8</v>
+        <v>184512.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5568174</v>
+        <v>10176512.15</v>
       </c>
       <c r="L9" t="n">
-        <v>2073659.45</v>
+        <v>39571578</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2997000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,37 +17836,40 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>65639574</v>
+        <v>65638782</v>
       </c>
       <c r="C10" t="n">
-        <v>141676920</v>
+        <v>108189648</v>
       </c>
       <c r="D10" t="n">
-        <v>178426091.49</v>
+        <v>338081610.24</v>
       </c>
       <c r="E10" t="n">
-        <v>36016893.36</v>
+        <v>67443705</v>
       </c>
       <c r="F10" t="n">
         <v>1375011</v>
       </c>
       <c r="G10" t="n">
-        <v>1495725</v>
+        <v>4365900</v>
       </c>
       <c r="H10" t="n">
-        <v>1477311</v>
+        <v>30438000</v>
       </c>
       <c r="I10" t="n">
-        <v>1103990.4</v>
+        <v>506924.64</v>
       </c>
       <c r="J10" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>3285436</v>
+        <v>6505532.88</v>
       </c>
       <c r="L10" t="n">
-        <v>1510341.57</v>
+        <v>28845612</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1971000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,34 +17880,37 @@
         <v>48651570</v>
       </c>
       <c r="C11" t="n">
-        <v>82217520</v>
+        <v>62784288</v>
       </c>
       <c r="D11" t="n">
-        <v>106935635.99</v>
+        <v>202621554.43</v>
       </c>
       <c r="E11" t="n">
-        <v>26229239.16</v>
+        <v>49115759.4</v>
       </c>
       <c r="F11" t="n">
         <v>458337</v>
       </c>
       <c r="G11" t="n">
-        <v>1070595</v>
+        <v>3124980</v>
       </c>
       <c r="H11" t="n">
-        <v>995940</v>
+        <v>20520000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>2474744</v>
+        <v>5060797.66</v>
       </c>
       <c r="L11" t="n">
-        <v>1505127.6</v>
+        <v>28711800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>954000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,34 +17921,37 @@
         <v>31560210</v>
       </c>
       <c r="C12" t="n">
-        <v>42217560</v>
+        <v>32238864</v>
       </c>
       <c r="D12" t="n">
-        <v>56651689.48</v>
+        <v>107343574.27</v>
       </c>
       <c r="E12" t="n">
-        <v>13949768.45</v>
+        <v>26121744</v>
       </c>
       <c r="F12" t="n">
         <v>333336</v>
       </c>
       <c r="G12" t="n">
-        <v>791985</v>
+        <v>2311740</v>
       </c>
       <c r="H12" t="n">
-        <v>248985</v>
+        <v>5130000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>1045366</v>
+        <v>2205559.19</v>
       </c>
       <c r="L12" t="n">
-        <v>756237.6</v>
+        <v>14412600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>864000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,34 +17962,37 @@
         <v>14918904</v>
       </c>
       <c r="C13" t="n">
-        <v>19514880</v>
+        <v>14902272</v>
       </c>
       <c r="D13" t="n">
-        <v>26822598.99</v>
+        <v>50823438.34</v>
       </c>
       <c r="E13" t="n">
-        <v>5528239.11</v>
+        <v>10351945.8</v>
       </c>
       <c r="F13" t="n">
         <v>166668</v>
       </c>
       <c r="G13" t="n">
-        <v>366855</v>
+        <v>1070820</v>
       </c>
       <c r="H13" t="n">
-        <v>224086.5</v>
+        <v>4617000</v>
       </c>
       <c r="I13" t="n">
-        <v>383330</v>
+        <v>184415.69</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>448014</v>
+        <v>968182.36</v>
       </c>
       <c r="L13" t="n">
-        <v>341380.8</v>
+        <v>6523200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>360000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>6842880</v>
       </c>
       <c r="C14" t="n">
-        <v>7733880</v>
+        <v>5905872</v>
       </c>
       <c r="D14" t="n">
-        <v>10881874.1</v>
+        <v>20618966.02</v>
       </c>
       <c r="E14" t="n">
-        <v>2643173.37</v>
+        <v>4949494.2</v>
       </c>
       <c r="F14" t="n">
         <v>83334</v>
       </c>
       <c r="G14" t="n">
-        <v>111555</v>
+        <v>325620</v>
       </c>
       <c r="H14" t="n">
-        <v>33198</v>
+        <v>684000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16768,10 +18027,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>213340</v>
+        <v>471964.32</v>
       </c>
       <c r="L14" t="n">
-        <v>138474</v>
+        <v>2646000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>99000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,22 +18044,22 @@
         <v>3154734</v>
       </c>
       <c r="C15" t="n">
-        <v>2134440</v>
+        <v>1629936</v>
       </c>
       <c r="D15" t="n">
-        <v>3046497.8</v>
+        <v>5772501.5</v>
       </c>
       <c r="E15" t="n">
-        <v>692132.5699999999</v>
+        <v>1296058.05</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>44400</v>
+        <v>129600</v>
       </c>
       <c r="H15" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>42668</v>
+        <v>95752.42999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>45498.6</v>
+        <v>869400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>1864566</v>
       </c>
       <c r="C16" t="n">
-        <v>637560</v>
+        <v>486864</v>
       </c>
       <c r="D16" t="n">
-        <v>922913.64</v>
+        <v>1748736</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,10 +18097,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9435</v>
+        <v>27540</v>
       </c>
       <c r="H16" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -16844,10 +18109,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>17521.2</v>
+        <v>334800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,10 +18126,10 @@
         <v>659736</v>
       </c>
       <c r="C17" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D17" t="n">
-        <v>561773.52</v>
+        <v>1064448</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16870,10 +18138,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H17" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16885,7 +18153,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>12434.4</v>
+        <v>237600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>449856</v>
       </c>
       <c r="C18" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D18" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16908,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16923,7 +18194,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14695.2</v>
+        <v>280800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>122760</v>
       </c>
       <c r="C19" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D19" t="n">
-        <v>321013.44</v>
+        <v>608256</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16946,10 +18220,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>69375</v>
+        <v>202500</v>
       </c>
       <c r="H19" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -16961,7 +18235,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>5934.6</v>
+        <v>113400</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16972,10 +18249,10 @@
         <v>26136</v>
       </c>
       <c r="C20" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D20" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16999,6 +18276,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D22" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D23" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>277200</v>
+        <v>211680</v>
       </c>
       <c r="D24" t="n">
-        <v>401266.8</v>
+        <v>760320</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>13314.78</v>
+        <v>13226.04</v>
       </c>
       <c r="C4" t="n">
         <v>3128832</v>
@@ -17308,7 +18609,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>54840</v>
+        <v>52500</v>
       </c>
       <c r="H4" t="n">
         <v>8910</v>
@@ -17320,10 +18621,13 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L4" t="n">
-        <v>157620</v>
+        <v>154800</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32640</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>21375.36</v>
+        <v>21316.23</v>
       </c>
       <c r="C5" t="n">
         <v>3530520</v>
@@ -17346,7 +18650,7 @@
         <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>69420</v>
+        <v>68550</v>
       </c>
       <c r="H5" t="n">
         <v>11640</v>
@@ -17358,10 +18662,13 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
-        <v>194280</v>
+        <v>192960</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12630</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>26358.12</v>
+        <v>26345.34</v>
       </c>
       <c r="C6" t="n">
         <v>4007808</v>
@@ -17384,10 +18691,10 @@
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>73230</v>
+        <v>72540</v>
       </c>
       <c r="H6" t="n">
-        <v>19080</v>
+        <v>19110</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L6" t="n">
-        <v>206370</v>
+        <v>205740</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6300</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>25907.58</v>
+        <v>25906.14</v>
       </c>
       <c r="C7" t="n">
         <v>3967488</v>
@@ -17422,7 +18732,7 @@
         <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>91680</v>
+        <v>91500</v>
       </c>
       <c r="H7" t="n">
         <v>15240</v>
@@ -17437,7 +18747,10 @@
         <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>251190</v>
+        <v>250230</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5370</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>28277.73</v>
+        <v>28277.55</v>
       </c>
       <c r="C8" t="n">
         <v>4052160</v>
@@ -17460,7 +18773,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>96180</v>
+        <v>95700</v>
       </c>
       <c r="H8" t="n">
         <v>2400</v>
@@ -17475,7 +18788,10 @@
         <v>203</v>
       </c>
       <c r="L8" t="n">
-        <v>234330</v>
+        <v>233670</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4080</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>87180</v>
+        <v>86880</v>
       </c>
       <c r="H9" t="n">
         <v>630</v>
@@ -17513,7 +18829,10 @@
         <v>191</v>
       </c>
       <c r="L9" t="n">
-        <v>178050</v>
+        <v>177810</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4890</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>117</v>
       </c>
       <c r="L10" t="n">
-        <v>98070</v>
+        <v>97980</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="11">
@@ -17574,7 +18896,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>22860</v>
+        <v>22890</v>
       </c>
       <c r="H11" t="n">
         <v>30</v>
@@ -17586,10 +18908,13 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>60960</v>
+        <v>60780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>21</v>
       </c>
       <c r="L12" t="n">
-        <v>23400</v>
+        <v>23190</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2280</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>8940</v>
       </c>
+      <c r="M13" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>2370</v>
       </c>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>840</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>120</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>210</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>120</v>
       </c>
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>9618.91</v>
+        <v>9592.299999999999</v>
       </c>
       <c r="C5" t="n">
         <v>1941786</v>
@@ -18290,10 +19666,13 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>65.94</v>
+        <v>48.66</v>
       </c>
       <c r="L5" t="n">
-        <v>40798.8</v>
+        <v>40521.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>252.6</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>21086.5</v>
+        <v>21076.27</v>
       </c>
       <c r="C6" t="n">
         <v>3607027.2</v>
@@ -18316,10 +19695,10 @@
         <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3661.5</v>
+        <v>3627</v>
       </c>
       <c r="H6" t="n">
-        <v>10875.6</v>
+        <v>10892.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>109.85</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>76356.89999999999</v>
+        <v>76123.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>504</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>24612.2</v>
+        <v>24610.83</v>
       </c>
       <c r="C7" t="n">
         <v>3967488</v>
@@ -18354,22 +19736,25 @@
         <v>8.4</v>
       </c>
       <c r="G7" t="n">
-        <v>13752</v>
+        <v>13725</v>
       </c>
       <c r="H7" t="n">
         <v>11125.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>170.56</v>
+        <v>132.7</v>
       </c>
       <c r="L7" t="n">
-        <v>150714</v>
+        <v>150138</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1879.5</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>28277.73</v>
+        <v>28277.55</v>
       </c>
       <c r="C8" t="n">
         <v>4052160</v>
@@ -18392,7 +19777,7 @@
         <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>62517</v>
+        <v>62205</v>
       </c>
       <c r="H8" t="n">
         <v>2040</v>
@@ -18404,10 +19789,13 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>182.7</v>
+        <v>149.41</v>
       </c>
       <c r="L8" t="n">
-        <v>166374.3</v>
+        <v>165905.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2448</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>74103</v>
+        <v>73848</v>
       </c>
       <c r="H9" t="n">
         <v>630</v>
@@ -18442,10 +19830,13 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>191</v>
+        <v>153.37</v>
       </c>
       <c r="L9" t="n">
-        <v>144220.5</v>
+        <v>144026.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4890</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>117</v>
+        <v>101.79</v>
       </c>
       <c r="L10" t="n">
-        <v>87282.3</v>
+        <v>87202.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3510</v>
       </c>
     </row>
     <row r="11">
@@ -18506,7 +19900,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>22860</v>
+        <v>22890</v>
       </c>
       <c r="H11" t="n">
         <v>30</v>
@@ -18518,10 +19912,13 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>69</v>
+        <v>62.9</v>
       </c>
       <c r="L11" t="n">
-        <v>60960</v>
+        <v>60780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2070</v>
       </c>
     </row>
     <row r="12">
@@ -18556,10 +19953,13 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>19.47</v>
       </c>
       <c r="L12" t="n">
-        <v>23400</v>
+        <v>23190</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2280</v>
       </c>
     </row>
     <row r="13">
@@ -18594,10 +19994,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="L13" t="n">
         <v>8940</v>
+      </c>
+      <c r="M13" t="n">
+        <v>870</v>
       </c>
     </row>
     <row r="14">
@@ -18632,10 +20035,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>2370</v>
+      </c>
+      <c r="M14" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>840</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>120</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>210</v>
       </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>120</v>
       </c>
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>21161606.4</v>
+        <v>21103067.7</v>
       </c>
       <c r="C5" t="n">
-        <v>106798230</v>
+        <v>81555012</v>
       </c>
       <c r="D5" t="n">
-        <v>93039927.22</v>
+        <v>176291976.96</v>
       </c>
       <c r="E5" t="n">
-        <v>39194408.79</v>
+        <v>73393785.45</v>
       </c>
       <c r="F5" t="n">
         <v>10833.42</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1159274.16</v>
+        <v>23885280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>1406763.96</v>
+        <v>2362589.29</v>
       </c>
       <c r="L5" t="n">
-        <v>384324.7</v>
+        <v>7293888</v>
+      </c>
+      <c r="M5" t="n">
+        <v>75780</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>46390291.2</v>
+        <v>46367798.4</v>
       </c>
       <c r="C6" t="n">
-        <v>198386496</v>
+        <v>151495142.4</v>
       </c>
       <c r="D6" t="n">
-        <v>161777291.2</v>
+        <v>306535477.25</v>
       </c>
       <c r="E6" t="n">
-        <v>53271540.5</v>
+        <v>99754024.5</v>
       </c>
       <c r="F6" t="n">
         <v>100000.8</v>
       </c>
       <c r="G6" t="n">
-        <v>67737.75</v>
+        <v>195858</v>
       </c>
       <c r="H6" t="n">
-        <v>3008734.74</v>
+        <v>62088390</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2343539.9</v>
+        <v>4135805.86</v>
       </c>
       <c r="L6" t="n">
-        <v>719282</v>
+        <v>13702284</v>
+      </c>
+      <c r="M6" t="n">
+        <v>151200</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>54146842.2</v>
+        <v>54143832.6</v>
       </c>
       <c r="C7" t="n">
-        <v>218211840</v>
+        <v>166634496</v>
       </c>
       <c r="D7" t="n">
-        <v>201529669.52</v>
+        <v>381858250.75</v>
       </c>
       <c r="E7" t="n">
-        <v>56183617.68</v>
+        <v>105207056.55</v>
       </c>
       <c r="F7" t="n">
         <v>350002.8</v>
       </c>
       <c r="G7" t="n">
-        <v>254412</v>
+        <v>741150</v>
       </c>
       <c r="H7" t="n">
-        <v>3077786.58</v>
+        <v>63413640</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>367497.9</v>
+        <v>152951.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3638727.04</v>
+        <v>6443575.42</v>
       </c>
       <c r="L7" t="n">
-        <v>1419725.88</v>
+        <v>27024840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>563850</v>
       </c>
     </row>
     <row r="8">
@@ -19309,37 +20766,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>62211006</v>
+        <v>62210610</v>
       </c>
       <c r="C8" t="n">
-        <v>222868800</v>
+        <v>170190720</v>
       </c>
       <c r="D8" t="n">
-        <v>237447221.3</v>
+        <v>449914798.08</v>
       </c>
       <c r="E8" t="n">
-        <v>54097304.18</v>
+        <v>101300314.5</v>
       </c>
       <c r="F8" t="n">
         <v>316669.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1156564.5</v>
+        <v>3359070</v>
       </c>
       <c r="H8" t="n">
-        <v>564366</v>
+        <v>11628000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>148749.15</v>
+        <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3897721.8</v>
+        <v>7254654.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1567245.91</v>
+        <v>29863026</v>
+      </c>
+      <c r="M8" t="n">
+        <v>734400</v>
       </c>
     </row>
     <row r="9">
@@ -19350,34 +20810,37 @@
         <v>63198630</v>
       </c>
       <c r="C9" t="n">
-        <v>191378880</v>
+        <v>146143872</v>
       </c>
       <c r="D9" t="n">
-        <v>222458782.77</v>
+        <v>421514717.18</v>
       </c>
       <c r="E9" t="n">
-        <v>42746552.3</v>
+        <v>80045378.55</v>
       </c>
       <c r="F9" t="n">
         <v>583338</v>
       </c>
       <c r="G9" t="n">
-        <v>1370905.5</v>
+        <v>3987792</v>
       </c>
       <c r="H9" t="n">
-        <v>174289.5</v>
+        <v>3591000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>221665.4</v>
+        <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>4074794</v>
+        <v>7447179.39</v>
       </c>
       <c r="L9" t="n">
-        <v>1358557.11</v>
+        <v>25924698</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1467000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,19 +20851,19 @@
         <v>47510496</v>
       </c>
       <c r="C10" t="n">
-        <v>98211960</v>
+        <v>74998224</v>
       </c>
       <c r="D10" t="n">
-        <v>123686879.7</v>
+        <v>234361797.12</v>
       </c>
       <c r="E10" t="n">
-        <v>24668446.32</v>
+        <v>46193085</v>
       </c>
       <c r="F10" t="n">
         <v>916674</v>
       </c>
       <c r="G10" t="n">
-        <v>990120</v>
+        <v>2890080</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19409,13 +20872,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>58333</v>
+        <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>2496078</v>
+        <v>4942515.24</v>
       </c>
       <c r="L10" t="n">
-        <v>822199.27</v>
+        <v>15696396</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1053000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,34 +20892,37 @@
         <v>31078674</v>
       </c>
       <c r="C11" t="n">
-        <v>47678400</v>
+        <v>36408960</v>
       </c>
       <c r="D11" t="n">
-        <v>62012573.81</v>
+        <v>117501373.44</v>
       </c>
       <c r="E11" t="n">
-        <v>15696772.66</v>
+        <v>29393109.9</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>422910</v>
+        <v>1236060</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>174999</v>
+        <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>1472046</v>
+        <v>3053929.62</v>
       </c>
       <c r="L11" t="n">
-        <v>574243.2</v>
+        <v>10940400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>621000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>17739216</v>
       </c>
       <c r="C12" t="n">
-        <v>19154520</v>
+        <v>14627088</v>
       </c>
       <c r="D12" t="n">
-        <v>25703425.76</v>
+        <v>48702829.82</v>
       </c>
       <c r="E12" t="n">
-        <v>3963002.4</v>
+        <v>7420950</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>325230</v>
+        <v>949320</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19485,13 +20954,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>448014</v>
+        <v>945239.65</v>
       </c>
       <c r="L12" t="n">
-        <v>220428</v>
+        <v>4174200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>684000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>8089884</v>
       </c>
       <c r="C13" t="n">
-        <v>5932080</v>
+        <v>4529952</v>
       </c>
       <c r="D13" t="n">
-        <v>8153460.49</v>
+        <v>15449170.18</v>
       </c>
       <c r="E13" t="n">
-        <v>789748.4399999999</v>
+        <v>1478849.4</v>
       </c>
       <c r="F13" t="n">
         <v>41667</v>
       </c>
       <c r="G13" t="n">
-        <v>155955</v>
+        <v>455220</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19526,10 +20998,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>213340</v>
+        <v>461039.22</v>
       </c>
       <c r="L13" t="n">
-        <v>84214.8</v>
+        <v>1609200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>261000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>2826648</v>
       </c>
       <c r="C14" t="n">
-        <v>1164240</v>
+        <v>889056</v>
       </c>
       <c r="D14" t="n">
-        <v>1638131.58</v>
+        <v>3103930.37</v>
       </c>
       <c r="E14" t="n">
-        <v>188798.1</v>
+        <v>353535.3</v>
       </c>
       <c r="F14" t="n">
         <v>83334</v>
       </c>
       <c r="G14" t="n">
-        <v>20535</v>
+        <v>59940</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19564,10 +21039,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>21334</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>22325.4</v>
+        <v>426600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,19 +21056,19 @@
         <v>920700</v>
       </c>
       <c r="C15" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D15" t="n">
-        <v>553908.6899999999</v>
+        <v>1049545.73</v>
       </c>
       <c r="E15" t="n">
-        <v>197752.16</v>
+        <v>370302.3</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>19980</v>
+        <v>58320</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19605,7 +21083,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7912.8</v>
+        <v>151200</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="16">
@@ -19616,10 +21097,10 @@
         <v>369072</v>
       </c>
       <c r="C16" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D16" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -19628,7 +21109,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -19640,10 +21121,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21334</v>
+        <v>48556</v>
       </c>
       <c r="L16" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -19654,10 +21138,10 @@
         <v>251460</v>
       </c>
       <c r="C17" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D17" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1978.2</v>
+        <v>37800</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="18">
@@ -19692,10 +21179,10 @@
         <v>222156</v>
       </c>
       <c r="C18" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D18" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -19704,7 +21191,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -19719,7 +21206,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M18" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="19">
@@ -19730,10 +21220,10 @@
         <v>80586</v>
       </c>
       <c r="C19" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D19" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19757,6 +21247,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19844,10 +21343,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19871,6 +21370,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19882,10 +21384,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -19909,6 +21411,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D24" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>141720</v>
+        <v>141810</v>
       </c>
       <c r="H4" t="n">
-        <v>25920</v>
+        <v>26010</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20116,10 +21633,13 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>404670</v>
+        <v>403140</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,7 +21662,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>83670</v>
+        <v>83850</v>
       </c>
       <c r="H5" t="n">
         <v>18990</v>
@@ -20157,7 +21677,10 @@
         <v>144</v>
       </c>
       <c r="L5" t="n">
-        <v>200700</v>
+        <v>200910</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>51180</v>
+        <v>51360</v>
       </c>
       <c r="H6" t="n">
-        <v>19380</v>
+        <v>19410</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>95</v>
       </c>
       <c r="L6" t="n">
-        <v>106110</v>
+        <v>106140</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20218,10 +21744,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>15750</v>
+        <v>15780</v>
       </c>
       <c r="H7" t="n">
-        <v>2490</v>
+        <v>2520</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -20233,7 +21759,10 @@
         <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>38730</v>
+        <v>38850</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20271,7 +21800,10 @@
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>6480</v>
+        <v>6450</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -20310,6 +21842,9 @@
       </c>
       <c r="L9" t="n">
         <v>1260</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>420</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21086,10 +22678,13 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>60.48</v>
+        <v>47.66</v>
       </c>
       <c r="L5" t="n">
-        <v>42147</v>
+        <v>42191.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2559</v>
+        <v>2568</v>
       </c>
       <c r="H6" t="n">
-        <v>11046.6</v>
+        <v>11063.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>61.75</v>
+        <v>48.16</v>
       </c>
       <c r="L6" t="n">
-        <v>39260.7</v>
+        <v>39271.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21150,10 +22748,10 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2362.5</v>
+        <v>2367</v>
       </c>
       <c r="H7" t="n">
-        <v>1817.7</v>
+        <v>1839.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20.5</v>
+        <v>15.95</v>
       </c>
       <c r="L7" t="n">
-        <v>23238</v>
+        <v>23310</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21200,10 +22801,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="L8" t="n">
-        <v>4600.8</v>
+        <v>4579.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>102</v>
+        <v>127.5</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -21242,6 +22846,9 @@
       </c>
       <c r="L9" t="n">
         <v>1020.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>373.8</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>90</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>30</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>29605346.1</v>
       </c>
       <c r="C5" t="n">
-        <v>90911898</v>
+        <v>69423631.2</v>
       </c>
       <c r="D5" t="n">
-        <v>79200155.03</v>
+        <v>150068388.1</v>
       </c>
       <c r="E5" t="n">
-        <v>6419616.18</v>
+        <v>12021100.65</v>
       </c>
       <c r="F5" t="n">
         <v>7500.06</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1891290.06</v>
+        <v>38967480</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1290280.32</v>
+        <v>2314373.18</v>
       </c>
       <c r="L5" t="n">
-        <v>397024.74</v>
+        <v>7594398</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>18720979.2</v>
       </c>
       <c r="C6" t="n">
-        <v>70777476</v>
+        <v>54048254.4</v>
       </c>
       <c r="D6" t="n">
-        <v>57716571.32</v>
+        <v>109361311.49</v>
       </c>
       <c r="E6" t="n">
-        <v>4091343.98</v>
+        <v>7661277</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>47341.5</v>
+        <v>138672</v>
       </c>
       <c r="H6" t="n">
-        <v>3056041.89</v>
+        <v>63063090</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>1317374.5</v>
+        <v>2338699.74</v>
       </c>
       <c r="L6" t="n">
-        <v>369835.79</v>
+        <v>7068924</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>9904029.300000001</v>
       </c>
       <c r="C7" t="n">
-        <v>25419240</v>
+        <v>19411056</v>
       </c>
       <c r="D7" t="n">
-        <v>23475953.63</v>
+        <v>44482217.47</v>
       </c>
       <c r="E7" t="n">
-        <v>1516569.72</v>
+        <v>2839864.05</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>43706.25</v>
+        <v>127818</v>
       </c>
       <c r="H7" t="n">
-        <v>502866.7</v>
+        <v>10485720</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>437347</v>
+        <v>774468.2</v>
       </c>
       <c r="L7" t="n">
-        <v>218901.96</v>
+        <v>4195800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,22 +23781,22 @@
         <v>581130</v>
       </c>
       <c r="C8" t="n">
-        <v>2605680</v>
+        <v>1989792</v>
       </c>
       <c r="D8" t="n">
-        <v>2776124.23</v>
+        <v>5260197.89</v>
       </c>
       <c r="E8" t="n">
-        <v>203373.32</v>
+        <v>380828.25</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7215</v>
+        <v>21060</v>
       </c>
       <c r="H8" t="n">
-        <v>112873.2</v>
+        <v>2325600</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22132,10 +23805,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>38401.2</v>
+        <v>71474.42999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>43339.54</v>
+        <v>824310</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>94446</v>
       </c>
       <c r="C9" t="n">
-        <v>360360</v>
+        <v>275184</v>
       </c>
       <c r="D9" t="n">
-        <v>418882.41</v>
+        <v>793698.05</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1887</v>
+        <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9614.049999999999</v>
+        <v>183708</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22184,10 +23863,10 @@
         <v>48114</v>
       </c>
       <c r="C10" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D10" t="n">
-        <v>69820.42</v>
+        <v>132295.68</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3521.2</v>
+        <v>67284</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22237,7 +23919,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22287,7 +23972,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>971</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
         <v>1328160</v>
@@ -590,7 +590,7 @@
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>550</v>
+        <v>225</v>
       </c>
       <c r="L5" t="n">
         <v>830100</v>
@@ -631,7 +631,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>525</v>
+        <v>170</v>
       </c>
       <c r="L6" t="n">
         <v>636210</v>
@@ -672,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>383</v>
+        <v>112</v>
       </c>
       <c r="L7" t="n">
         <v>492990</v>
@@ -713,7 +713,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>320</v>
+        <v>96</v>
       </c>
       <c r="L8" t="n">
         <v>385440</v>
@@ -754,7 +754,7 @@
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>261</v>
+        <v>63</v>
       </c>
       <c r="L9" t="n">
         <v>271410</v>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
         <v>180060</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>159510</v>
@@ -877,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>80070</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>36240</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>14700</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1860</v>
@@ -1553,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>18090</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>29160</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
         <v>33270</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
         <v>41400</v>
@@ -1717,7 +1717,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>48540</v>
@@ -1758,7 +1758,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>44820</v>
@@ -1799,7 +1799,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>70290</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>93510</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>53310</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>25980</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>11340</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3630</v>
@@ -2598,7 +2598,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>7.61</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>6123.6</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>11.66</v>
+        <v>5.58</v>
       </c>
       <c r="L6" t="n">
         <v>12309.9</v>
@@ -2680,7 +2680,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>14.67</v>
+        <v>9.57</v>
       </c>
       <c r="L7" t="n">
         <v>24840</v>
@@ -2721,7 +2721,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>18.4</v>
+        <v>4.42</v>
       </c>
       <c r="L8" t="n">
         <v>34463.4</v>
@@ -2762,7 +2762,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>18.47</v>
+        <v>3.21</v>
       </c>
       <c r="L9" t="n">
         <v>36304.2</v>
@@ -2803,7 +2803,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>27.84</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
         <v>62558.1</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>39.53</v>
+        <v>5.39</v>
       </c>
       <c r="L11" t="n">
         <v>93510</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>25.96</v>
+        <v>3.71</v>
       </c>
       <c r="L12" t="n">
         <v>53310</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10.44</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>25980</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>11340</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3630</v>
@@ -3602,7 +3602,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>369656.83</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
         <v>1102248</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>566211.52</v>
+        <v>270796.81</v>
       </c>
       <c r="L6" t="n">
         <v>2215782</v>
@@ -3684,7 +3684,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>712510.74</v>
+        <v>464680.92</v>
       </c>
       <c r="L7" t="n">
         <v>4471200</v>
@@ -3725,7 +3725,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>893430.4</v>
+        <v>214423.3</v>
       </c>
       <c r="L8" t="n">
         <v>6203412</v>
@@ -3766,7 +3766,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>896780.76</v>
+        <v>155961.87</v>
       </c>
       <c r="L9" t="n">
         <v>6534756</v>
@@ -3807,7 +3807,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>1351799.04</v>
+        <v>126731.16</v>
       </c>
       <c r="L10" t="n">
         <v>11260458</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1919612.9</v>
+        <v>261765.4</v>
       </c>
       <c r="L11" t="n">
         <v>16831800</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1260319.54</v>
+        <v>180045.65</v>
       </c>
       <c r="L12" t="n">
         <v>9595800</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>507143.14</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>4676400</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>424767.89</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2041200</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>95752.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>653400</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
         <v>120360</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>45690</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>9120</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.95</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>9594.9</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3374.4</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>337512.76</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1727082</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>607392</v>
@@ -7577,7 +7577,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
         <v>94350</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>28800</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7080</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2790</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1020</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.94</v>
+        <v>1.32</v>
       </c>
       <c r="L5" t="n">
         <v>6048</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2619.6</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1674</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>724.2</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>385728.86</v>
+        <v>64288.14</v>
       </c>
       <c r="L5" t="n">
         <v>1088640</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>196943.14</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>471528</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>301320</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>35737.22</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>130356</v>
@@ -10589,7 +10589,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>223</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
         <v>199770</v>
@@ -10630,7 +10630,7 @@
         <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="L5" t="n">
         <v>190710</v>
@@ -10671,7 +10671,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>228</v>
+        <v>83</v>
       </c>
       <c r="L6" t="n">
         <v>211560</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
         <v>130770</v>
@@ -10753,7 +10753,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="L8" t="n">
         <v>76770</v>
@@ -10794,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>40500</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>9270</v>
@@ -11634,7 +11634,7 @@
         <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>182.05</v>
+        <v>74.48</v>
       </c>
       <c r="L5" t="n">
         <v>174321</v>
@@ -11675,7 +11675,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>266.18</v>
+        <v>86.19</v>
       </c>
       <c r="L6" t="n">
         <v>235397.7</v>
@@ -11716,7 +11716,7 @@
         <v>9.1</v>
       </c>
       <c r="K7" t="n">
-        <v>244.35</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>295794</v>
@@ -11757,7 +11757,7 @@
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>235.52</v>
+        <v>70.66</v>
       </c>
       <c r="L8" t="n">
         <v>273662.4</v>
@@ -11798,7 +11798,7 @@
         <v>7.6</v>
       </c>
       <c r="K9" t="n">
-        <v>209.58</v>
+        <v>50.59</v>
       </c>
       <c r="L9" t="n">
         <v>219842.1</v>
@@ -11839,7 +11839,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>133.98</v>
+        <v>27.84</v>
       </c>
       <c r="L10" t="n">
         <v>160253.4</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>104.23</v>
+        <v>15.27</v>
       </c>
       <c r="L11" t="n">
         <v>159510</v>
@@ -11921,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>45.42</v>
+        <v>4.64</v>
       </c>
       <c r="L12" t="n">
         <v>80070</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>19.94</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>36240</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>14700</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1860</v>
@@ -12638,7 +12638,7 @@
         <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>55.94</v>
+        <v>27.8</v>
       </c>
       <c r="L5" t="n">
         <v>40049.1</v>
@@ -12679,7 +12679,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>115.6</v>
+        <v>42.08</v>
       </c>
       <c r="L6" t="n">
         <v>78277.2</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>77.84</v>
+        <v>25.52</v>
       </c>
       <c r="L7" t="n">
         <v>78462</v>
@@ -12761,7 +12761,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>64.77</v>
+        <v>24.29</v>
       </c>
       <c r="L8" t="n">
         <v>54506.7</v>
@@ -12802,7 +12802,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>36.94</v>
+        <v>5.62</v>
       </c>
       <c r="L9" t="n">
         <v>32805</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.35</v>
+        <v>1.74</v>
       </c>
       <c r="L10" t="n">
         <v>8250.299999999999</v>
@@ -13642,7 +13642,7 @@
         <v>65550.60000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2716174.08</v>
+        <v>1350051.02</v>
       </c>
       <c r="L5" t="n">
         <v>7208838</v>
@@ -13683,7 +13683,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>5612879.38</v>
+        <v>2043285.04</v>
       </c>
       <c r="L6" t="n">
         <v>14089896</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3779404.82</v>
+        <v>1239149.12</v>
       </c>
       <c r="L7" t="n">
         <v>14123160</v>
@@ -13765,7 +13765,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3144875.01</v>
+        <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
         <v>9811206</v>
@@ -13806,7 +13806,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1793561.53</v>
+        <v>272933.28</v>
       </c>
       <c r="L9" t="n">
         <v>5904900</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>211218.6</v>
+        <v>84487.44</v>
       </c>
       <c r="L10" t="n">
         <v>1485054</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>276810</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>81420</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.62</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>17098.2</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321440.72</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>3077676</v>
@@ -17658,7 +17658,7 @@
         <v>174801.6</v>
       </c>
       <c r="K5" t="n">
-        <v>8839619.800000001</v>
+        <v>3616208.1</v>
       </c>
       <c r="L5" t="n">
         <v>31377780</v>
@@ -17699,7 +17699,7 @@
         <v>121390</v>
       </c>
       <c r="K6" t="n">
-        <v>12924393.3</v>
+        <v>4185041.64</v>
       </c>
       <c r="L6" t="n">
         <v>42371586</v>
@@ -17740,7 +17740,7 @@
         <v>220929.8</v>
       </c>
       <c r="K7" t="n">
-        <v>11864852.82</v>
+        <v>3469617.54</v>
       </c>
       <c r="L7" t="n">
         <v>53242920</v>
@@ -17781,7 +17781,7 @@
         <v>144454.1</v>
       </c>
       <c r="K8" t="n">
-        <v>11435909.12</v>
+        <v>3430772.74</v>
       </c>
       <c r="L8" t="n">
         <v>49259232</v>
@@ -17822,7 +17822,7 @@
         <v>184512.8</v>
       </c>
       <c r="K9" t="n">
-        <v>10176512.15</v>
+        <v>2456399.48</v>
       </c>
       <c r="L9" t="n">
         <v>39571578</v>
@@ -17863,7 +17863,7 @@
         <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>6505532.88</v>
+        <v>1351799.04</v>
       </c>
       <c r="L10" t="n">
         <v>28845612</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>5060797.66</v>
+        <v>741668.62</v>
       </c>
       <c r="L11" t="n">
         <v>28711800</v>
@@ -17945,7 +17945,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>2205559.19</v>
+        <v>225057.06</v>
       </c>
       <c r="L12" t="n">
         <v>14412600</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>968182.36</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>6523200</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>471964.32</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2646000</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>95752.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>869400</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>334800</v>
@@ -18621,7 +18621,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>137</v>
+        <v>66</v>
       </c>
       <c r="L4" t="n">
         <v>154800</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="L5" t="n">
         <v>192960</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="L6" t="n">
         <v>205740</v>
@@ -18744,7 +18744,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>208</v>
+        <v>54</v>
       </c>
       <c r="L7" t="n">
         <v>250230</v>
@@ -18785,7 +18785,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="L8" t="n">
         <v>233670</v>
@@ -18826,7 +18826,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
         <v>177810</v>
@@ -18867,7 +18867,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
         <v>97980</v>
@@ -18908,7 +18908,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>60780</v>
@@ -18949,7 +18949,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>23190</v>
@@ -18990,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>8940</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2370</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>120</v>
@@ -19666,7 +19666,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>48.66</v>
+        <v>20.19</v>
       </c>
       <c r="L5" t="n">
         <v>40521.6</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>85.18000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="L6" t="n">
         <v>76123.8</v>
@@ -19748,7 +19748,7 @@
         <v>6.3</v>
       </c>
       <c r="K7" t="n">
-        <v>132.7</v>
+        <v>34.45</v>
       </c>
       <c r="L7" t="n">
         <v>150138</v>
@@ -19789,7 +19789,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>149.41</v>
+        <v>41.95</v>
       </c>
       <c r="L8" t="n">
         <v>165905.7</v>
@@ -19830,7 +19830,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>153.37</v>
+        <v>40.95</v>
       </c>
       <c r="L9" t="n">
         <v>144026.1</v>
@@ -19871,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>101.79</v>
+        <v>23.49</v>
       </c>
       <c r="L10" t="n">
         <v>87202.2</v>
@@ -19912,7 +19912,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>62.9</v>
+        <v>8.09</v>
       </c>
       <c r="L11" t="n">
         <v>60780</v>
@@ -19953,7 +19953,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>19.47</v>
+        <v>0.93</v>
       </c>
       <c r="L12" t="n">
         <v>23190</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>8940</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>2370</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>120</v>
@@ -20670,7 +20670,7 @@
         <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>2362589.29</v>
+        <v>980394.2</v>
       </c>
       <c r="L5" t="n">
         <v>7293888</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>4135805.86</v>
+        <v>1403219.84</v>
       </c>
       <c r="L6" t="n">
         <v>13702284</v>
@@ -20752,7 +20752,7 @@
         <v>152951.4</v>
       </c>
       <c r="K7" t="n">
-        <v>6443575.42</v>
+        <v>1672851.31</v>
       </c>
       <c r="L7" t="n">
         <v>27024840</v>
@@ -20793,7 +20793,7 @@
         <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7254654.85</v>
+        <v>2037021.31</v>
       </c>
       <c r="L8" t="n">
         <v>29863026</v>
@@ -20834,7 +20834,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>7447179.39</v>
+        <v>1988513.87</v>
       </c>
       <c r="L9" t="n">
         <v>25924698</v>
@@ -20875,7 +20875,7 @@
         <v>24278</v>
       </c>
       <c r="K10" t="n">
-        <v>4942515.24</v>
+        <v>1140580.44</v>
       </c>
       <c r="L10" t="n">
         <v>15696396</v>
@@ -20916,7 +20916,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>3053929.62</v>
+        <v>392648.09</v>
       </c>
       <c r="L11" t="n">
         <v>10940400</v>
@@ -20957,7 +20957,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>945239.65</v>
+        <v>45011.41</v>
       </c>
       <c r="L12" t="n">
         <v>4174200</v>
@@ -20998,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>461039.22</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>1609200</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>47196.43</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>426600</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>21600</v>
@@ -21633,7 +21633,7 @@
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>87</v>
       </c>
       <c r="L4" t="n">
         <v>403140</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="L5" t="n">
         <v>200910</v>
@@ -21715,7 +21715,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>106140</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>38850</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>6450</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>47.66</v>
+        <v>15.23</v>
       </c>
       <c r="L5" t="n">
         <v>42191.1</v>
@@ -22719,7 +22719,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>48.16</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>39271.8</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>15.95</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>23310</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>4579.5</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2314373.18</v>
+        <v>739313.66</v>
       </c>
       <c r="L5" t="n">
         <v>7594398</v>
@@ -23723,7 +23723,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2338699.74</v>
+        <v>467739.95</v>
       </c>
       <c r="L6" t="n">
         <v>7068924</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>774468.2</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
         <v>4195800</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>824310</v>

--- a/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_50yrs_Future_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>497340</v>
       </c>
       <c r="H4" t="n">
-        <v>69060</v>
+        <v>75480</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -572,22 +572,22 @@
         <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>1328160</v>
+        <v>1429530</v>
       </c>
       <c r="M4" t="n">
-        <v>66180</v>
+        <v>50220</v>
       </c>
       <c r="N4" t="n">
-        <v>76170</v>
+        <v>77580</v>
       </c>
       <c r="O4" t="n">
-        <v>229920</v>
+        <v>237300</v>
       </c>
       <c r="P4" t="n">
-        <v>46860</v>
+        <v>18510</v>
       </c>
       <c r="Q4" t="n">
-        <v>197580.66</v>
+        <v>2047509.23</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>330270</v>
       </c>
       <c r="H5" t="n">
-        <v>49080</v>
+        <v>54390</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -625,22 +625,22 @@
         <v>225</v>
       </c>
       <c r="L5" t="n">
-        <v>830100</v>
+        <v>867750</v>
       </c>
       <c r="M5" t="n">
-        <v>50400</v>
+        <v>32220</v>
       </c>
       <c r="N5" t="n">
-        <v>57780</v>
+        <v>72630</v>
       </c>
       <c r="O5" t="n">
-        <v>166380</v>
+        <v>188970</v>
       </c>
       <c r="P5" t="n">
-        <v>60480</v>
+        <v>38880</v>
       </c>
       <c r="Q5" t="n">
-        <v>134900.96</v>
+        <v>1397965.64</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>248220</v>
       </c>
       <c r="H6" t="n">
-        <v>57150</v>
+        <v>57930</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>170</v>
       </c>
       <c r="L6" t="n">
-        <v>636210</v>
+        <v>636570</v>
       </c>
       <c r="M6" t="n">
-        <v>29670</v>
+        <v>25800</v>
       </c>
       <c r="N6" t="n">
-        <v>13680</v>
+        <v>22770</v>
       </c>
       <c r="O6" t="n">
-        <v>108900</v>
+        <v>120900</v>
       </c>
       <c r="P6" t="n">
-        <v>61020</v>
+        <v>44310</v>
       </c>
       <c r="Q6" t="n">
-        <v>107181.87</v>
+        <v>1110715.32</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>202590</v>
       </c>
       <c r="H7" t="n">
-        <v>26130</v>
+        <v>28800</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -731,22 +731,22 @@
         <v>112</v>
       </c>
       <c r="L7" t="n">
-        <v>492990</v>
+        <v>498690</v>
       </c>
       <c r="M7" t="n">
-        <v>20550</v>
+        <v>27660</v>
       </c>
       <c r="N7" t="n">
-        <v>2970</v>
+        <v>6540</v>
       </c>
       <c r="O7" t="n">
-        <v>71730</v>
+        <v>79470</v>
       </c>
       <c r="P7" t="n">
-        <v>70170</v>
+        <v>53970</v>
       </c>
       <c r="Q7" t="n">
-        <v>87735.23</v>
+        <v>909191.73</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>163590</v>
       </c>
       <c r="H8" t="n">
-        <v>6270</v>
+        <v>8670</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -784,22 +784,22 @@
         <v>96</v>
       </c>
       <c r="L8" t="n">
-        <v>385440</v>
+        <v>408210</v>
       </c>
       <c r="M8" t="n">
-        <v>12540</v>
+        <v>30810</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="O8" t="n">
-        <v>61470</v>
+        <v>68430</v>
       </c>
       <c r="P8" t="n">
-        <v>69360</v>
+        <v>65880</v>
       </c>
       <c r="Q8" t="n">
-        <v>77139.48</v>
+        <v>799388.99</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>125310</v>
       </c>
       <c r="H9" t="n">
-        <v>4290</v>
+        <v>4590</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>63</v>
       </c>
       <c r="L9" t="n">
-        <v>271410</v>
+        <v>309270</v>
       </c>
       <c r="M9" t="n">
-        <v>9990</v>
+        <v>31800</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>35250</v>
+        <v>51360</v>
       </c>
       <c r="P9" t="n">
-        <v>74610</v>
+        <v>71190</v>
       </c>
       <c r="Q9" t="n">
-        <v>61277.89</v>
+        <v>635016.8</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>80850</v>
       </c>
       <c r="H10" t="n">
-        <v>5340</v>
+        <v>5040</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -890,22 +890,22 @@
         <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>180060</v>
+        <v>208710</v>
       </c>
       <c r="M10" t="n">
-        <v>6570</v>
+        <v>25830</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>10800</v>
+        <v>21210</v>
       </c>
       <c r="P10" t="n">
-        <v>81180</v>
+        <v>94680</v>
       </c>
       <c r="Q10" t="n">
-        <v>36996.4</v>
+        <v>383390.16</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>57870</v>
       </c>
       <c r="H11" t="n">
-        <v>3600</v>
+        <v>4710</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>159510</v>
+        <v>206760</v>
       </c>
       <c r="M11" t="n">
-        <v>3180</v>
+        <v>25860</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4710</v>
+        <v>13950</v>
       </c>
       <c r="P11" t="n">
-        <v>63600</v>
+        <v>99000</v>
       </c>
       <c r="Q11" t="n">
-        <v>27421.79</v>
+        <v>284169.4</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>42810</v>
       </c>
       <c r="H12" t="n">
-        <v>900</v>
+        <v>1260</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>80070</v>
+        <v>124140</v>
       </c>
       <c r="M12" t="n">
-        <v>2880</v>
+        <v>17040</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2100</v>
+        <v>3480</v>
       </c>
       <c r="P12" t="n">
-        <v>48660</v>
+        <v>83160</v>
       </c>
       <c r="Q12" t="n">
-        <v>17788.48</v>
+        <v>184340.32</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>19830</v>
       </c>
       <c r="H13" t="n">
-        <v>810</v>
+        <v>960</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1049,22 +1049,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>36240</v>
+        <v>58260</v>
       </c>
       <c r="M13" t="n">
-        <v>1200</v>
+        <v>19530</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3480</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>30660</v>
+        <v>46170</v>
       </c>
       <c r="Q13" t="n">
-        <v>8408.84</v>
+        <v>87139.96000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>6030</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,22 +1102,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>14700</v>
+        <v>28950</v>
       </c>
       <c r="M14" t="n">
-        <v>330</v>
+        <v>6150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="P14" t="n">
-        <v>33780</v>
+        <v>37200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3856.9</v>
+        <v>39968.64</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>2400</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4830</v>
+        <v>18720</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>2640</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P15" t="n">
-        <v>34710</v>
+        <v>50700</v>
       </c>
       <c r="Q15" t="n">
-        <v>1778.12</v>
+        <v>18426.51</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>510</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1860</v>
+        <v>8340</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>1380</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>24000</v>
+        <v>39390</v>
       </c>
       <c r="Q16" t="n">
-        <v>1050.94</v>
+        <v>10890.76</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>180</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1320</v>
+        <v>5640</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>930</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>16830</v>
+        <v>23190</v>
       </c>
       <c r="Q17" t="n">
-        <v>371.85</v>
+        <v>3853.46</v>
       </c>
     </row>
     <row r="18">
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1560</v>
+        <v>5220</v>
       </c>
       <c r="M18" t="n">
-        <v>90</v>
+        <v>1380</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18810</v>
+        <v>26820</v>
       </c>
       <c r="Q18" t="n">
-        <v>253.56</v>
+        <v>2627.57</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
         <v>3750</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1367,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>2370</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5040</v>
+        <v>14340</v>
       </c>
       <c r="Q19" t="n">
-        <v>69.19</v>
+        <v>717.03</v>
       </c>
     </row>
     <row r="20">
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.73</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="21">
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.78</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="22">
@@ -1852,7 +1852,7 @@
         <v>7470</v>
       </c>
       <c r="H4" t="n">
-        <v>2730</v>
+        <v>3450</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>18090</v>
+        <v>15270</v>
       </c>
       <c r="M4" t="n">
-        <v>6300</v>
+        <v>2520</v>
       </c>
       <c r="N4" t="n">
-        <v>1050</v>
+        <v>600</v>
       </c>
       <c r="O4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>236.9</v>
+        <v>26848.44</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>8970</v>
       </c>
       <c r="H5" t="n">
-        <v>2250</v>
+        <v>2820</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>29160</v>
+        <v>21600</v>
       </c>
       <c r="M5" t="n">
-        <v>13440</v>
+        <v>6270</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>630</v>
       </c>
       <c r="O5" t="n">
-        <v>330</v>
+        <v>120</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>497.29</v>
+        <v>56359.08</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>9930</v>
       </c>
       <c r="H6" t="n">
-        <v>3030</v>
+        <v>2880</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>33270</v>
+        <v>25410</v>
       </c>
       <c r="M6" t="n">
-        <v>9510</v>
+        <v>5670</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>690</v>
+        <v>780</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1047.33</v>
+        <v>118697.4</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>17610</v>
       </c>
       <c r="H7" t="n">
-        <v>4260</v>
+        <v>3240</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>41400</v>
+        <v>36300</v>
       </c>
       <c r="M7" t="n">
-        <v>6660</v>
+        <v>3000</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1384.56</v>
+        <v>156916.8</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>22350</v>
       </c>
       <c r="H8" t="n">
-        <v>2940</v>
+        <v>4170</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -2076,10 +2076,10 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>48540</v>
+        <v>49470</v>
       </c>
       <c r="M8" t="n">
-        <v>3630</v>
+        <v>2970</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1477.41</v>
+        <v>167440.14</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>15690</v>
       </c>
       <c r="H9" t="n">
-        <v>3570</v>
+        <v>3600</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>44820</v>
+        <v>46050</v>
       </c>
       <c r="M9" t="n">
-        <v>2700</v>
+        <v>2040</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1351.62</v>
+        <v>153183.6</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>24030</v>
       </c>
       <c r="H10" t="n">
-        <v>5310</v>
+        <v>4830</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -2182,22 +2182,22 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>70290</v>
+        <v>66900</v>
       </c>
       <c r="M10" t="n">
-        <v>1830</v>
+        <v>3630</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1378.86</v>
+        <v>156271.14</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>33690</v>
       </c>
       <c r="H11" t="n">
-        <v>3510</v>
+        <v>4290</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -2235,22 +2235,22 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>93510</v>
+        <v>98790</v>
       </c>
       <c r="M11" t="n">
-        <v>660</v>
+        <v>4440</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1956.07</v>
+        <v>221687.82</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>24960</v>
       </c>
       <c r="H12" t="n">
-        <v>900</v>
+        <v>1110</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>53310</v>
+        <v>63330</v>
       </c>
       <c r="M12" t="n">
-        <v>300</v>
+        <v>4050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1592.65</v>
+        <v>180500.22</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>11070</v>
       </c>
       <c r="H13" t="n">
-        <v>810</v>
+        <v>960</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>25980</v>
+        <v>32700</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>3420</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>735.9400000000001</v>
+        <v>83406.42</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>4380</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11340</v>
+        <v>16410</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>3180</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>423.87</v>
+        <v>48038.94</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>1170</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3630</v>
+        <v>8700</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1470</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>168.61</v>
+        <v>19109.7</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>300</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1440</v>
+        <v>3150</v>
       </c>
       <c r="M16" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>106.16</v>
+        <v>12031.92</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>30</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>810</v>
+        <v>1650</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>840</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.5</v>
+        <v>4476.78</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>780</v>
+        <v>2430</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.33</v>
+        <v>1964.52</v>
       </c>
     </row>
     <row r="19">
@@ -2647,7 +2647,7 @@
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>510</v>
+        <v>1890</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.67</v>
+        <v>642.6</v>
       </c>
     </row>
     <row r="20">
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.32</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="21">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.11</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="22">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>810</v>
+        <v>1015.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>2.98</v>
       </c>
       <c r="L5" t="n">
-        <v>6123.6</v>
+        <v>4536</v>
       </c>
       <c r="M5" t="n">
-        <v>268.8</v>
+        <v>125.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="O5" t="n">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>24.86</v>
+        <v>2817.95</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>496.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1727.1</v>
+        <v>1641.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>5.58</v>
       </c>
       <c r="L6" t="n">
-        <v>12309.9</v>
+        <v>9401.700000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>760.8</v>
+        <v>453.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>172.5</v>
+        <v>195</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>785.5</v>
+        <v>89023.05</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>2641.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3109.8</v>
+        <v>2365.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>9.57</v>
       </c>
       <c r="L7" t="n">
-        <v>24840</v>
+        <v>21780</v>
       </c>
       <c r="M7" t="n">
-        <v>2331</v>
+        <v>1050</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1107.65</v>
+        <v>125533.44</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>14527.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2499</v>
+        <v>3544.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -3368,10 +3368,10 @@
         <v>4.42</v>
       </c>
       <c r="L8" t="n">
-        <v>34463.4</v>
+        <v>35123.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1996.5</v>
+        <v>1633.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1403.54</v>
+        <v>159068.13</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>13336.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3570</v>
+        <v>3600</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>3.21</v>
       </c>
       <c r="L9" t="n">
-        <v>36304.2</v>
+        <v>37300.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1890</v>
+        <v>1428</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>82.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1311.07</v>
+        <v>148588.09</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>24030</v>
       </c>
       <c r="H10" t="n">
-        <v>5310</v>
+        <v>4830</v>
       </c>
       <c r="I10" t="n">
         <v>1.74</v>
@@ -3474,22 +3474,22 @@
         <v>2.61</v>
       </c>
       <c r="L10" t="n">
-        <v>62558.1</v>
+        <v>59541</v>
       </c>
       <c r="M10" t="n">
-        <v>1555.5</v>
+        <v>3085.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1378.86</v>
+        <v>156271.14</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>33690</v>
       </c>
       <c r="H11" t="n">
-        <v>3510</v>
+        <v>4290</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>5.39</v>
       </c>
       <c r="L11" t="n">
-        <v>93510</v>
+        <v>98790</v>
       </c>
       <c r="M11" t="n">
-        <v>594</v>
+        <v>3996</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>76.5</v>
+        <v>178.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1956.07</v>
+        <v>221687.82</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>24960</v>
       </c>
       <c r="H12" t="n">
-        <v>900</v>
+        <v>1110</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>3.71</v>
       </c>
       <c r="L12" t="n">
-        <v>53310</v>
+        <v>63330</v>
       </c>
       <c r="M12" t="n">
-        <v>285</v>
+        <v>3847.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1592.65</v>
+        <v>180500.22</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>11070</v>
       </c>
       <c r="H13" t="n">
-        <v>810</v>
+        <v>960</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>25980</v>
+        <v>32700</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>3420</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>735.9400000000001</v>
+        <v>83406.42</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>4380</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11340</v>
+        <v>16410</v>
       </c>
       <c r="M14" t="n">
-        <v>150</v>
+        <v>3180</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>423.87</v>
+        <v>48038.94</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>1170</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3630</v>
+        <v>8700</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1470</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>168.61</v>
+        <v>19109.7</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>300</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1440</v>
+        <v>3150</v>
       </c>
       <c r="M16" t="n">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>106.16</v>
+        <v>12031.92</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>30</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>810</v>
+        <v>1650</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>840</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.5</v>
+        <v>4476.78</v>
       </c>
     </row>
     <row r="18">
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>780</v>
+        <v>2430</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.33</v>
+        <v>1964.52</v>
       </c>
     </row>
     <row r="19">
@@ -3939,7 +3939,7 @@
         <v>60</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>510</v>
+        <v>1890</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1290</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.67</v>
+        <v>642.6</v>
       </c>
     </row>
     <row r="20">
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.32</v>
+        <v>149.94</v>
       </c>
     </row>
     <row r="21">
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.11</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="22">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4617000</v>
+        <v>5786640</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>1102248</v>
+        <v>816480</v>
       </c>
       <c r="M5" t="n">
-        <v>94080</v>
+        <v>43890</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>1071</v>
       </c>
       <c r="O5" t="n">
-        <v>2805</v>
+        <v>1020</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14918.58</v>
+        <v>1690772.4</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>26811</v>
       </c>
       <c r="H6" t="n">
-        <v>9844470</v>
+        <v>9357120</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>270796.81</v>
       </c>
       <c r="L6" t="n">
-        <v>2215782</v>
+        <v>1692306</v>
       </c>
       <c r="M6" t="n">
-        <v>266280</v>
+        <v>158760</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>29325</v>
+        <v>33150</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>471298.5</v>
+        <v>53413830</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>142641</v>
       </c>
       <c r="H7" t="n">
-        <v>17725860</v>
+        <v>13481640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>464680.92</v>
       </c>
       <c r="L7" t="n">
-        <v>4471200</v>
+        <v>3920400</v>
       </c>
       <c r="M7" t="n">
-        <v>815850</v>
+        <v>367500</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24990</v>
+        <v>28560</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>664588.8</v>
+        <v>75320064</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>784485</v>
       </c>
       <c r="H8" t="n">
-        <v>14244300</v>
+        <v>20203650</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -4660,10 +4660,10 @@
         <v>214423.3</v>
       </c>
       <c r="L8" t="n">
-        <v>6203412</v>
+        <v>6322266</v>
       </c>
       <c r="M8" t="n">
-        <v>698775</v>
+        <v>571725</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>842125.41</v>
+        <v>95440879.8</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>720171</v>
       </c>
       <c r="H9" t="n">
-        <v>20349000</v>
+        <v>20520000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>155961.87</v>
       </c>
       <c r="L9" t="n">
-        <v>6534756</v>
+        <v>6714090</v>
       </c>
       <c r="M9" t="n">
-        <v>661500</v>
+        <v>499800</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>14025</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>786642.84</v>
+        <v>89152855.2</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1297620</v>
       </c>
       <c r="H10" t="n">
-        <v>30267000</v>
+        <v>27531000</v>
       </c>
       <c r="I10" t="n">
         <v>337949.76</v>
@@ -4766,22 +4766,22 @@
         <v>126731.16</v>
       </c>
       <c r="L10" t="n">
-        <v>11260458</v>
+        <v>10717380</v>
       </c>
       <c r="M10" t="n">
-        <v>544425</v>
+        <v>1079925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21420</v>
+        <v>10710</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>827317.8</v>
+        <v>93762684</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1819260</v>
       </c>
       <c r="H11" t="n">
-        <v>20007000</v>
+        <v>24453000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4819,22 +4819,22 @@
         <v>261765.4</v>
       </c>
       <c r="L11" t="n">
-        <v>16831800</v>
+        <v>17782200</v>
       </c>
       <c r="M11" t="n">
-        <v>207900</v>
+        <v>1398600</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13005</v>
+        <v>30345</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1173641.4</v>
+        <v>133012692</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1347840</v>
       </c>
       <c r="H12" t="n">
-        <v>5130000</v>
+        <v>6327000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>180045.65</v>
       </c>
       <c r="L12" t="n">
-        <v>9595800</v>
+        <v>11399400</v>
       </c>
       <c r="M12" t="n">
-        <v>99750</v>
+        <v>1346625</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>955589.4</v>
+        <v>108300132</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>597780</v>
       </c>
       <c r="H13" t="n">
-        <v>4617000</v>
+        <v>5472000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4676400</v>
+        <v>5886000</v>
       </c>
       <c r="M13" t="n">
-        <v>63000</v>
+        <v>1197000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>441563.4</v>
+        <v>50043852</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>236520</v>
       </c>
       <c r="H14" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2041200</v>
+        <v>2953800</v>
       </c>
       <c r="M14" t="n">
-        <v>52500</v>
+        <v>1113000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>254323.8</v>
+        <v>28823364</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>63180</v>
       </c>
       <c r="H15" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>653400</v>
+        <v>1566000</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>514500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>101169</v>
+        <v>11465820</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>16200</v>
       </c>
       <c r="H16" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>259200</v>
+        <v>567000</v>
       </c>
       <c r="M16" t="n">
-        <v>52500</v>
+        <v>262500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>63698.4</v>
+        <v>7219152</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>1620</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>145800</v>
+        <v>297000</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>294000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23700.6</v>
+        <v>2686068</v>
       </c>
     </row>
     <row r="18">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>140400</v>
+        <v>437400</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>451500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>10400.4</v>
+        <v>1178712</v>
       </c>
     </row>
     <row r="19">
@@ -5231,7 +5231,7 @@
         <v>3240</v>
       </c>
       <c r="H19" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>91800</v>
+        <v>340200</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>451500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3402</v>
+        <v>385560</v>
       </c>
     </row>
     <row r="20">
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>793.8</v>
+        <v>89964</v>
       </c>
     </row>
     <row r="21">
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>64.8</v>
+        <v>7344</v>
       </c>
     </row>
     <row r="22">
@@ -5728,7 +5728,7 @@
         <v>38490</v>
       </c>
       <c r="H4" t="n">
-        <v>4170</v>
+        <v>6360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>120360</v>
+        <v>140700</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9060</v>
+        <v>7710</v>
       </c>
       <c r="O4" t="n">
-        <v>18990</v>
+        <v>20730</v>
       </c>
       <c r="P4" t="n">
-        <v>10950</v>
+        <v>8640</v>
       </c>
       <c r="Q4" t="n">
-        <v>21475</v>
+        <v>113026.32</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>13860</v>
       </c>
       <c r="H5" t="n">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>45690</v>
+        <v>59700</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8190</v>
+        <v>10380</v>
       </c>
       <c r="O5" t="n">
-        <v>6000</v>
+        <v>9900</v>
       </c>
       <c r="P5" t="n">
-        <v>8550</v>
+        <v>12240</v>
       </c>
       <c r="Q5" t="n">
-        <v>8874.49</v>
+        <v>46707.84</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1770</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9120</v>
+        <v>14040</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="O6" t="n">
-        <v>360</v>
+        <v>1170</v>
       </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>8730</v>
       </c>
       <c r="Q6" t="n">
-        <v>729.28</v>
+        <v>3838.32</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>420</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1980</v>
+        <v>3720</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5580</v>
+        <v>8280</v>
       </c>
       <c r="Q7" t="n">
-        <v>81.05</v>
+        <v>426.6</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>420</v>
+        <v>1920</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5100</v>
+        <v>10260</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.53</v>
+        <v>234.36</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4170</v>
+        <v>10380</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.78</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1350</v>
+        <v>3930</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.210000000000001</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>172.8</v>
+        <v>432</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>9594.9</v>
+        <v>12537</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>81.90000000000001</v>
+        <v>103.8</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>495</v>
       </c>
       <c r="P5" t="n">
-        <v>171</v>
+        <v>244.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>443.72</v>
+        <v>2335.39</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>88.5</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3374.4</v>
+        <v>5194.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>292.5</v>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>1309.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>546.96</v>
+        <v>2878.74</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>63</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>109.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1188</v>
+        <v>2232</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1395</v>
+        <v>2070</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.84</v>
+        <v>341.28</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>298.2</v>
+        <v>1363.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1938</v>
+        <v>3898.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>42.3</v>
+        <v>222.64</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>704.7</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2085</v>
+        <v>5190</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.09</v>
+        <v>116.28</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1147.5</v>
+        <v>3340.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.210000000000001</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>984960</v>
+        <v>2462400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1727082</v>
+        <v>2256660</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>13923</v>
+        <v>17646</v>
       </c>
       <c r="O5" t="n">
-        <v>51000</v>
+        <v>84150</v>
       </c>
       <c r="P5" t="n">
-        <v>11115</v>
+        <v>15912</v>
       </c>
       <c r="Q5" t="n">
-        <v>266234.69</v>
+        <v>1401235.2</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>607392</v>
+        <v>935064</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1530</v>
+        <v>3570</v>
       </c>
       <c r="O6" t="n">
-        <v>15300</v>
+        <v>49725</v>
       </c>
       <c r="P6" t="n">
-        <v>58500</v>
+        <v>85117.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>328176.36</v>
+        <v>1727244</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>3402</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>624150</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>213840</v>
+        <v>401760</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>90675</v>
+        <v>134550</v>
       </c>
       <c r="Q7" t="n">
-        <v>38905.92</v>
+        <v>204768</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>53676</v>
+        <v>245376</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>125970</v>
+        <v>253422</v>
       </c>
       <c r="Q8" t="n">
-        <v>25381.19</v>
+        <v>133585.2</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>126846</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>135525</v>
+        <v>337350</v>
       </c>
       <c r="Q9" t="n">
-        <v>13256.33</v>
+        <v>69770.16</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>74587.5</v>
+        <v>217132.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4924.8</v>
+        <v>25920</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>63540</v>
       </c>
       <c r="H4" t="n">
-        <v>4470</v>
+        <v>4560</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>94350</v>
+        <v>114570</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>18600</v>
+        <v>21720</v>
       </c>
       <c r="O4" t="n">
-        <v>31680</v>
+        <v>31980</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>26663.87</v>
+        <v>144687.69</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>14940</v>
       </c>
       <c r="H5" t="n">
-        <v>3180</v>
+        <v>3750</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>28800</v>
+        <v>34470</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7530</v>
+        <v>8340</v>
       </c>
       <c r="O5" t="n">
-        <v>26340</v>
+        <v>26280</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5505.11</v>
+        <v>29872.71</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>4440</v>
       </c>
       <c r="H6" t="n">
-        <v>960</v>
+        <v>1470</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7080</v>
+        <v>12720</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3660</v>
+        <v>4410</v>
       </c>
       <c r="O6" t="n">
-        <v>21450</v>
+        <v>23670</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>755.11</v>
+        <v>4097.52</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>1500</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2790</v>
+        <v>4380</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>720</v>
+        <v>2220</v>
       </c>
       <c r="O7" t="n">
-        <v>8970</v>
+        <v>11010</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>198.41</v>
+        <v>1076.67</v>
       </c>
     </row>
     <row r="8">
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1020</v>
+        <v>1800</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O8" t="n">
-        <v>1740</v>
+        <v>3840</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>69.2</v>
+        <v>375.48</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.02</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1144.8</v>
+        <v>1350</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>1.32</v>
       </c>
       <c r="L5" t="n">
-        <v>6048</v>
+        <v>7238.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>75.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>275.26</v>
+        <v>1493.64</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>222</v>
       </c>
       <c r="H6" t="n">
-        <v>547.2</v>
+        <v>837.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2619.6</v>
+        <v>4706.4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>183</v>
+        <v>220.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5362.5</v>
+        <v>5917.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>566.34</v>
+        <v>3073.14</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>225</v>
       </c>
       <c r="H7" t="n">
-        <v>87.59999999999999</v>
+        <v>372.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1674</v>
+        <v>2628</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>50.4</v>
+        <v>155.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3139.5</v>
+        <v>3853.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>158.73</v>
+        <v>861.34</v>
       </c>
     </row>
     <row r="8">
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>724.2</v>
+        <v>1278</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O8" t="n">
-        <v>783</v>
+        <v>1728</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>65.73999999999999</v>
+        <v>356.71</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>396</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.93</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6525360</v>
+        <v>7695000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>64288.14</v>
       </c>
       <c r="L5" t="n">
-        <v>1088640</v>
+        <v>1302966</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>12801</v>
+        <v>14178</v>
       </c>
       <c r="O5" t="n">
-        <v>223890</v>
+        <v>223380</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>165153.41</v>
+        <v>896181.3</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>11988</v>
       </c>
       <c r="H6" t="n">
-        <v>3119040</v>
+        <v>4776030</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>471528</v>
+        <v>847152</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>31110</v>
+        <v>37485</v>
       </c>
       <c r="O6" t="n">
-        <v>911625</v>
+        <v>1005975</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>339801.48</v>
+        <v>1843884</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>12150</v>
       </c>
       <c r="H7" t="n">
-        <v>499320</v>
+        <v>2122110</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>301320</v>
+        <v>473040</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8568</v>
+        <v>26418</v>
       </c>
       <c r="O7" t="n">
-        <v>533715</v>
+        <v>655095</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>95239.14999999999</v>
+        <v>516801.6</v>
       </c>
     </row>
     <row r="8">
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>130356</v>
+        <v>230040</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4080</v>
       </c>
       <c r="O8" t="n">
-        <v>133110</v>
+        <v>293760</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39441.49</v>
+        <v>214023.6</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>28050</v>
+        <v>67320</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1756.83</v>
+        <v>9533.16</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>81510</v>
       </c>
       <c r="H4" t="n">
-        <v>9060</v>
+        <v>9930</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>130</v>
       </c>
       <c r="L4" t="n">
-        <v>199770</v>
+        <v>197490</v>
       </c>
       <c r="M4" t="n">
-        <v>17280</v>
+        <v>960</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>37380</v>
+        <v>40980</v>
       </c>
       <c r="P4" t="n">
-        <v>23790</v>
+        <v>4920</v>
       </c>
       <c r="Q4" t="n">
         <v>34191</v>
@@ -13533,7 +13533,7 @@
         <v>88410</v>
       </c>
       <c r="H5" t="n">
-        <v>7590</v>
+        <v>8040</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -13545,19 +13545,19 @@
         <v>84</v>
       </c>
       <c r="L5" t="n">
-        <v>190710</v>
+        <v>179520</v>
       </c>
       <c r="M5" t="n">
-        <v>18630</v>
+        <v>1980</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31440</v>
+        <v>37920</v>
       </c>
       <c r="P5" t="n">
-        <v>35550</v>
+        <v>16320</v>
       </c>
       <c r="Q5" t="n">
         <v>37590.79</v>
@@ -13586,7 +13586,7 @@
         <v>84780</v>
       </c>
       <c r="H6" t="n">
-        <v>12150</v>
+        <v>12930</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>83</v>
       </c>
       <c r="L6" t="n">
-        <v>211560</v>
+        <v>195570</v>
       </c>
       <c r="M6" t="n">
-        <v>10740</v>
+        <v>3870</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>24420</v>
+        <v>24000</v>
       </c>
       <c r="P6" t="n">
-        <v>35010</v>
+        <v>23190</v>
       </c>
       <c r="Q6" t="n">
         <v>43525.45</v>
@@ -13639,7 +13639,7 @@
         <v>63510</v>
       </c>
       <c r="H7" t="n">
-        <v>3960</v>
+        <v>4020</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -13651,19 +13651,19 @@
         <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>130770</v>
+        <v>121980</v>
       </c>
       <c r="M7" t="n">
-        <v>6480</v>
+        <v>5490</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>20850</v>
+        <v>22080</v>
       </c>
       <c r="P7" t="n">
-        <v>35400</v>
+        <v>29010</v>
       </c>
       <c r="Q7" t="n">
         <v>34456.05</v>
@@ -13692,7 +13692,7 @@
         <v>38400</v>
       </c>
       <c r="H8" t="n">
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>33</v>
       </c>
       <c r="L8" t="n">
-        <v>76770</v>
+        <v>83430</v>
       </c>
       <c r="M8" t="n">
-        <v>3570</v>
+        <v>10560</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>28050</v>
+        <v>26850</v>
       </c>
       <c r="P8" t="n">
-        <v>32370</v>
+        <v>33660</v>
       </c>
       <c r="Q8" t="n">
         <v>28858.42</v>
@@ -13745,7 +13745,7 @@
         <v>18630</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>40500</v>
+        <v>49680</v>
       </c>
       <c r="M9" t="n">
-        <v>2100</v>
+        <v>12540</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>9780</v>
+        <v>15390</v>
       </c>
       <c r="P9" t="n">
-        <v>36240</v>
+        <v>36180</v>
       </c>
       <c r="Q9" t="n">
         <v>15852.22</v>
@@ -13810,19 +13810,19 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>9270</v>
+        <v>21840</v>
       </c>
       <c r="M10" t="n">
-        <v>930</v>
+        <v>11040</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>630</v>
+        <v>1680</v>
       </c>
       <c r="P10" t="n">
-        <v>38790</v>
+        <v>44790</v>
       </c>
       <c r="Q10" t="n">
         <v>1705.92</v>
@@ -13863,10 +13863,10 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>4290</v>
+        <v>29730</v>
       </c>
       <c r="M11" t="n">
-        <v>360</v>
+        <v>10110</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>30630</v>
+        <v>47520</v>
       </c>
       <c r="Q11" t="n">
         <v>332.57</v>
@@ -13904,7 +13904,7 @@
         <v>150</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>24840</v>
       </c>
       <c r="M12" t="n">
-        <v>210</v>
+        <v>6000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>25890</v>
+        <v>47280</v>
       </c>
       <c r="Q12" t="n">
         <v>241.95</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1230</v>
+        <v>10560</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>9450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14280</v>
+        <v>25740</v>
       </c>
       <c r="Q13" t="n">
         <v>111.6</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>3810</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>5700</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12600</v>
+        <v>21450</v>
       </c>
       <c r="Q15" t="n">
         <v>21.32</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>2820</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10380</v>
+        <v>24270</v>
       </c>
       <c r="Q16" t="n">
         <v>12.28</v>
@@ -14181,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>2640</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3540</v>
+        <v>8130</v>
       </c>
       <c r="Q17" t="n">
         <v>6.25</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>1170</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q18" t="n">
         <v>1.79</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17668.8</v>
+        <v>19580.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -14837,22 +14837,22 @@
         <v>74.48</v>
       </c>
       <c r="L5" t="n">
-        <v>174321</v>
+        <v>182227.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1008</v>
+        <v>644.4</v>
       </c>
       <c r="N5" t="n">
-        <v>577.8</v>
+        <v>726.3</v>
       </c>
       <c r="O5" t="n">
-        <v>8319</v>
+        <v>9448.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1209.6</v>
+        <v>777.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>6745.05</v>
+        <v>69898.28</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12411</v>
       </c>
       <c r="H6" t="n">
-        <v>32575.5</v>
+        <v>33020.1</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>86.19</v>
       </c>
       <c r="L6" t="n">
-        <v>235397.7</v>
+        <v>235530.9</v>
       </c>
       <c r="M6" t="n">
-        <v>2373.6</v>
+        <v>2064</v>
       </c>
       <c r="N6" t="n">
-        <v>684</v>
+        <v>1138.5</v>
       </c>
       <c r="O6" t="n">
-        <v>27225</v>
+        <v>30225</v>
       </c>
       <c r="P6" t="n">
-        <v>9153</v>
+        <v>6646.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>80386.39999999999</v>
+        <v>833036.49</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>30388.5</v>
       </c>
       <c r="H7" t="n">
-        <v>19074.9</v>
+        <v>21024</v>
       </c>
       <c r="I7" t="n">
         <v>2.55</v>
@@ -14943,22 +14943,22 @@
         <v>71.45999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>295794</v>
+        <v>299214</v>
       </c>
       <c r="M7" t="n">
-        <v>7192.5</v>
+        <v>9681</v>
       </c>
       <c r="N7" t="n">
-        <v>207.9</v>
+        <v>457.8</v>
       </c>
       <c r="O7" t="n">
-        <v>25105.5</v>
+        <v>27814.5</v>
       </c>
       <c r="P7" t="n">
-        <v>17542.5</v>
+        <v>13492.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>70188.19</v>
+        <v>727353.38</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>106333.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5329.5</v>
+        <v>7369.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -14996,22 +14996,22 @@
         <v>70.66</v>
       </c>
       <c r="L8" t="n">
-        <v>273662.4</v>
+        <v>289829.1</v>
       </c>
       <c r="M8" t="n">
-        <v>6897</v>
+        <v>16945.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O8" t="n">
-        <v>27661.5</v>
+        <v>30793.5</v>
       </c>
       <c r="P8" t="n">
-        <v>26356.8</v>
+        <v>25034.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>73282.50999999999</v>
+        <v>759419.54</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>106513.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4290</v>
+        <v>4590</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>50.59</v>
       </c>
       <c r="L9" t="n">
-        <v>219842.1</v>
+        <v>250508.7</v>
       </c>
       <c r="M9" t="n">
-        <v>6993</v>
+        <v>22260</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>19387.5</v>
+        <v>28248</v>
       </c>
       <c r="P9" t="n">
-        <v>37305</v>
+        <v>35595</v>
       </c>
       <c r="Q9" t="n">
-        <v>59439.55</v>
+        <v>615966.3</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>80850</v>
       </c>
       <c r="H10" t="n">
-        <v>5340</v>
+        <v>5040</v>
       </c>
       <c r="I10" t="n">
         <v>2.61</v>
@@ -15102,22 +15102,22 @@
         <v>27.84</v>
       </c>
       <c r="L10" t="n">
-        <v>160253.4</v>
+        <v>185751.9</v>
       </c>
       <c r="M10" t="n">
-        <v>5584.5</v>
+        <v>21955.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>7560</v>
+        <v>14847</v>
       </c>
       <c r="P10" t="n">
-        <v>69003</v>
+        <v>80478</v>
       </c>
       <c r="Q10" t="n">
-        <v>36996.4</v>
+        <v>383390.16</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>57870</v>
       </c>
       <c r="H11" t="n">
-        <v>3600</v>
+        <v>4710</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15155,22 +15155,22 @@
         <v>15.27</v>
       </c>
       <c r="L11" t="n">
-        <v>159510</v>
+        <v>206760</v>
       </c>
       <c r="M11" t="n">
-        <v>2862</v>
+        <v>23274</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4003.5</v>
+        <v>11857.5</v>
       </c>
       <c r="P11" t="n">
-        <v>57240</v>
+        <v>89100</v>
       </c>
       <c r="Q11" t="n">
-        <v>27421.79</v>
+        <v>284169.4</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>42810</v>
       </c>
       <c r="H12" t="n">
-        <v>900</v>
+        <v>1260</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>80070</v>
+        <v>124140</v>
       </c>
       <c r="M12" t="n">
-        <v>2736</v>
+        <v>16188</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2100</v>
+        <v>3480</v>
       </c>
       <c r="P12" t="n">
-        <v>48660</v>
+        <v>83160</v>
       </c>
       <c r="Q12" t="n">
-        <v>17788.48</v>
+        <v>184340.32</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>19830</v>
       </c>
       <c r="H13" t="n">
-        <v>810</v>
+        <v>960</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
@@ -15261,22 +15261,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>36240</v>
+        <v>58260</v>
       </c>
       <c r="M13" t="n">
-        <v>1200</v>
+        <v>19530</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3480</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>30660</v>
+        <v>46170</v>
       </c>
       <c r="Q13" t="n">
-        <v>8408.84</v>
+        <v>87139.96000000001</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>6030</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,22 +15314,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>14700</v>
+        <v>28950</v>
       </c>
       <c r="M14" t="n">
-        <v>330</v>
+        <v>6150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="P14" t="n">
-        <v>33780</v>
+        <v>37200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3856.9</v>
+        <v>39968.64</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>2400</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4830</v>
+        <v>18720</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>2640</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P15" t="n">
-        <v>34710</v>
+        <v>50700</v>
       </c>
       <c r="Q15" t="n">
-        <v>1778.12</v>
+        <v>18426.51</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>510</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1860</v>
+        <v>8340</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>1380</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>24000</v>
+        <v>39390</v>
       </c>
       <c r="Q16" t="n">
-        <v>1050.94</v>
+        <v>10890.76</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>180</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1320</v>
+        <v>5640</v>
       </c>
       <c r="M17" t="n">
-        <v>150</v>
+        <v>930</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>16830</v>
+        <v>23190</v>
       </c>
       <c r="Q17" t="n">
-        <v>371.85</v>
+        <v>3853.46</v>
       </c>
     </row>
     <row r="18">
@@ -15526,22 +15526,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1560</v>
+        <v>5220</v>
       </c>
       <c r="M18" t="n">
-        <v>90</v>
+        <v>1380</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18810</v>
+        <v>26820</v>
       </c>
       <c r="Q18" t="n">
-        <v>253.56</v>
+        <v>2627.57</v>
       </c>
     </row>
     <row r="19">
@@ -15567,7 +15567,7 @@
         <v>3750</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>2370</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -15591,10 +15591,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5040</v>
+        <v>14340</v>
       </c>
       <c r="Q19" t="n">
-        <v>69.19</v>
+        <v>717.03</v>
       </c>
     </row>
     <row r="20">
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.73</v>
+        <v>152.66</v>
       </c>
     </row>
     <row r="21">
@@ -15685,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.78</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="22">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2732.4</v>
+        <v>2894.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.99</v>
@@ -16129,19 +16129,19 @@
         <v>27.8</v>
       </c>
       <c r="L5" t="n">
-        <v>40049.1</v>
+        <v>37699.2</v>
       </c>
       <c r="M5" t="n">
-        <v>372.6</v>
+        <v>39.6</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1572</v>
+        <v>1896</v>
       </c>
       <c r="P5" t="n">
-        <v>711</v>
+        <v>326.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1879.54</v>
@@ -16170,7 +16170,7 @@
         <v>4239</v>
       </c>
       <c r="H6" t="n">
-        <v>6925.5</v>
+        <v>7370.1</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>42.08</v>
       </c>
       <c r="L6" t="n">
-        <v>78277.2</v>
+        <v>72360.89999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>859.2</v>
+        <v>309.6</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6105</v>
+        <v>6000</v>
       </c>
       <c r="P6" t="n">
-        <v>5251.5</v>
+        <v>3478.5</v>
       </c>
       <c r="Q6" t="n">
         <v>32644.09</v>
@@ -16223,7 +16223,7 @@
         <v>9526.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2890.8</v>
+        <v>2934.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.91</v>
@@ -16235,19 +16235,19 @@
         <v>25.52</v>
       </c>
       <c r="L7" t="n">
-        <v>78462</v>
+        <v>73188</v>
       </c>
       <c r="M7" t="n">
-        <v>2268</v>
+        <v>1921.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>7297.5</v>
+        <v>7728</v>
       </c>
       <c r="P7" t="n">
-        <v>8850</v>
+        <v>7252.5</v>
       </c>
       <c r="Q7" t="n">
         <v>27564.84</v>
@@ -16276,7 +16276,7 @@
         <v>24960</v>
       </c>
       <c r="H8" t="n">
-        <v>382.5</v>
+        <v>637.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>24.29</v>
       </c>
       <c r="L8" t="n">
-        <v>54506.7</v>
+        <v>59235.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1963.5</v>
+        <v>5808</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>12622.5</v>
+        <v>12082.5</v>
       </c>
       <c r="P8" t="n">
-        <v>12300.6</v>
+        <v>12790.8</v>
       </c>
       <c r="Q8" t="n">
         <v>27415.5</v>
@@ -16329,7 +16329,7 @@
         <v>15835.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>5.62</v>
       </c>
       <c r="L9" t="n">
-        <v>32805</v>
+        <v>40240.8</v>
       </c>
       <c r="M9" t="n">
-        <v>1470</v>
+        <v>8778</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5379</v>
+        <v>8464.5</v>
       </c>
       <c r="P9" t="n">
-        <v>18120</v>
+        <v>18090</v>
       </c>
       <c r="Q9" t="n">
         <v>15376.66</v>
@@ -16394,19 +16394,19 @@
         <v>1.74</v>
       </c>
       <c r="L10" t="n">
-        <v>8250.299999999999</v>
+        <v>19437.6</v>
       </c>
       <c r="M10" t="n">
-        <v>790.5</v>
+        <v>9384</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>441</v>
+        <v>1176</v>
       </c>
       <c r="P10" t="n">
-        <v>32971.5</v>
+        <v>38071.5</v>
       </c>
       <c r="Q10" t="n">
         <v>1705.92</v>
@@ -16447,10 +16447,10 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>4290</v>
+        <v>29730</v>
       </c>
       <c r="M11" t="n">
-        <v>324</v>
+        <v>9099</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>27567</v>
+        <v>42768</v>
       </c>
       <c r="Q11" t="n">
         <v>332.57</v>
@@ -16488,7 +16488,7 @@
         <v>150</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3450</v>
+        <v>24840</v>
       </c>
       <c r="M12" t="n">
-        <v>199.5</v>
+        <v>5700</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>25890</v>
+        <v>47280</v>
       </c>
       <c r="Q12" t="n">
         <v>241.95</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1230</v>
+        <v>10560</v>
       </c>
       <c r="M13" t="n">
-        <v>150</v>
+        <v>9450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14280</v>
+        <v>25740</v>
       </c>
       <c r="Q13" t="n">
         <v>111.6</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>480</v>
+        <v>3810</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>360</v>
+        <v>5700</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12600</v>
+        <v>21450</v>
       </c>
       <c r="Q15" t="n">
         <v>21.32</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>2820</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>10380</v>
+        <v>24270</v>
       </c>
       <c r="Q16" t="n">
         <v>12.28</v>
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>2640</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3540</v>
+        <v>8130</v>
       </c>
       <c r="Q17" t="n">
         <v>6.25</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>660</v>
+        <v>1170</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q18" t="n">
         <v>1.79</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>15574680</v>
+        <v>16498080</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -17421,19 +17421,19 @@
         <v>1350051.02</v>
       </c>
       <c r="L5" t="n">
-        <v>7208838</v>
+        <v>6785856</v>
       </c>
       <c r="M5" t="n">
-        <v>130410</v>
+        <v>13860</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>267240</v>
+        <v>322320</v>
       </c>
       <c r="P5" t="n">
-        <v>46215</v>
+        <v>21216</v>
       </c>
       <c r="Q5" t="n">
         <v>1127723.58</v>
@@ -17462,7 +17462,7 @@
         <v>228906</v>
       </c>
       <c r="H6" t="n">
-        <v>39475350</v>
+        <v>42009570</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>2043285.04</v>
       </c>
       <c r="L6" t="n">
-        <v>14089896</v>
+        <v>13024962</v>
       </c>
       <c r="M6" t="n">
-        <v>300720</v>
+        <v>108360</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1037850</v>
+        <v>1020000</v>
       </c>
       <c r="P6" t="n">
-        <v>341347.5</v>
+        <v>226102.5</v>
       </c>
       <c r="Q6" t="n">
         <v>19586452.86</v>
@@ -17515,7 +17515,7 @@
         <v>514431</v>
       </c>
       <c r="H7" t="n">
-        <v>16477560</v>
+        <v>16727220</v>
       </c>
       <c r="I7" t="n">
         <v>371744.74</v>
@@ -17527,19 +17527,19 @@
         <v>1239149.12</v>
       </c>
       <c r="L7" t="n">
-        <v>14123160</v>
+        <v>13173840</v>
       </c>
       <c r="M7" t="n">
-        <v>793800</v>
+        <v>672525</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1240575</v>
+        <v>1313760</v>
       </c>
       <c r="P7" t="n">
-        <v>575250</v>
+        <v>471412.5</v>
       </c>
       <c r="Q7" t="n">
         <v>16538905.73</v>
@@ -17568,7 +17568,7 @@
         <v>1347840</v>
       </c>
       <c r="H8" t="n">
-        <v>2180250</v>
+        <v>3633750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>1179328.13</v>
       </c>
       <c r="L8" t="n">
-        <v>9811206</v>
+        <v>10662354</v>
       </c>
       <c r="M8" t="n">
-        <v>687225</v>
+        <v>2032800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2145825</v>
+        <v>2054025</v>
       </c>
       <c r="P8" t="n">
-        <v>799539</v>
+        <v>831402</v>
       </c>
       <c r="Q8" t="n">
         <v>16449299.86</v>
@@ -17621,7 +17621,7 @@
         <v>855117</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>272933.28</v>
       </c>
       <c r="L9" t="n">
-        <v>5904900</v>
+        <v>7243344</v>
       </c>
       <c r="M9" t="n">
-        <v>514500</v>
+        <v>3072300</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>914430</v>
+        <v>1438965</v>
       </c>
       <c r="P9" t="n">
-        <v>1177800</v>
+        <v>1175850</v>
       </c>
       <c r="Q9" t="n">
         <v>9225993.199999999</v>
@@ -17686,19 +17686,19 @@
         <v>84487.44</v>
       </c>
       <c r="L10" t="n">
-        <v>1485054</v>
+        <v>3498768</v>
       </c>
       <c r="M10" t="n">
-        <v>276675</v>
+        <v>3284400</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>74970</v>
+        <v>199920</v>
       </c>
       <c r="P10" t="n">
-        <v>2143147.5</v>
+        <v>2474647.5</v>
       </c>
       <c r="Q10" t="n">
         <v>1023550.56</v>
@@ -17739,10 +17739,10 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>772200</v>
+        <v>5351400</v>
       </c>
       <c r="M11" t="n">
-        <v>113400</v>
+        <v>3184650</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1791855</v>
+        <v>2779920</v>
       </c>
       <c r="Q11" t="n">
         <v>199540.8</v>
@@ -17780,7 +17780,7 @@
         <v>8100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>621000</v>
+        <v>4471200</v>
       </c>
       <c r="M12" t="n">
-        <v>69825</v>
+        <v>1995000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>1682850</v>
+        <v>3073200</v>
       </c>
       <c r="Q12" t="n">
         <v>145169.28</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>221400</v>
+        <v>1900800</v>
       </c>
       <c r="M13" t="n">
-        <v>52500</v>
+        <v>3307500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>928200</v>
+        <v>1673100</v>
       </c>
       <c r="Q13" t="n">
         <v>66960</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>86400</v>
+        <v>685800</v>
       </c>
       <c r="M14" t="n">
-        <v>21000</v>
+        <v>336000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>64800</v>
+        <v>1026000</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>819000</v>
+        <v>1394250</v>
       </c>
       <c r="Q15" t="n">
         <v>12789.36</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>507600</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>674700</v>
+        <v>1577550</v>
       </c>
       <c r="Q16" t="n">
         <v>7365.6</v>
@@ -18057,7 +18057,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>54000</v>
+        <v>475200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>230100</v>
+        <v>528450</v>
       </c>
       <c r="Q17" t="n">
         <v>3749.76</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>118800</v>
+        <v>210600</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>44850</v>
+        <v>79950</v>
       </c>
       <c r="Q18" t="n">
         <v>1071.36</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>21600</v>
+        <v>86400</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>84570</v>
       </c>
       <c r="H4" t="n">
-        <v>9930</v>
+        <v>12600</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>276810</v>
+        <v>320190</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>16260</v>
+        <v>12660</v>
       </c>
       <c r="O4" t="n">
-        <v>50400</v>
+        <v>54030</v>
       </c>
       <c r="P4" t="n">
-        <v>6270</v>
+        <v>3450</v>
       </c>
       <c r="Q4" t="n">
-        <v>27183.6</v>
+        <v>311478.75</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>19050</v>
       </c>
       <c r="H5" t="n">
-        <v>1860</v>
+        <v>3150</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>81420</v>
+        <v>107910</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>20790</v>
+        <v>27180</v>
       </c>
       <c r="O5" t="n">
-        <v>25950</v>
+        <v>36750</v>
       </c>
       <c r="P5" t="n">
-        <v>5190</v>
+        <v>7110</v>
       </c>
       <c r="Q5" t="n">
-        <v>7648.13</v>
+        <v>87634.8</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>2010</v>
       </c>
       <c r="H6" t="n">
-        <v>270</v>
+        <v>420</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12450</v>
+        <v>20460</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2220</v>
+        <v>5970</v>
       </c>
       <c r="O6" t="n">
-        <v>3990</v>
+        <v>6240</v>
       </c>
       <c r="P6" t="n">
-        <v>3540</v>
+        <v>7200</v>
       </c>
       <c r="Q6" t="n">
-        <v>675.13</v>
+        <v>7735.86</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1200</v>
+        <v>4140</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="O7" t="n">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="P7" t="n">
-        <v>3600</v>
+        <v>9060</v>
       </c>
       <c r="Q7" t="n">
-        <v>101.43</v>
+        <v>1162.26</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>210</v>
+        <v>540</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1200</v>
+        <v>4110</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.6</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>669.6</v>
+        <v>1134</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>17098.2</v>
+        <v>22661.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>207.9</v>
+        <v>271.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1297.5</v>
+        <v>1837.5</v>
       </c>
       <c r="P5" t="n">
-        <v>103.8</v>
+        <v>142.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>382.41</v>
+        <v>4381.74</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>100.5</v>
       </c>
       <c r="H6" t="n">
-        <v>153.9</v>
+        <v>239.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4606.5</v>
+        <v>7570.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>111</v>
+        <v>298.5</v>
       </c>
       <c r="O6" t="n">
-        <v>997.5</v>
+        <v>1560</v>
       </c>
       <c r="P6" t="n">
-        <v>531</v>
+        <v>1080</v>
       </c>
       <c r="Q6" t="n">
-        <v>506.35</v>
+        <v>5801.9</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>720</v>
+        <v>2484</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>16.8</v>
       </c>
       <c r="O7" t="n">
-        <v>115.5</v>
+        <v>315</v>
       </c>
       <c r="P7" t="n">
-        <v>900</v>
+        <v>2265</v>
       </c>
       <c r="Q7" t="n">
-        <v>81.15000000000001</v>
+        <v>929.8099999999999</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>149.1</v>
+        <v>383.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>456</v>
+        <v>1561.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.22</v>
+        <v>82.76000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3816720</v>
+        <v>6463800</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3077676</v>
+        <v>4078998</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>35343</v>
+        <v>46206</v>
       </c>
       <c r="O5" t="n">
-        <v>220575</v>
+        <v>312375</v>
       </c>
       <c r="P5" t="n">
-        <v>6747</v>
+        <v>9243</v>
       </c>
       <c r="Q5" t="n">
-        <v>229443.84</v>
+        <v>2629044</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>5427</v>
       </c>
       <c r="H6" t="n">
-        <v>877230</v>
+        <v>1364580</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>829170</v>
+        <v>1362636</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>18870</v>
+        <v>50745</v>
       </c>
       <c r="O6" t="n">
-        <v>169575</v>
+        <v>265200</v>
       </c>
       <c r="P6" t="n">
-        <v>34515</v>
+        <v>70200</v>
       </c>
       <c r="Q6" t="n">
-        <v>303808.32</v>
+        <v>3481137</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>129600</v>
+        <v>447120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>714</v>
+        <v>2856</v>
       </c>
       <c r="O7" t="n">
-        <v>19635</v>
+        <v>53550</v>
       </c>
       <c r="P7" t="n">
-        <v>58500</v>
+        <v>147225</v>
       </c>
       <c r="Q7" t="n">
-        <v>48688.13</v>
+        <v>557884.8</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>69012</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>29640</v>
+        <v>101517</v>
       </c>
       <c r="Q8" t="n">
-        <v>4333.82</v>
+        <v>49658.4</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10800</v>
+        <v>27000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>100712160</v>
+        <v>111608280</v>
       </c>
       <c r="I5" t="n">
         <v>192864.43</v>
@@ -22589,22 +22589,22 @@
         <v>3616208.1</v>
       </c>
       <c r="L5" t="n">
-        <v>31377780</v>
+        <v>32800950</v>
       </c>
       <c r="M5" t="n">
-        <v>352800</v>
+        <v>225540</v>
       </c>
       <c r="N5" t="n">
-        <v>98226</v>
+        <v>123471</v>
       </c>
       <c r="O5" t="n">
-        <v>1414230</v>
+        <v>1606245</v>
       </c>
       <c r="P5" t="n">
-        <v>78624</v>
+        <v>50544</v>
       </c>
       <c r="Q5" t="n">
-        <v>4047028.92</v>
+        <v>41938969.05</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>670194</v>
       </c>
       <c r="H6" t="n">
-        <v>185680350</v>
+        <v>188214570</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>4185041.64</v>
       </c>
       <c r="L6" t="n">
-        <v>42371586</v>
+        <v>42395562</v>
       </c>
       <c r="M6" t="n">
-        <v>830760</v>
+        <v>722400</v>
       </c>
       <c r="N6" t="n">
-        <v>116280</v>
+        <v>193545</v>
       </c>
       <c r="O6" t="n">
-        <v>4628250</v>
+        <v>5138250</v>
       </c>
       <c r="P6" t="n">
-        <v>594945</v>
+        <v>432022.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>48231840.42</v>
+        <v>499821894.68</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1640979</v>
       </c>
       <c r="H7" t="n">
-        <v>108726930</v>
+        <v>119836800</v>
       </c>
       <c r="I7" t="n">
         <v>495659.65</v>
@@ -22695,22 +22695,22 @@
         <v>3469617.54</v>
       </c>
       <c r="L7" t="n">
-        <v>53242920</v>
+        <v>53858520</v>
       </c>
       <c r="M7" t="n">
-        <v>2517375</v>
+        <v>3388350</v>
       </c>
       <c r="N7" t="n">
-        <v>35343</v>
+        <v>77826</v>
       </c>
       <c r="O7" t="n">
-        <v>4267935</v>
+        <v>4728465</v>
       </c>
       <c r="P7" t="n">
-        <v>1140262.5</v>
+        <v>877012.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>42112911.74</v>
+        <v>436412028.96</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>5742009</v>
       </c>
       <c r="H8" t="n">
-        <v>30378150</v>
+        <v>42006150</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -22748,22 +22748,22 @@
         <v>3430772.74</v>
       </c>
       <c r="L8" t="n">
-        <v>49259232</v>
+        <v>52169238</v>
       </c>
       <c r="M8" t="n">
-        <v>2413950</v>
+        <v>5930925</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7140</v>
       </c>
       <c r="O8" t="n">
-        <v>4702455</v>
+        <v>5234895</v>
       </c>
       <c r="P8" t="n">
-        <v>1713192</v>
+        <v>1627236</v>
       </c>
       <c r="Q8" t="n">
-        <v>43969504.97</v>
+        <v>455651724.87</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>5751729</v>
       </c>
       <c r="H9" t="n">
-        <v>24453000</v>
+        <v>26163000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>2456399.48</v>
       </c>
       <c r="L9" t="n">
-        <v>39571578</v>
+        <v>45091566</v>
       </c>
       <c r="M9" t="n">
-        <v>2447550</v>
+        <v>7791000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3295875</v>
+        <v>4802160</v>
       </c>
       <c r="P9" t="n">
-        <v>2424825</v>
+        <v>2313675</v>
       </c>
       <c r="Q9" t="n">
-        <v>35663729.65</v>
+        <v>369579779.05</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>4365900</v>
       </c>
       <c r="H10" t="n">
-        <v>30438000</v>
+        <v>28728000</v>
       </c>
       <c r="I10" t="n">
         <v>506924.64</v>
@@ -22854,22 +22854,22 @@
         <v>1351799.04</v>
       </c>
       <c r="L10" t="n">
-        <v>28845612</v>
+        <v>33435342</v>
       </c>
       <c r="M10" t="n">
-        <v>1954575</v>
+        <v>7684425</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1285200</v>
+        <v>2523990</v>
       </c>
       <c r="P10" t="n">
-        <v>4485195</v>
+        <v>5231070</v>
       </c>
       <c r="Q10" t="n">
-        <v>22197842.64</v>
+        <v>230034095.1</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>3124980</v>
       </c>
       <c r="H11" t="n">
-        <v>20520000</v>
+        <v>26847000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22907,22 +22907,22 @@
         <v>741668.62</v>
       </c>
       <c r="L11" t="n">
-        <v>28711800</v>
+        <v>37216800</v>
       </c>
       <c r="M11" t="n">
-        <v>1001700</v>
+        <v>8145900</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>680595</v>
+        <v>2015775</v>
       </c>
       <c r="P11" t="n">
-        <v>3720600</v>
+        <v>5791500</v>
       </c>
       <c r="Q11" t="n">
-        <v>16453076.4</v>
+        <v>170501638.5</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>2311740</v>
       </c>
       <c r="H12" t="n">
-        <v>5130000</v>
+        <v>7182000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>225057.06</v>
       </c>
       <c r="L12" t="n">
-        <v>14412600</v>
+        <v>22345200</v>
       </c>
       <c r="M12" t="n">
-        <v>957600</v>
+        <v>5665800</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>357000</v>
+        <v>591600</v>
       </c>
       <c r="P12" t="n">
-        <v>3162900</v>
+        <v>5405400</v>
       </c>
       <c r="Q12" t="n">
-        <v>10673089.2</v>
+        <v>110604190.5</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>1070820</v>
       </c>
       <c r="H13" t="n">
-        <v>4617000</v>
+        <v>5472000</v>
       </c>
       <c r="I13" t="n">
         <v>184415.69</v>
@@ -23013,22 +23013,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6523200</v>
+        <v>10486800</v>
       </c>
       <c r="M13" t="n">
-        <v>420000</v>
+        <v>6835500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>591600</v>
+        <v>663000</v>
       </c>
       <c r="P13" t="n">
-        <v>1992900</v>
+        <v>3001050</v>
       </c>
       <c r="Q13" t="n">
-        <v>5045302.08</v>
+        <v>52283977.2</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>325620</v>
       </c>
       <c r="H14" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,22 +23066,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2646000</v>
+        <v>5211000</v>
       </c>
       <c r="M14" t="n">
-        <v>115500</v>
+        <v>2152500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>76500</v>
+        <v>107100</v>
       </c>
       <c r="P14" t="n">
-        <v>2195700</v>
+        <v>2418000</v>
       </c>
       <c r="Q14" t="n">
-        <v>2314137.6</v>
+        <v>23981184</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>129600</v>
       </c>
       <c r="H15" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>869400</v>
+        <v>3369600</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>924000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="P15" t="n">
-        <v>2256150</v>
+        <v>3295500</v>
       </c>
       <c r="Q15" t="n">
-        <v>1066873.68</v>
+        <v>11055908.7</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>27540</v>
       </c>
       <c r="H16" t="n">
-        <v>513000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>334800</v>
+        <v>1501200</v>
       </c>
       <c r="M16" t="n">
-        <v>73500</v>
+        <v>483000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1560000</v>
+        <v>2560350</v>
       </c>
       <c r="Q16" t="n">
-        <v>630562.3199999999</v>
+        <v>6534456.3</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>9720</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>237600</v>
+        <v>1015200</v>
       </c>
       <c r="M17" t="n">
-        <v>52500</v>
+        <v>325500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1093950</v>
+        <v>1507350</v>
       </c>
       <c r="Q17" t="n">
-        <v>223110.72</v>
+        <v>2312074.8</v>
       </c>
     </row>
     <row r="18">
@@ -23278,22 +23278,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>280800</v>
+        <v>939600</v>
       </c>
       <c r="M18" t="n">
-        <v>31500</v>
+        <v>483000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1222650</v>
+        <v>1743300</v>
       </c>
       <c r="Q18" t="n">
-        <v>152133.12</v>
+        <v>1576540.8</v>
       </c>
     </row>
     <row r="19">
@@ -23319,7 +23319,7 @@
         <v>202500</v>
       </c>
       <c r="H19" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>113400</v>
+        <v>426600</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>483000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23343,10 +23343,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>327600</v>
+        <v>932100</v>
       </c>
       <c r="Q19" t="n">
-        <v>41515.2</v>
+        <v>430218</v>
       </c>
     </row>
     <row r="20">
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>8838.719999999999</v>
+        <v>91594.8</v>
       </c>
     </row>
     <row r="21">
@@ -23437,7 +23437,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>468.72</v>
+        <v>4857.3</v>
       </c>
     </row>
     <row r="22">
@@ -23816,7 +23816,7 @@
         <v>52500</v>
       </c>
       <c r="H4" t="n">
-        <v>8910</v>
+        <v>8160</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>66</v>
       </c>
       <c r="L4" t="n">
-        <v>154800</v>
+        <v>143640</v>
       </c>
       <c r="M4" t="n">
-        <v>32640</v>
+        <v>42570</v>
       </c>
       <c r="N4" t="n">
-        <v>16230</v>
+        <v>17250</v>
       </c>
       <c r="O4" t="n">
-        <v>16890</v>
+        <v>17220</v>
       </c>
       <c r="P4" t="n">
-        <v>2880</v>
+        <v>1110</v>
       </c>
       <c r="Q4" t="n">
-        <v>13490.56</v>
+        <v>132260.4</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>68550</v>
       </c>
       <c r="H5" t="n">
-        <v>11640</v>
+        <v>12090</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>61</v>
       </c>
       <c r="L5" t="n">
-        <v>192960</v>
+        <v>180390</v>
       </c>
       <c r="M5" t="n">
-        <v>12630</v>
+        <v>21540</v>
       </c>
       <c r="N5" t="n">
-        <v>13050</v>
+        <v>15000</v>
       </c>
       <c r="O5" t="n">
-        <v>19680</v>
+        <v>21720</v>
       </c>
       <c r="P5" t="n">
-        <v>3600</v>
+        <v>1350</v>
       </c>
       <c r="Q5" t="n">
-        <v>21742.55</v>
+        <v>213162.3</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>72540</v>
       </c>
       <c r="H6" t="n">
-        <v>19110</v>
+        <v>18000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>57</v>
       </c>
       <c r="L6" t="n">
-        <v>205740</v>
+        <v>199380</v>
       </c>
       <c r="M6" t="n">
-        <v>6300</v>
+        <v>13380</v>
       </c>
       <c r="N6" t="n">
-        <v>6060</v>
+        <v>8400</v>
       </c>
       <c r="O6" t="n">
-        <v>22530</v>
+        <v>21600</v>
       </c>
       <c r="P6" t="n">
-        <v>4260</v>
+        <v>2550</v>
       </c>
       <c r="Q6" t="n">
-        <v>26872.25</v>
+        <v>263453.4</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>91500</v>
       </c>
       <c r="H7" t="n">
-        <v>15240</v>
+        <v>17400</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -23987,22 +23987,22 @@
         <v>54</v>
       </c>
       <c r="L7" t="n">
-        <v>250230</v>
+        <v>256200</v>
       </c>
       <c r="M7" t="n">
-        <v>5370</v>
+        <v>14070</v>
       </c>
       <c r="N7" t="n">
-        <v>1230</v>
+        <v>2340</v>
       </c>
       <c r="O7" t="n">
-        <v>22650</v>
+        <v>23850</v>
       </c>
       <c r="P7" t="n">
-        <v>6090</v>
+        <v>4740</v>
       </c>
       <c r="Q7" t="n">
-        <v>26424.26</v>
+        <v>259061.4</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>95700</v>
       </c>
       <c r="H8" t="n">
-        <v>2400</v>
+        <v>3120</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>57</v>
       </c>
       <c r="L8" t="n">
-        <v>233670</v>
+        <v>242610</v>
       </c>
       <c r="M8" t="n">
-        <v>4080</v>
+        <v>11400</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>19680</v>
+        <v>20820</v>
       </c>
       <c r="P8" t="n">
-        <v>9000</v>
+        <v>6510</v>
       </c>
       <c r="Q8" t="n">
-        <v>28843.1</v>
+        <v>282775.5</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>86880</v>
       </c>
       <c r="H9" t="n">
-        <v>630</v>
+        <v>840</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>177810</v>
+        <v>200700</v>
       </c>
       <c r="M9" t="n">
-        <v>4890</v>
+        <v>10950</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22410</v>
+        <v>26940</v>
       </c>
       <c r="P9" t="n">
-        <v>11310</v>
+        <v>5280</v>
       </c>
       <c r="Q9" t="n">
-        <v>29301.18</v>
+        <v>287266.5</v>
       </c>
     </row>
     <row r="10">
@@ -24146,22 +24146,22 @@
         <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>97980</v>
+        <v>112770</v>
       </c>
       <c r="M10" t="n">
-        <v>3510</v>
+        <v>6450</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>9720</v>
+        <v>16890</v>
       </c>
       <c r="P10" t="n">
-        <v>15750</v>
+        <v>9690</v>
       </c>
       <c r="Q10" t="n">
-        <v>22027.59</v>
+        <v>215956.8</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>22890</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>60780</v>
+        <v>73080</v>
       </c>
       <c r="M11" t="n">
-        <v>2070</v>
+        <v>6090</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4680</v>
+        <v>13800</v>
       </c>
       <c r="P11" t="n">
         <v>14280</v>
       </c>
       <c r="Q11" t="n">
-        <v>14409.2</v>
+        <v>141266.7</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>23190</v>
+        <v>33480</v>
       </c>
       <c r="M12" t="n">
-        <v>2280</v>
+        <v>4590</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2100</v>
+        <v>3450</v>
       </c>
       <c r="P12" t="n">
-        <v>13320</v>
+        <v>12630</v>
       </c>
       <c r="Q12" t="n">
-        <v>8224.549999999999</v>
+        <v>80632.8</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8940</v>
+        <v>14700</v>
       </c>
       <c r="M13" t="n">
-        <v>870</v>
+        <v>4440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3480</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>12330</v>
+        <v>10860</v>
       </c>
       <c r="Q13" t="n">
-        <v>3750.76</v>
+        <v>36772.2</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2370</v>
+        <v>8040</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>1680</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="P14" t="n">
-        <v>21180</v>
+        <v>23550</v>
       </c>
       <c r="Q14" t="n">
-        <v>1310.54</v>
+        <v>12848.4</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>840</v>
+        <v>4320</v>
       </c>
       <c r="M15" t="n">
+        <v>780</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>90</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>21810</v>
+        <v>28650</v>
       </c>
       <c r="Q15" t="n">
-        <v>426.87</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="16">
@@ -24464,10 +24464,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>120</v>
+        <v>2370</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>13620</v>
+        <v>15120</v>
       </c>
       <c r="Q16" t="n">
-        <v>171.12</v>
+        <v>1677.6</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>1350</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13320</v>
+        <v>15090</v>
       </c>
       <c r="Q17" t="n">
-        <v>116.59</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="18">
@@ -24570,7 +24570,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1620</v>
       </c>
       <c r="M18" t="n">
         <v>90</v>
@@ -24579,13 +24579,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18120</v>
+        <v>25590</v>
       </c>
       <c r="Q18" t="n">
-        <v>103</v>
+        <v>1009.8</v>
       </c>
     </row>
     <row r="19">
@@ -24626,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5040</v>
+        <v>14340</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.36</v>
+        <v>366.3</v>
       </c>
     </row>
     <row r="20">
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.62</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="21">
@@ -24744,7 +24744,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.28</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4190.4</v>
+        <v>4352.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>20.19</v>
       </c>
       <c r="L5" t="n">
-        <v>40521.6</v>
+        <v>37881.9</v>
       </c>
       <c r="M5" t="n">
-        <v>252.6</v>
+        <v>430.8</v>
       </c>
       <c r="N5" t="n">
-        <v>130.5</v>
+        <v>150</v>
       </c>
       <c r="O5" t="n">
-        <v>984</v>
+        <v>1086</v>
       </c>
       <c r="P5" t="n">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
-        <v>1087.13</v>
+        <v>10658.12</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3627</v>
       </c>
       <c r="H6" t="n">
-        <v>10892.7</v>
+        <v>10260</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>28.9</v>
       </c>
       <c r="L6" t="n">
-        <v>76123.8</v>
+        <v>73770.60000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>504</v>
+        <v>1070.4</v>
       </c>
       <c r="N6" t="n">
-        <v>303</v>
+        <v>420</v>
       </c>
       <c r="O6" t="n">
-        <v>5632.5</v>
+        <v>5400</v>
       </c>
       <c r="P6" t="n">
-        <v>639</v>
+        <v>382.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>20154.19</v>
+        <v>197590.05</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>13725</v>
       </c>
       <c r="H7" t="n">
-        <v>11125.2</v>
+        <v>12702</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -25279,22 +25279,22 @@
         <v>34.45</v>
       </c>
       <c r="L7" t="n">
-        <v>150138</v>
+        <v>153720</v>
       </c>
       <c r="M7" t="n">
-        <v>1879.5</v>
+        <v>4924.5</v>
       </c>
       <c r="N7" t="n">
-        <v>86.09999999999999</v>
+        <v>163.8</v>
       </c>
       <c r="O7" t="n">
-        <v>7927.5</v>
+        <v>8347.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1522.5</v>
+        <v>1185</v>
       </c>
       <c r="Q7" t="n">
-        <v>21139.41</v>
+        <v>207249.12</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>62205</v>
       </c>
       <c r="H8" t="n">
-        <v>2040</v>
+        <v>2652</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>41.95</v>
       </c>
       <c r="L8" t="n">
-        <v>165905.7</v>
+        <v>172253.1</v>
       </c>
       <c r="M8" t="n">
-        <v>2244</v>
+        <v>6270</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8856</v>
+        <v>9369</v>
       </c>
       <c r="P8" t="n">
-        <v>3420</v>
+        <v>2473.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>27400.95</v>
+        <v>268636.72</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>73848</v>
       </c>
       <c r="H9" t="n">
-        <v>630</v>
+        <v>840</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>40.95</v>
       </c>
       <c r="L9" t="n">
-        <v>144026.1</v>
+        <v>162567</v>
       </c>
       <c r="M9" t="n">
-        <v>3423</v>
+        <v>7665</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>12325.5</v>
+        <v>14817</v>
       </c>
       <c r="P9" t="n">
-        <v>5655</v>
+        <v>2640</v>
       </c>
       <c r="Q9" t="n">
-        <v>28422.15</v>
+        <v>278648.5</v>
       </c>
     </row>
     <row r="10">
@@ -25438,22 +25438,22 @@
         <v>23.49</v>
       </c>
       <c r="L10" t="n">
-        <v>87202.2</v>
+        <v>100365.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2983.5</v>
+        <v>5482.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6804</v>
+        <v>11823</v>
       </c>
       <c r="P10" t="n">
-        <v>13387.5</v>
+        <v>8236.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>22027.59</v>
+        <v>215956.8</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>22890</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>8.09</v>
       </c>
       <c r="L11" t="n">
-        <v>60780</v>
+        <v>73080</v>
       </c>
       <c r="M11" t="n">
-        <v>1863</v>
+        <v>5481</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3978</v>
+        <v>11730</v>
       </c>
       <c r="P11" t="n">
         <v>12852</v>
       </c>
       <c r="Q11" t="n">
-        <v>14409.2</v>
+        <v>141266.7</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0.93</v>
       </c>
       <c r="L12" t="n">
-        <v>23190</v>
+        <v>33480</v>
       </c>
       <c r="M12" t="n">
-        <v>2166</v>
+        <v>4360.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2100</v>
+        <v>3450</v>
       </c>
       <c r="P12" t="n">
-        <v>13320</v>
+        <v>12630</v>
       </c>
       <c r="Q12" t="n">
-        <v>8224.549999999999</v>
+        <v>80632.8</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>8940</v>
+        <v>14700</v>
       </c>
       <c r="M13" t="n">
-        <v>870</v>
+        <v>4440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3480</v>
+        <v>3900</v>
       </c>
       <c r="P13" t="n">
-        <v>12330</v>
+        <v>10860</v>
       </c>
       <c r="Q13" t="n">
-        <v>3750.76</v>
+        <v>36772.2</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2370</v>
+        <v>8040</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>1680</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="P14" t="n">
-        <v>21180</v>
+        <v>23550</v>
       </c>
       <c r="Q14" t="n">
-        <v>1310.54</v>
+        <v>12848.4</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>840</v>
+        <v>4320</v>
       </c>
       <c r="M15" t="n">
+        <v>780</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>90</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>21810</v>
+        <v>28650</v>
       </c>
       <c r="Q15" t="n">
-        <v>426.87</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="16">
@@ -25756,10 +25756,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>120</v>
+        <v>2370</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>13620</v>
+        <v>15120</v>
       </c>
       <c r="Q16" t="n">
-        <v>171.12</v>
+        <v>1677.6</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>1350</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13320</v>
+        <v>15090</v>
       </c>
       <c r="Q17" t="n">
-        <v>116.59</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="18">
@@ -25862,7 +25862,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1620</v>
       </c>
       <c r="M18" t="n">
         <v>90</v>
@@ -25871,13 +25871,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P18" t="n">
-        <v>18120</v>
+        <v>25590</v>
       </c>
       <c r="Q18" t="n">
-        <v>103</v>
+        <v>1009.8</v>
       </c>
     </row>
     <row r="19">
@@ -25918,7 +25918,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5040</v>
+        <v>14340</v>
       </c>
       <c r="Q19" t="n">
-        <v>37.36</v>
+        <v>366.3</v>
       </c>
     </row>
     <row r="20">
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.62</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="21">
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.28</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>23885280</v>
+        <v>24808680</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>980394.2</v>
       </c>
       <c r="L5" t="n">
-        <v>7293888</v>
+        <v>6818742</v>
       </c>
       <c r="M5" t="n">
-        <v>88410</v>
+        <v>150780</v>
       </c>
       <c r="N5" t="n">
-        <v>22185</v>
+        <v>25500</v>
       </c>
       <c r="O5" t="n">
-        <v>167280</v>
+        <v>184620</v>
       </c>
       <c r="P5" t="n">
-        <v>4680</v>
+        <v>1755</v>
       </c>
       <c r="Q5" t="n">
-        <v>652276.64</v>
+        <v>6394869</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>195858</v>
       </c>
       <c r="H6" t="n">
-        <v>62088390</v>
+        <v>58482000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1403219.84</v>
       </c>
       <c r="L6" t="n">
-        <v>13702284</v>
+        <v>13278708</v>
       </c>
       <c r="M6" t="n">
-        <v>176400</v>
+        <v>374640</v>
       </c>
       <c r="N6" t="n">
-        <v>51510</v>
+        <v>71400</v>
       </c>
       <c r="O6" t="n">
-        <v>957525</v>
+        <v>918000</v>
       </c>
       <c r="P6" t="n">
-        <v>41535</v>
+        <v>24862.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12092511.06</v>
+        <v>118554030</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>741150</v>
       </c>
       <c r="H7" t="n">
-        <v>63413640</v>
+        <v>72401400</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -26571,22 +26571,22 @@
         <v>1672851.31</v>
       </c>
       <c r="L7" t="n">
-        <v>27024840</v>
+        <v>27669600</v>
       </c>
       <c r="M7" t="n">
-        <v>657825</v>
+        <v>1723575</v>
       </c>
       <c r="N7" t="n">
-        <v>14637</v>
+        <v>27846</v>
       </c>
       <c r="O7" t="n">
-        <v>1347675</v>
+        <v>1419075</v>
       </c>
       <c r="P7" t="n">
-        <v>98962.5</v>
+        <v>77025</v>
       </c>
       <c r="Q7" t="n">
-        <v>12683646.14</v>
+        <v>124349472</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>3359070</v>
       </c>
       <c r="H8" t="n">
-        <v>11628000</v>
+        <v>15116400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>2037021.31</v>
       </c>
       <c r="L8" t="n">
-        <v>29863026</v>
+        <v>31005558</v>
       </c>
       <c r="M8" t="n">
-        <v>785400</v>
+        <v>2194500</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1505520</v>
+        <v>1592730</v>
       </c>
       <c r="P8" t="n">
-        <v>222300</v>
+        <v>160797</v>
       </c>
       <c r="Q8" t="n">
-        <v>16440567.57</v>
+        <v>161182035</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>3987792</v>
       </c>
       <c r="H9" t="n">
-        <v>3591000</v>
+        <v>4788000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>1988513.87</v>
       </c>
       <c r="L9" t="n">
-        <v>25924698</v>
+        <v>29262060</v>
       </c>
       <c r="M9" t="n">
-        <v>1198050</v>
+        <v>2682750</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2095335</v>
+        <v>2518890</v>
       </c>
       <c r="P9" t="n">
-        <v>367575</v>
+        <v>171600</v>
       </c>
       <c r="Q9" t="n">
-        <v>17053288.51</v>
+        <v>167189103</v>
       </c>
     </row>
     <row r="10">
@@ -26730,22 +26730,22 @@
         <v>1140580.44</v>
       </c>
       <c r="L10" t="n">
-        <v>15696396</v>
+        <v>18065754</v>
       </c>
       <c r="M10" t="n">
-        <v>1044225</v>
+        <v>1918875</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1156680</v>
+        <v>2009910</v>
       </c>
       <c r="P10" t="n">
-        <v>870187.5</v>
+        <v>535372.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>13216556.16</v>
+        <v>129574080</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>1236060</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>392648.09</v>
       </c>
       <c r="L11" t="n">
-        <v>10940400</v>
+        <v>13154400</v>
       </c>
       <c r="M11" t="n">
-        <v>652050</v>
+        <v>1918350</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>676260</v>
+        <v>1994100</v>
       </c>
       <c r="P11" t="n">
         <v>835380</v>
       </c>
       <c r="Q11" t="n">
-        <v>8645522.039999999</v>
+        <v>84760020</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>45011.41</v>
       </c>
       <c r="L12" t="n">
-        <v>4174200</v>
+        <v>6026400</v>
       </c>
       <c r="M12" t="n">
-        <v>758100</v>
+        <v>1526175</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>357000</v>
+        <v>586500</v>
       </c>
       <c r="P12" t="n">
-        <v>865800</v>
+        <v>820950</v>
       </c>
       <c r="Q12" t="n">
-        <v>4934727.36</v>
+        <v>48379680</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1609200</v>
+        <v>2646000</v>
       </c>
       <c r="M13" t="n">
-        <v>304500</v>
+        <v>1554000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>591600</v>
+        <v>663000</v>
       </c>
       <c r="P13" t="n">
-        <v>801450</v>
+        <v>705900</v>
       </c>
       <c r="Q13" t="n">
-        <v>2250458.64</v>
+        <v>22063320</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>426600</v>
+        <v>1447200</v>
       </c>
       <c r="M14" t="n">
-        <v>42000</v>
+        <v>588000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>76500</v>
+        <v>107100</v>
       </c>
       <c r="P14" t="n">
-        <v>1376700</v>
+        <v>1530750</v>
       </c>
       <c r="Q14" t="n">
-        <v>786322.08</v>
+        <v>7709040</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>151200</v>
+        <v>777600</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>273000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>15300</v>
       </c>
       <c r="P15" t="n">
-        <v>1417650</v>
+        <v>1862250</v>
       </c>
       <c r="Q15" t="n">
-        <v>256122</v>
+        <v>2511000</v>
       </c>
     </row>
     <row r="16">
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>21600</v>
+        <v>426600</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>189000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>885300</v>
+        <v>982800</v>
       </c>
       <c r="Q16" t="n">
-        <v>102669.12</v>
+        <v>1006560</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>37800</v>
+        <v>243000</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>31500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>865800</v>
+        <v>980850</v>
       </c>
       <c r="Q17" t="n">
-        <v>69951.60000000001</v>
+        <v>685800</v>
       </c>
     </row>
     <row r="18">
@@ -27154,7 +27154,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>21600</v>
+        <v>291600</v>
       </c>
       <c r="M18" t="n">
         <v>31500</v>
@@ -27163,13 +27163,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P18" t="n">
-        <v>1177800</v>
+        <v>1663350</v>
       </c>
       <c r="Q18" t="n">
-        <v>61799.76</v>
+        <v>605880</v>
       </c>
     </row>
     <row r="19">
@@ -27210,7 +27210,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -27219,10 +27219,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>327600</v>
+        <v>932100</v>
       </c>
       <c r="Q19" t="n">
-        <v>22417.56</v>
+        <v>219780</v>
       </c>
     </row>
     <row r="20">
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q20" t="n">
-        <v>4571.64</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="21">
@@ -27328,7 +27328,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>165.24</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="22">
@@ -27692,7 +27692,7 @@
         <v>141810</v>
       </c>
       <c r="H4" t="n">
-        <v>26010</v>
+        <v>26190</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>87</v>
       </c>
       <c r="L4" t="n">
-        <v>403140</v>
+        <v>437400</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>72630</v>
+        <v>70470</v>
       </c>
       <c r="P4" t="n">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>41635.16</v>
+        <v>579730.14</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>83850</v>
       </c>
       <c r="H5" t="n">
-        <v>18990</v>
+        <v>20010</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>46</v>
       </c>
       <c r="L5" t="n">
-        <v>200910</v>
+        <v>222000</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>50130</v>
+        <v>51030</v>
       </c>
       <c r="P5" t="n">
-        <v>1170</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>23624.47</v>
+        <v>328948.29</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>51360</v>
       </c>
       <c r="H6" t="n">
-        <v>19410</v>
+        <v>19860</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>106140</v>
+        <v>114900</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>32010</v>
+        <v>38760</v>
       </c>
       <c r="P6" t="n">
-        <v>2370</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>8403.17</v>
+        <v>117006.12</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>15780</v>
       </c>
       <c r="H7" t="n">
-        <v>2520</v>
+        <v>3060</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>38850</v>
+        <v>43080</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>13530</v>
+        <v>15930</v>
       </c>
       <c r="P7" t="n">
-        <v>3510</v>
+        <v>420</v>
       </c>
       <c r="Q7" t="n">
-        <v>3743.63</v>
+        <v>52126.47</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>600</v>
       </c>
       <c r="H8" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6450</v>
+        <v>7980</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5970</v>
+        <v>10230</v>
       </c>
       <c r="P8" t="n">
-        <v>4650</v>
+        <v>1140</v>
       </c>
       <c r="Q8" t="n">
-        <v>208.68</v>
+        <v>2905.65</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>150</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1260</v>
+        <v>2310</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2250</v>
+        <v>7620</v>
       </c>
       <c r="P9" t="n">
-        <v>5280</v>
+        <v>3510</v>
       </c>
       <c r="Q9" t="n">
-        <v>33.91</v>
+        <v>472.23</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>330</v>
+        <v>2610</v>
       </c>
       <c r="P10" t="n">
-        <v>5550</v>
+        <v>9660</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.28</v>
+        <v>240.57</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>1680</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>2580</v>
+        <v>6300</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.91</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1590</v>
+        <v>5610</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>270</v>
+        <v>1230</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,7 +28246,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6836.4</v>
+        <v>7203.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>15.23</v>
       </c>
       <c r="L5" t="n">
-        <v>42191.1</v>
+        <v>46620</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2506.5</v>
+        <v>2551.5</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1181.22</v>
+        <v>16447.41</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2568</v>
       </c>
       <c r="H6" t="n">
-        <v>11063.7</v>
+        <v>11320.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>39271.8</v>
+        <v>42513</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8002.5</v>
+        <v>9690</v>
       </c>
       <c r="P6" t="n">
-        <v>355.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6302.38</v>
+        <v>87754.59</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>2367</v>
       </c>
       <c r="H7" t="n">
-        <v>1839.6</v>
+        <v>2233.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>1.28</v>
       </c>
       <c r="L7" t="n">
-        <v>23310</v>
+        <v>25848</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4735.5</v>
+        <v>5575.5</v>
       </c>
       <c r="P7" t="n">
-        <v>877.5</v>
+        <v>105</v>
       </c>
       <c r="Q7" t="n">
-        <v>2994.9</v>
+        <v>41701.18</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>390</v>
       </c>
       <c r="H8" t="n">
-        <v>408</v>
+        <v>535.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4579.5</v>
+        <v>5665.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2686.5</v>
+        <v>4603.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1767</v>
+        <v>433.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>198.24</v>
+        <v>2760.37</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>127.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1020.6</v>
+        <v>1871.1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1237.5</v>
+        <v>4191</v>
       </c>
       <c r="P9" t="n">
-        <v>2640</v>
+        <v>1755</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.9</v>
+        <v>458.06</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>373.8</v>
+        <v>2162.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>231</v>
+        <v>1827</v>
       </c>
       <c r="P10" t="n">
-        <v>4717.5</v>
+        <v>8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.28</v>
+        <v>240.57</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>1680</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
-        <v>2322</v>
+        <v>5670</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.91</v>
+        <v>54.45</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1590</v>
+        <v>5610</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>270</v>
+        <v>1230</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,7 +29538,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>38967480</v>
+        <v>41060520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>739313.66</v>
       </c>
       <c r="L5" t="n">
-        <v>7594398</v>
+        <v>8391600</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>426105</v>
+        <v>433755</v>
       </c>
       <c r="P5" t="n">
-        <v>1521</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>708734.04</v>
+        <v>9868448.699999999</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>138672</v>
       </c>
       <c r="H6" t="n">
-        <v>63063090</v>
+        <v>64525140</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>467739.95</v>
       </c>
       <c r="L6" t="n">
-        <v>7068924</v>
+        <v>7652340</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1360425</v>
+        <v>1647300</v>
       </c>
       <c r="P6" t="n">
-        <v>23107.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3781425.06</v>
+        <v>52652754</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>127818</v>
       </c>
       <c r="H7" t="n">
-        <v>10485720</v>
+        <v>12732660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>4195800</v>
+        <v>4652640</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>805035</v>
+        <v>947835</v>
       </c>
       <c r="P7" t="n">
-        <v>57037.5</v>
+        <v>6825</v>
       </c>
       <c r="Q7" t="n">
-        <v>1796941.58</v>
+        <v>25020705.6</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>21060</v>
       </c>
       <c r="H8" t="n">
-        <v>2325600</v>
+        <v>3052350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>824310</v>
+        <v>1019844</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>456705</v>
+        <v>782595</v>
       </c>
       <c r="P8" t="n">
-        <v>114855</v>
+        <v>28158</v>
       </c>
       <c r="Q8" t="n">
-        <v>118946.74</v>
+        <v>1656220.5</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>6885</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>183708</v>
+        <v>336798</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>210375</v>
+        <v>712470</v>
       </c>
       <c r="P9" t="n">
-        <v>171600</v>
+        <v>114075</v>
       </c>
       <c r="Q9" t="n">
-        <v>19738.36</v>
+        <v>274837.86</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>67284</v>
+        <v>389286</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>39270</v>
+        <v>310590</v>
       </c>
       <c r="P10" t="n">
-        <v>306637.5</v>
+        <v>533715</v>
       </c>
       <c r="Q10" t="n">
-        <v>10366.38</v>
+        <v>144342</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>1710000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>302400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
-        <v>150930</v>
+        <v>368550</v>
       </c>
       <c r="Q11" t="n">
-        <v>2346.3</v>
+        <v>32670</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>194400</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>103350</v>
+        <v>364650</v>
       </c>
       <c r="Q12" t="n">
-        <v>255.96</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>17550</v>
+        <v>79950</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.31999999999999</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1950</v>
+        <v>13650</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
